--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
@@ -171,7 +171,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 21.10.2026, 19:14:00 · ceny netto w zł · szablon NK38</t>
+    <t>Wygenerowano 21.10.2026, 19:25:58 · ceny netto w zł · szablon NK38</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 14%</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
@@ -171,7 +171,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 21.10.2026, 19:25:58 · ceny netto w zł · szablon NK38</t>
+    <t>Wygenerowano 22.10.2026, 08:15:57 · ceny netto w zł · szablon NK38</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 14%</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
@@ -171,7 +171,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 22.10.2026, 08:15:57 · ceny netto w zł · szablon NK38</t>
+    <t>Wygenerowano 22.10.2026, 08:47:04 · ceny netto w zł · szablon NK38</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 14%</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
@@ -171,7 +171,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 22.10.2026, 08:47:04 · ceny netto w zł · szablon NK38</t>
+    <t>Wygenerowano 23.10.2026, 05:42:40 · ceny netto w zł · szablon NK38</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 14%</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
@@ -171,7 +171,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 23.10.2026, 05:42:40 · ceny netto w zł · szablon NK38</t>
+    <t>Wygenerowano 23.10.2026, 06:31:44 · ceny netto w zł · szablon NK38</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 14%</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
@@ -171,7 +171,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 23.10.2026, 06:31:44 · ceny netto w zł · szablon NK38</t>
+    <t>Wygenerowano 23.10.2026, 06:32:55 · ceny netto w zł · szablon NK38</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 14%</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
@@ -171,7 +171,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 23.10.2026, 06:32:55 · ceny netto w zł · szablon NK38</t>
+    <t>Wygenerowano 27.10.2026, 12:24:44 · ceny netto w zł · szablon NK38</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 14%</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
@@ -171,7 +171,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 27.10.2026, 12:24:44 · ceny netto w zł · szablon NK38</t>
+    <t>Wygenerowano 27.10.2026, 14:03:05 · ceny netto w zł · szablon NK38</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 14%</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
@@ -171,7 +171,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 27.10.2026, 14:03:05 · ceny netto w zł · szablon NK38</t>
+    <t>Wygenerowano 27.10.2026, 14:04:44 · ceny netto w zł · szablon NK38</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 14%</t>
@@ -246,7 +246,7 @@
     <t>20 urządzeń = 80 miejsc postojowych</t>
   </si>
   <si>
-    <t>390 cm</t>
+    <t>P 390 cm</t>
   </si>
   <si>
     <t>Agregaty</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
@@ -157,7 +157,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="209">
   <si>
     <t>KALKULACJA NK38</t>
   </si>
@@ -171,7 +171,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 27.10.2026, 14:04:44 · ceny netto w zł · szablon NK38</t>
+    <t>Wygenerowano 27.10.2026, 14:13:51 · ceny netto w zł · szablon NK38</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 14%</t>
@@ -264,67 +264,73 @@
     <t>Barierki / maskownice / magistrala</t>
   </si>
   <si>
+    <t>KOB / GDW</t>
+  </si>
+  <si>
+    <t>barierki 20 · maskownice 0 · magistrala 6 × 6 m</t>
+  </si>
+  <si>
+    <t>0,5% / 2,5%</t>
+  </si>
+  <si>
+    <t>Opis wariantu</t>
+  </si>
+  <si>
+    <t>H-200/205 | L-540 | P-390 | Hpoj. G-185 D-185 | A-4 | Bok-20 Tył-0 | mgstrl-6</t>
+  </si>
+  <si>
+    <t>Lokalizacja</t>
+  </si>
+  <si>
+    <t>Montaż</t>
+  </si>
+  <si>
+    <t>Transport</t>
+  </si>
+  <si>
+    <t>Poza Krakowem · 80 km od Krakowa</t>
+  </si>
+  <si>
+    <t>9 tyg. (44 dni pracy), ekipa 4 os.</t>
+  </si>
+  <si>
+    <t>3 TIR × 2500 zł · Spider Crane 4 dni</t>
+  </si>
+  <si>
+    <t>Opcja (dopłata do ceny 2000 kg)</t>
+  </si>
+  <si>
+    <t>Skąd</t>
+  </si>
+  <si>
+    <t>przy zysku 14%</t>
+  </si>
+  <si>
+    <t>przy zysku 10%</t>
+  </si>
+  <si>
+    <t>Wariant 2500 kg</t>
+  </si>
+  <si>
+    <t>+7% do ceny urządzeń</t>
+  </si>
+  <si>
+    <t>Słupki e-ładowarek 3,7 kW</t>
+  </si>
+  <si>
+    <t>80 MP × 1700 zł + montaż</t>
+  </si>
+  <si>
+    <t>Słupki e-ładowarek 22 kW</t>
+  </si>
+  <si>
+    <t>jak 3,7 kW + 4600 zł/MP</t>
+  </si>
+  <si>
+    <t>Malowanie proszkowe RAL</t>
+  </si>
+  <si>
     <t/>
-  </si>
-  <si>
-    <t>barierki 20 · maskownice 0 · magistrala 6 × 6 m</t>
-  </si>
-  <si>
-    <t>Opis wariantu</t>
-  </si>
-  <si>
-    <t>H-200/205 | L-540 | P-390 | Hpoj. G-185 D-185 | A-4 | Bok-20 Tył-0 | mgstrl-6</t>
-  </si>
-  <si>
-    <t>Lokalizacja</t>
-  </si>
-  <si>
-    <t>Montaż</t>
-  </si>
-  <si>
-    <t>Transport</t>
-  </si>
-  <si>
-    <t>Poza Krakowem · 80 km od Krakowa</t>
-  </si>
-  <si>
-    <t>9 tyg. (44 dni pracy), ekipa 4 os.</t>
-  </si>
-  <si>
-    <t>3 TIR × 2500 zł · Spider Crane 4 dni</t>
-  </si>
-  <si>
-    <t>Opcja (dopłata do ceny 2000 kg)</t>
-  </si>
-  <si>
-    <t>Skąd</t>
-  </si>
-  <si>
-    <t>przy zysku 14%</t>
-  </si>
-  <si>
-    <t>przy zysku 10%</t>
-  </si>
-  <si>
-    <t>Wariant 2500 kg</t>
-  </si>
-  <si>
-    <t>+7% do ceny urządzeń</t>
-  </si>
-  <si>
-    <t>Słupki e-ładowarek 3,7 kW</t>
-  </si>
-  <si>
-    <t>80 MP × 1700 zł + montaż</t>
-  </si>
-  <si>
-    <t>Słupki e-ładowarek 22 kW</t>
-  </si>
-  <si>
-    <t>jak 3,7 kW + 4600 zł/MP</t>
-  </si>
-  <si>
-    <t>Malowanie proszkowe RAL</t>
   </si>
   <si>
     <t>Konserwacja · wariant 1 · 80 MP</t>
@@ -1994,17 +2000,17 @@
       <c r="B30" s="32"/>
       <c r="C30" s="32"/>
       <c r="D30" s="32" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E30" s="32"/>
       <c r="F30" s="32"/>
     </row>
     <row r="32" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B32" s="34" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C32" s="34"/>
       <c r="D32" s="34"/>
@@ -2013,54 +2019,54 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="35" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33" s="35"/>
       <c r="C33" s="35" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D33" s="35"/>
       <c r="E33" s="35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F33" s="35"/>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="36" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D34" s="36"/>
       <c r="E34" s="36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F34" s="36"/>
     </row>
     <row r="36" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
       <c r="E36" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C37" s="38"/>
       <c r="D37" s="38"/>
@@ -2073,10 +2079,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="37" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C38" s="38"/>
       <c r="D38" s="38"/>
@@ -2089,10 +2095,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C39" s="38"/>
       <c r="D39" s="38"/>
@@ -2105,10 +2111,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="37" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C40" s="38"/>
       <c r="D40" s="38"/>
@@ -2121,55 +2127,55 @@
     </row>
     <row r="42" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="40" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B42" s="40"/>
       <c r="C42" s="40"/>
       <c r="D42" s="40" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E42" s="40"/>
       <c r="F42" s="40"/>
     </row>
     <row r="43" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="41" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B43" s="41"/>
       <c r="C43" s="41"/>
       <c r="D43" s="41" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E43" s="41"/>
       <c r="F43" s="41"/>
     </row>
     <row r="44" ht="17" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="42" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B44" s="42"/>
       <c r="C44" s="42"/>
       <c r="D44" s="42" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E44" s="42"/>
       <c r="F44" s="42"/>
     </row>
     <row r="45" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="43" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B45" s="43"/>
       <c r="C45" s="43"/>
       <c r="D45" s="43" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E45" s="43"/>
       <c r="F45" s="43"/>
     </row>
     <row r="47" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B47" s="10"/>
       <c r="C47" s="10"/>
@@ -2179,10 +2185,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="44" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B48" s="45" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C48" s="45"/>
       <c r="D48" s="45"/>
@@ -2191,10 +2197,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="44" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B49" s="45" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C49" s="45"/>
       <c r="D49" s="45"/>
@@ -2203,10 +2209,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="44" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B50" s="45" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C50" s="45"/>
       <c r="D50" s="45"/>
@@ -2215,10 +2221,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="44" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B51" s="45" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C51" s="45"/>
       <c r="D51" s="45"/>
@@ -2227,10 +2233,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="44" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B52" s="45" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C52" s="45"/>
       <c r="D52" s="45"/>
@@ -2239,10 +2245,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="44" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B53" s="45" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C53" s="45"/>
       <c r="D53" s="45"/>
@@ -2333,7 +2339,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="46" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B1" s="46"/>
       <c r="C1" s="46"/>
@@ -2342,7 +2348,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -2351,7 +2357,7 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -2360,10 +2366,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="44" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B5" s="45" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C5" s="45"/>
       <c r="D5" s="45"/>
@@ -2371,10 +2377,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="44" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B6" s="45" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C6" s="45"/>
       <c r="D6" s="45"/>
@@ -2382,10 +2388,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="44" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B7" s="45" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C7" s="45"/>
       <c r="D7" s="45"/>
@@ -2393,10 +2399,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="44" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="45" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C8" s="45"/>
       <c r="D8" s="45"/>
@@ -2404,10 +2410,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="44" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B9" s="45" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C9" s="45"/>
       <c r="D9" s="45"/>
@@ -2415,10 +2421,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="44" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B10" s="45" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C10" s="45"/>
       <c r="D10" s="45"/>
@@ -2426,10 +2432,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="44" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B11" s="45" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C11" s="45"/>
       <c r="D11" s="45"/>
@@ -2437,10 +2443,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="44" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C12" s="45"/>
       <c r="D12" s="45"/>
@@ -2448,10 +2454,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="44" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B13" s="45" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C13" s="45"/>
       <c r="D13" s="45"/>
@@ -2459,10 +2465,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="44" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B14" s="45" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C14" s="45"/>
       <c r="D14" s="45"/>
@@ -2470,10 +2476,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="44" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B15" s="45" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C15" s="45"/>
       <c r="D15" s="45"/>
@@ -2481,7 +2487,7 @@
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -2490,23 +2496,23 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="47" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B18" s="47" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C18" s="47"/>
       <c r="D18" s="47"/>
       <c r="E18" s="48" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="49" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B19" s="50" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C19" s="50"/>
       <c r="D19" s="50"/>
@@ -2516,10 +2522,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="52" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B20" s="53" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C20" s="53"/>
       <c r="D20" s="53"/>
@@ -2529,10 +2535,10 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="49" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B21" s="50" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C21" s="50"/>
       <c r="D21" s="50"/>
@@ -2542,10 +2548,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="52" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B22" s="53" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C22" s="53"/>
       <c r="D22" s="53"/>
@@ -2555,10 +2561,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="49" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B23" s="50" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C23" s="50"/>
       <c r="D23" s="50"/>
@@ -2568,10 +2574,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="52" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B24" s="53" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C24" s="53"/>
       <c r="D24" s="53"/>
@@ -2584,7 +2590,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="50" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C25" s="50"/>
       <c r="D25" s="50"/>
@@ -2594,10 +2600,10 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="52" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B26" s="53" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C26" s="53"/>
       <c r="D26" s="53"/>
@@ -2607,10 +2613,10 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="49" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B27" s="50" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C27" s="50"/>
       <c r="D27" s="50"/>
@@ -2620,10 +2626,10 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="52" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B28" s="53" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C28" s="53"/>
       <c r="D28" s="53"/>
@@ -2633,10 +2639,10 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="49" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B29" s="50" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C29" s="50"/>
       <c r="D29" s="50"/>
@@ -2646,10 +2652,10 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="52" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B30" s="53" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C30" s="53"/>
       <c r="D30" s="53"/>
@@ -2659,10 +2665,10 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="49" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B31" s="50" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C31" s="50"/>
       <c r="D31" s="50"/>
@@ -2672,10 +2678,10 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="52" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B32" s="53" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C32" s="53"/>
       <c r="D32" s="53"/>
@@ -2685,10 +2691,10 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="49" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B33" s="50" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C33" s="50"/>
       <c r="D33" s="50"/>
@@ -2698,10 +2704,10 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="52" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B34" s="53" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C34" s="53"/>
       <c r="D34" s="53"/>
@@ -2711,10 +2717,10 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="58" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B35" s="59" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C35" s="59"/>
       <c r="D35" s="59"/>
@@ -2724,10 +2730,10 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="52" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B36" s="53" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C36" s="53"/>
       <c r="D36" s="53"/>
@@ -2737,10 +2743,10 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="49" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B37" s="50" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C37" s="50"/>
       <c r="D37" s="50"/>
@@ -2750,10 +2756,10 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="52" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B38" s="53" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C38" s="53"/>
       <c r="D38" s="53"/>
@@ -2763,10 +2769,10 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="49" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B39" s="50" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C39" s="50"/>
       <c r="D39" s="50"/>
@@ -2776,10 +2782,10 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="52" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B40" s="53" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C40" s="53"/>
       <c r="D40" s="53"/>
@@ -2789,10 +2795,10 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="58" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B41" s="59" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C41" s="59"/>
       <c r="D41" s="59"/>
@@ -2802,10 +2808,10 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="58" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B42" s="59" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C42" s="59"/>
       <c r="D42" s="59"/>
@@ -2815,7 +2821,7 @@
     </row>
     <row r="43" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="46" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B43" s="46"/>
       <c r="C43" s="46"/>
@@ -2824,7 +2830,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -2833,13 +2839,13 @@
     </row>
     <row r="46" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="61" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B46" s="62" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C46" s="63" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D46" s="63"/>
       <c r="E46" s="64">
@@ -2848,13 +2854,13 @@
     </row>
     <row r="47" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="63" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B47" s="64">
         <v>130</v>
       </c>
       <c r="C47" s="63" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D47" s="63"/>
       <c r="E47" s="64">
@@ -2863,13 +2869,13 @@
     </row>
     <row r="48" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="63" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B48" s="64">
         <v>45</v>
       </c>
       <c r="C48" s="63" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D48" s="63"/>
       <c r="E48" s="64">
@@ -2878,13 +2884,13 @@
     </row>
     <row r="49" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="61" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B49" s="62" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C49" s="63" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D49" s="63"/>
       <c r="E49" s="64">
@@ -2893,13 +2899,13 @@
     </row>
     <row r="50" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="63" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B50" s="65" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C50" s="63" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D50" s="63"/>
       <c r="E50" s="64">
@@ -2908,13 +2914,13 @@
     </row>
     <row r="51" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="63" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B51" s="65" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C51" s="63" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D51" s="63"/>
       <c r="E51" s="64">
@@ -2923,13 +2929,13 @@
     </row>
     <row r="52" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="63" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B52" s="65" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C52" s="63" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D52" s="63"/>
       <c r="E52" s="64">
@@ -2938,13 +2944,13 @@
     </row>
     <row r="53" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="61" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B53" s="62" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C53" s="63" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D53" s="63"/>
       <c r="E53" s="64">
@@ -2953,13 +2959,13 @@
     </row>
     <row r="54" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="63" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B54" s="64">
         <v>0</v>
       </c>
       <c r="C54" s="63" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D54" s="63"/>
       <c r="E54" s="64">
@@ -2968,13 +2974,13 @@
     </row>
     <row r="55" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="63" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B55" s="64">
         <v>500</v>
       </c>
       <c r="C55" s="63" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D55" s="63"/>
       <c r="E55" s="64">
@@ -2983,13 +2989,13 @@
     </row>
     <row r="56" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="63" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B56" s="64">
         <v>550</v>
       </c>
       <c r="C56" s="63" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D56" s="63"/>
       <c r="E56" s="64">
@@ -2998,13 +3004,13 @@
     </row>
     <row r="57" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="63" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B57" s="64">
         <v>600</v>
       </c>
       <c r="C57" s="63" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D57" s="63"/>
       <c r="E57" s="64">
@@ -3013,13 +3019,13 @@
     </row>
     <row r="58" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="63" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B58" s="64">
         <v>650</v>
       </c>
       <c r="C58" s="63" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D58" s="63"/>
       <c r="E58" s="64">
@@ -3028,13 +3034,13 @@
     </row>
     <row r="59" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="63" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B59" s="64">
         <v>700</v>
       </c>
       <c r="C59" s="63" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D59" s="63"/>
       <c r="E59" s="64">
@@ -3043,13 +3049,13 @@
     </row>
     <row r="60" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="63" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B60" s="64">
         <v>750</v>
       </c>
       <c r="C60" s="63" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D60" s="63"/>
       <c r="E60" s="64">
@@ -3058,13 +3064,13 @@
     </row>
     <row r="61" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="63" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B61" s="64">
         <v>800</v>
       </c>
       <c r="C61" s="63" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D61" s="63"/>
       <c r="E61" s="64">
@@ -3073,13 +3079,13 @@
     </row>
     <row r="62" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="63" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B62" s="64">
         <v>850</v>
       </c>
       <c r="C62" s="63" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D62" s="63"/>
       <c r="E62" s="64">
@@ -3088,13 +3094,13 @@
     </row>
     <row r="63" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="61" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B63" s="62" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C63" s="63" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D63" s="63"/>
       <c r="E63" s="64">
@@ -3103,13 +3109,13 @@
     </row>
     <row r="64" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="63" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B64" s="64">
         <v>1170</v>
       </c>
       <c r="C64" s="63" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D64" s="63"/>
       <c r="E64" s="64">
@@ -3118,13 +3124,13 @@
     </row>
     <row r="65" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="63" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B65" s="64">
         <v>1560</v>
       </c>
       <c r="C65" s="63" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D65" s="63"/>
       <c r="E65" s="64">
@@ -3133,13 +3139,13 @@
     </row>
     <row r="66" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="63" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B66" s="64">
         <v>1820</v>
       </c>
       <c r="C66" s="63" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D66" s="63"/>
       <c r="E66" s="64">
@@ -3148,13 +3154,13 @@
     </row>
     <row r="67" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="63" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B67" s="64">
         <v>3110</v>
       </c>
       <c r="C67" s="63" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D67" s="63"/>
       <c r="E67" s="64">
@@ -3163,13 +3169,13 @@
     </row>
     <row r="68" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="63" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B68" s="64">
         <v>2340</v>
       </c>
       <c r="C68" s="63" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D68" s="63"/>
       <c r="E68" s="64">
@@ -3178,13 +3184,13 @@
     </row>
     <row r="69" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="63" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B69" s="64">
         <v>10</v>
       </c>
       <c r="C69" s="63" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D69" s="63"/>
       <c r="E69" s="64">
@@ -3193,13 +3199,13 @@
     </row>
     <row r="70" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="63" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B70" s="64">
         <v>20</v>
       </c>
       <c r="C70" s="63" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D70" s="63"/>
       <c r="E70" s="64">
@@ -3208,13 +3214,13 @@
     </row>
     <row r="71" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="61" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B71" s="62" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C71" s="63" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D71" s="63"/>
       <c r="E71" s="64">
@@ -3223,17 +3229,17 @@
     </row>
     <row r="72" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="63" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B72" s="64">
         <v>45</v>
       </c>
       <c r="C72" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="D72"/>
       <c r="E72" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
@@ -171,7 +171,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 27.10.2026, 14:13:51 · ceny netto w zł · szablon NK38</t>
+    <t>Wygenerowano 27.10.2026, 14:16:58 · ceny netto w zł · szablon NK38</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 14%</t>
@@ -456,13 +456,13 @@
     <t>68 550 zł</t>
   </si>
   <si>
-    <t>Suma Q=2000 (dawne F87)</t>
+    <t>Suma Q=2000</t>
   </si>
   <si>
     <t>850 524 zł</t>
   </si>
   <si>
-    <t>Suma Q=2500 (dawne F90, +7%)</t>
+    <t>Suma Q=2500 (+7%)</t>
   </si>
   <si>
     <t>910 061 zł</t>
@@ -480,25 +480,25 @@
     <t>Kwota</t>
   </si>
   <si>
-    <t>Osobodni montażu (F50)</t>
+    <t>Osobodni montażu</t>
   </si>
   <si>
     <t>z cennika osobodni na urządzenie + utrudnienia</t>
   </si>
   <si>
-    <t>Tygodnie / dni montażu (B55)</t>
+    <t>Tygodnie / dni montażu</t>
   </si>
   <si>
     <t>tygodniowe wyjazdy ekipy</t>
   </si>
   <si>
-    <t>Osobodni podróży i rozładunku (G59)</t>
+    <t>Osobodni podróży i rozładunku</t>
   </si>
   <si>
     <t>pomiary, odbiory, rozładunek i dojazdy ekipy</t>
   </si>
   <si>
-    <t>Dni pracy ekipy (J39)</t>
+    <t>Dni pracy ekipy</t>
   </si>
   <si>
     <t>(osd montażu + podróży) ÷ 4 os.</t>
@@ -603,7 +603,7 @@
     <t>14% od robocizny (78 078 zł) i zysku z narzutem</t>
   </si>
   <si>
-    <t>Cena kontraktu, zysk 14% (K39)</t>
+    <t>Cena kontraktu, zysk 14%</t>
   </si>
   <si>
     <t>suma ÷ (1 − KOB − GDW − zysk) + podatek</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
@@ -157,7 +157,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="207">
   <si>
     <t>KALKULACJA NK38</t>
   </si>
@@ -171,7 +171,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 27.10.2026, 14:16:58 · ceny netto w zł · szablon NK38</t>
+    <t>Wygenerowano 27.10.2026, 14:20:06 · ceny netto w zł · szablon NK38</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 14%</t>
@@ -319,12 +319,6 @@
   </si>
   <si>
     <t>80 MP × 1700 zł + montaż</t>
-  </si>
-  <si>
-    <t>Słupki e-ładowarek 22 kW</t>
-  </si>
-  <si>
-    <t>jak 3,7 kW + 4600 zł/MP</t>
   </si>
   <si>
     <t>Malowanie proszkowe RAL</t>
@@ -1602,7 +1596,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2103,85 +2097,81 @@
       <c r="C39" s="38"/>
       <c r="D39" s="38"/>
       <c r="E39" s="39">
-        <v>647951.3450766264</v>
+        <v>337746.2650602409</v>
       </c>
       <c r="F39" s="39">
-        <v>614882.4343144828</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="37" t="s">
+        <v>320454.0229885057</v>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="B40" s="38" t="s">
+      <c r="B41" s="40"/>
+      <c r="C41" s="40"/>
+      <c r="D41" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="C40" s="38"/>
-      <c r="D40" s="38"/>
-      <c r="E40" s="39">
-        <v>337746.2650602409</v>
-      </c>
-      <c r="F40" s="39">
-        <v>320454.0229885057</v>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="40" t="s">
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+    </row>
+    <row r="42" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="B42" s="40"/>
-      <c r="C42" s="40"/>
-      <c r="D42" s="40" t="s">
+      <c r="B42" s="41"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="E42" s="40"/>
-      <c r="F42" s="40"/>
-    </row>
-    <row r="43" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="41" t="s">
+      <c r="E42" s="41"/>
+      <c r="F42" s="41"/>
+    </row>
+    <row r="43" ht="17" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="B43" s="41"/>
-      <c r="C43" s="41"/>
-      <c r="D43" s="41" t="s">
+      <c r="B43" s="42"/>
+      <c r="C43" s="42"/>
+      <c r="D43" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="E43" s="41"/>
-      <c r="F43" s="41"/>
-    </row>
-    <row r="44" ht="17" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="42" t="s">
+      <c r="E43" s="42"/>
+      <c r="F43" s="42"/>
+    </row>
+    <row r="44" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="B44" s="42"/>
-      <c r="C44" s="42"/>
-      <c r="D44" s="42" t="s">
+      <c r="B44" s="43"/>
+      <c r="C44" s="43"/>
+      <c r="D44" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="E44" s="42"/>
-      <c r="F44" s="42"/>
-    </row>
-    <row r="45" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="43" t="s">
+      <c r="E44" s="43"/>
+      <c r="F44" s="43"/>
+    </row>
+    <row r="46" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B45" s="43"/>
-      <c r="C45" s="43"/>
-      <c r="D45" s="43" t="s">
+      <c r="B46" s="10"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="E45" s="43"/>
-      <c r="F45" s="43"/>
-    </row>
-    <row r="47" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="10" t="s">
+      <c r="B47" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
+      <c r="C47" s="45"/>
+      <c r="D47" s="45"/>
+      <c r="E47" s="45"/>
+      <c r="F47" s="45"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="44" t="s">
@@ -2243,20 +2233,8 @@
       <c r="E52" s="45"/>
       <c r="F52" s="45"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="44" t="s">
-        <v>77</v>
-      </c>
-      <c r="B53" s="45" t="s">
-        <v>78</v>
-      </c>
-      <c r="C53" s="45"/>
-      <c r="D53" s="45"/>
-      <c r="E53" s="45"/>
-      <c r="F53" s="45"/>
-    </row>
   </sheetData>
-  <mergeCells count="62">
+  <mergeCells count="61">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A2:D2"/>
@@ -2303,22 +2281,21 @@
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="D41:F41"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="D42:F42"/>
     <mergeCell ref="A43:C43"/>
     <mergeCell ref="D43:F43"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="D44:F44"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="B47:F47"/>
     <mergeCell ref="B48:F48"/>
     <mergeCell ref="B49:F49"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B51:F51"/>
     <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B53:F53"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.25" footer="0.25"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="80" fitToWidth="1" fitToHeight="1"/>
@@ -2339,7 +2316,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="46" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B1" s="46"/>
       <c r="C1" s="46"/>
@@ -2348,7 +2325,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -2357,7 +2334,7 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -2366,10 +2343,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="44" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B5" s="45" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C5" s="45"/>
       <c r="D5" s="45"/>
@@ -2377,10 +2354,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="44" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B6" s="45" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C6" s="45"/>
       <c r="D6" s="45"/>
@@ -2388,10 +2365,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="44" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B7" s="45" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C7" s="45"/>
       <c r="D7" s="45"/>
@@ -2399,10 +2376,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="44" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B8" s="45" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C8" s="45"/>
       <c r="D8" s="45"/>
@@ -2410,10 +2387,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="44" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B9" s="45" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C9" s="45"/>
       <c r="D9" s="45"/>
@@ -2421,10 +2398,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="44" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B10" s="45" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C10" s="45"/>
       <c r="D10" s="45"/>
@@ -2432,10 +2409,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="44" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B11" s="45" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C11" s="45"/>
       <c r="D11" s="45"/>
@@ -2443,10 +2420,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="44" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C12" s="45"/>
       <c r="D12" s="45"/>
@@ -2454,10 +2431,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="44" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B13" s="45" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C13" s="45"/>
       <c r="D13" s="45"/>
@@ -2465,10 +2442,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="44" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B14" s="45" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C14" s="45"/>
       <c r="D14" s="45"/>
@@ -2476,10 +2453,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="44" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B15" s="45" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C15" s="45"/>
       <c r="D15" s="45"/>
@@ -2487,7 +2464,7 @@
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -2496,23 +2473,23 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="47" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B18" s="47" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C18" s="47"/>
       <c r="D18" s="47"/>
       <c r="E18" s="48" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="49" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B19" s="50" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C19" s="50"/>
       <c r="D19" s="50"/>
@@ -2522,10 +2499,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="52" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B20" s="53" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C20" s="53"/>
       <c r="D20" s="53"/>
@@ -2535,10 +2512,10 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="49" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B21" s="50" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C21" s="50"/>
       <c r="D21" s="50"/>
@@ -2548,10 +2525,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="52" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B22" s="53" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C22" s="53"/>
       <c r="D22" s="53"/>
@@ -2561,10 +2538,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="49" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B23" s="50" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C23" s="50"/>
       <c r="D23" s="50"/>
@@ -2574,10 +2551,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="52" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B24" s="53" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C24" s="53"/>
       <c r="D24" s="53"/>
@@ -2590,7 +2567,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="50" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C25" s="50"/>
       <c r="D25" s="50"/>
@@ -2600,10 +2577,10 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="52" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B26" s="53" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C26" s="53"/>
       <c r="D26" s="53"/>
@@ -2613,10 +2590,10 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="49" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B27" s="50" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C27" s="50"/>
       <c r="D27" s="50"/>
@@ -2629,7 +2606,7 @@
         <v>42</v>
       </c>
       <c r="B28" s="53" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C28" s="53"/>
       <c r="D28" s="53"/>
@@ -2639,10 +2616,10 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="49" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B29" s="50" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C29" s="50"/>
       <c r="D29" s="50"/>
@@ -2652,10 +2629,10 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="52" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B30" s="53" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C30" s="53"/>
       <c r="D30" s="53"/>
@@ -2665,10 +2642,10 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="49" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B31" s="50" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C31" s="50"/>
       <c r="D31" s="50"/>
@@ -2678,10 +2655,10 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="52" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B32" s="53" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C32" s="53"/>
       <c r="D32" s="53"/>
@@ -2694,7 +2671,7 @@
         <v>41</v>
       </c>
       <c r="B33" s="50" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C33" s="50"/>
       <c r="D33" s="50"/>
@@ -2704,10 +2681,10 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="52" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B34" s="53" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C34" s="53"/>
       <c r="D34" s="53"/>
@@ -2717,10 +2694,10 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="58" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B35" s="59" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C35" s="59"/>
       <c r="D35" s="59"/>
@@ -2730,10 +2707,10 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="52" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B36" s="53" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C36" s="53"/>
       <c r="D36" s="53"/>
@@ -2743,10 +2720,10 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="49" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B37" s="50" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C37" s="50"/>
       <c r="D37" s="50"/>
@@ -2756,10 +2733,10 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="52" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B38" s="53" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C38" s="53"/>
       <c r="D38" s="53"/>
@@ -2769,10 +2746,10 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="49" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B39" s="50" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C39" s="50"/>
       <c r="D39" s="50"/>
@@ -2782,10 +2759,10 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="52" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B40" s="53" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C40" s="53"/>
       <c r="D40" s="53"/>
@@ -2795,10 +2772,10 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="58" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B41" s="59" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C41" s="59"/>
       <c r="D41" s="59"/>
@@ -2808,10 +2785,10 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="58" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B42" s="59" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C42" s="59"/>
       <c r="D42" s="59"/>
@@ -2821,7 +2798,7 @@
     </row>
     <row r="43" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="46" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B43" s="46"/>
       <c r="C43" s="46"/>
@@ -2830,7 +2807,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -2842,10 +2819,10 @@
         <v>41</v>
       </c>
       <c r="B46" s="62" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C46" s="63" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D46" s="63"/>
       <c r="E46" s="64">
@@ -2854,13 +2831,13 @@
     </row>
     <row r="47" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="63" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B47" s="64">
         <v>130</v>
       </c>
       <c r="C47" s="63" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D47" s="63"/>
       <c r="E47" s="64">
@@ -2869,13 +2846,13 @@
     </row>
     <row r="48" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="63" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B48" s="64">
         <v>45</v>
       </c>
       <c r="C48" s="63" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D48" s="63"/>
       <c r="E48" s="64">
@@ -2884,13 +2861,13 @@
     </row>
     <row r="49" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="61" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B49" s="62" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C49" s="63" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D49" s="63"/>
       <c r="E49" s="64">
@@ -2899,13 +2876,13 @@
     </row>
     <row r="50" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="63" t="s">
+        <v>159</v>
+      </c>
+      <c r="B50" s="65" t="s">
+        <v>160</v>
+      </c>
+      <c r="C50" s="63" t="s">
         <v>161</v>
-      </c>
-      <c r="B50" s="65" t="s">
-        <v>162</v>
-      </c>
-      <c r="C50" s="63" t="s">
-        <v>163</v>
       </c>
       <c r="D50" s="63"/>
       <c r="E50" s="64">
@@ -2914,13 +2891,13 @@
     </row>
     <row r="51" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="63" t="s">
+        <v>162</v>
+      </c>
+      <c r="B51" s="65" t="s">
+        <v>163</v>
+      </c>
+      <c r="C51" s="63" t="s">
         <v>164</v>
-      </c>
-      <c r="B51" s="65" t="s">
-        <v>165</v>
-      </c>
-      <c r="C51" s="63" t="s">
-        <v>166</v>
       </c>
       <c r="D51" s="63"/>
       <c r="E51" s="64">
@@ -2929,13 +2906,13 @@
     </row>
     <row r="52" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="63" t="s">
+        <v>165</v>
+      </c>
+      <c r="B52" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="C52" s="63" t="s">
         <v>167</v>
-      </c>
-      <c r="B52" s="65" t="s">
-        <v>168</v>
-      </c>
-      <c r="C52" s="63" t="s">
-        <v>169</v>
       </c>
       <c r="D52" s="63"/>
       <c r="E52" s="64">
@@ -2944,13 +2921,13 @@
     </row>
     <row r="53" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="61" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B53" s="62" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C53" s="63" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D53" s="63"/>
       <c r="E53" s="64">
@@ -2959,13 +2936,13 @@
     </row>
     <row r="54" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="63" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B54" s="64">
         <v>0</v>
       </c>
       <c r="C54" s="63" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D54" s="63"/>
       <c r="E54" s="64">
@@ -2974,13 +2951,13 @@
     </row>
     <row r="55" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="63" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B55" s="64">
         <v>500</v>
       </c>
       <c r="C55" s="63" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D55" s="63"/>
       <c r="E55" s="64">
@@ -2989,13 +2966,13 @@
     </row>
     <row r="56" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="63" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B56" s="64">
         <v>550</v>
       </c>
       <c r="C56" s="63" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D56" s="63"/>
       <c r="E56" s="64">
@@ -3004,13 +2981,13 @@
     </row>
     <row r="57" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="63" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B57" s="64">
         <v>600</v>
       </c>
       <c r="C57" s="63" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D57" s="63"/>
       <c r="E57" s="64">
@@ -3019,13 +2996,13 @@
     </row>
     <row r="58" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="63" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B58" s="64">
         <v>650</v>
       </c>
       <c r="C58" s="63" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D58" s="63"/>
       <c r="E58" s="64">
@@ -3034,13 +3011,13 @@
     </row>
     <row r="59" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="63" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B59" s="64">
         <v>700</v>
       </c>
       <c r="C59" s="63" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D59" s="63"/>
       <c r="E59" s="64">
@@ -3049,13 +3026,13 @@
     </row>
     <row r="60" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="63" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B60" s="64">
         <v>750</v>
       </c>
       <c r="C60" s="63" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D60" s="63"/>
       <c r="E60" s="64">
@@ -3064,13 +3041,13 @@
     </row>
     <row r="61" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="63" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B61" s="64">
         <v>800</v>
       </c>
       <c r="C61" s="63" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D61" s="63"/>
       <c r="E61" s="64">
@@ -3079,13 +3056,13 @@
     </row>
     <row r="62" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="63" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B62" s="64">
         <v>850</v>
       </c>
       <c r="C62" s="63" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D62" s="63"/>
       <c r="E62" s="64">
@@ -3094,13 +3071,13 @@
     </row>
     <row r="63" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="61" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B63" s="62" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C63" s="63" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D63" s="63"/>
       <c r="E63" s="64">
@@ -3109,13 +3086,13 @@
     </row>
     <row r="64" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="63" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B64" s="64">
         <v>1170</v>
       </c>
       <c r="C64" s="63" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D64" s="63"/>
       <c r="E64" s="64">
@@ -3124,13 +3101,13 @@
     </row>
     <row r="65" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="63" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B65" s="64">
         <v>1560</v>
       </c>
       <c r="C65" s="63" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D65" s="63"/>
       <c r="E65" s="64">
@@ -3139,13 +3116,13 @@
     </row>
     <row r="66" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="63" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B66" s="64">
         <v>1820</v>
       </c>
       <c r="C66" s="63" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D66" s="63"/>
       <c r="E66" s="64">
@@ -3154,13 +3131,13 @@
     </row>
     <row r="67" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="63" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B67" s="64">
         <v>3110</v>
       </c>
       <c r="C67" s="63" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D67" s="63"/>
       <c r="E67" s="64">
@@ -3169,13 +3146,13 @@
     </row>
     <row r="68" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="63" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B68" s="64">
         <v>2340</v>
       </c>
       <c r="C68" s="63" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D68" s="63"/>
       <c r="E68" s="64">
@@ -3184,13 +3161,13 @@
     </row>
     <row r="69" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="63" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B69" s="64">
         <v>10</v>
       </c>
       <c r="C69" s="63" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D69" s="63"/>
       <c r="E69" s="64">
@@ -3199,13 +3176,13 @@
     </row>
     <row r="70" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="63" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B70" s="64">
         <v>20</v>
       </c>
       <c r="C70" s="63" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D70" s="63"/>
       <c r="E70" s="64">
@@ -3214,13 +3191,13 @@
     </row>
     <row r="71" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="61" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B71" s="62" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C71" s="63" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D71" s="63"/>
       <c r="E71" s="64">
@@ -3229,17 +3206,17 @@
     </row>
     <row r="72" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="63" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B72" s="64">
         <v>45</v>
       </c>
       <c r="C72" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D72"/>
       <c r="E72" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
@@ -171,7 +171,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 27.10.2026, 14:20:06 · ceny netto w zł · szablon NK38</t>
+    <t>Wygenerowano 27.10.2026, 14:21:22 · ceny netto w zł · szablon NK38</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 14%</t>
@@ -255,7 +255,7 @@
     <t>Wysokość pojazdów</t>
   </si>
   <si>
-    <t>4 szt.</t>
+    <t>4 szt. (3 kW / 6 kW: nie podano)</t>
   </si>
   <si>
     <t>▲ 185 cm    ▼ 185 cm</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
@@ -171,7 +171,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 27.10.2026, 14:21:22 · ceny netto w zł · szablon NK38</t>
+    <t>Wygenerowano 27.10.2026, 14:28:46 · ceny netto w zł · szablon NK38</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 14%</t>
@@ -183,13 +183,13 @@
     <t>Próg opłacalności · zysk 0%</t>
   </si>
   <si>
-    <t>15 146 zł / MP · 3502 € / MP</t>
-  </si>
-  <si>
-    <t>rabat −61 476 zł (−5,07%)</t>
-  </si>
-  <si>
-    <t>maks. rabat −192 985 zł (−15,93%)</t>
+    <t>15 186 zł / MP · 3511 € / MP</t>
+  </si>
+  <si>
+    <t>rabat −61 766 zł (−5,08%)</t>
+  </si>
+  <si>
+    <t>maks. rabat −193 847 zł (−15,96%)</t>
   </si>
   <si>
     <t>Pole do negocjacji: o ile można zejść z ceny (2000 kg)</t>
@@ -270,7 +270,7 @@
     <t>barierki 20 · maskownice 0 · magistrala 6 × 6 m</t>
   </si>
   <si>
-    <t>0,5% / 2,5%</t>
+    <t>0,52% / 2,69%</t>
   </si>
   <si>
     <t>Opis wariantu</t>
@@ -570,13 +570,13 @@
     <t>KOB</t>
   </si>
   <si>
-    <t>0,5% ceny przed podatkiem (1 173 624 zł)</t>
+    <t>0,52% ceny przed podatkiem (1 176 459 zł)</t>
   </si>
   <si>
     <t>GDW</t>
   </si>
   <si>
-    <t>2,5% ceny przed podatkiem</t>
+    <t>2,69% ceny przed podatkiem</t>
   </si>
   <si>
     <t>Zysk 14%</t>
@@ -588,7 +588,7 @@
     <t>Zysk z narzutem (zysk + GDW)</t>
   </si>
   <si>
-    <t>zysk 14% + GDW 2,5%</t>
+    <t>zysk 14% + GDW 2,69%</t>
   </si>
   <si>
     <t>Podatek</t>
@@ -1655,15 +1655,15 @@
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
-        <v>1211666.1118636145</v>
+        <v>1214871.141271744</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7">
-        <v>1150189.775685977</v>
+        <v>1153105.4573421704</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="8">
-        <v>1018681.1183987629</v>
+        <v>1021023.8811704587</v>
       </c>
       <c r="F6" s="8"/>
     </row>
@@ -1716,7 +1716,7 @@
         <v>0.14</v>
       </c>
       <c r="B11" s="14">
-        <v>1211666.1118636145</v>
+        <v>1214871.141271744</v>
       </c>
       <c r="C11" s="14">
         <v>0</v>
@@ -1725,10 +1725,10 @@
         <v>0</v>
       </c>
       <c r="E11" s="14">
-        <v>193648.03077108436</v>
+        <v>196292.22928816426</v>
       </c>
       <c r="F11" s="14">
-        <v>15145.826398295181</v>
+        <v>15185.8892658968</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1736,19 +1736,19 @@
         <v>0.12</v>
       </c>
       <c r="B12" s="17">
-        <v>1180204.692760941</v>
+        <v>1183259.9303926933</v>
       </c>
       <c r="C12" s="17">
-        <v>-31461.41910267342</v>
+        <v>-31611.21087905066</v>
       </c>
       <c r="D12" s="18">
-        <v>-0.025965419676781985</v>
+        <v>-0.026020217128509292</v>
       </c>
       <c r="E12" s="17">
-        <v>166171.41178823527</v>
+        <v>168688.44378608488</v>
       </c>
       <c r="F12" s="17">
-        <v>14752.558659511764</v>
+        <v>14790.749129908665</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1756,19 +1756,19 @@
         <v>0.1</v>
       </c>
       <c r="B13" s="20">
-        <v>1150189.775685977</v>
+        <v>1153105.4573421704</v>
       </c>
       <c r="C13" s="20">
-        <v>-61476.33617763757</v>
+        <v>-61765.68392957351</v>
       </c>
       <c r="D13" s="21">
-        <v>-0.050737026954631344</v>
+        <v>-0.05084134591008256</v>
       </c>
       <c r="E13" s="20">
-        <v>139958.0856321839</v>
+        <v>142356.72213202767</v>
       </c>
       <c r="F13" s="20">
-        <v>14377.372196074712</v>
+        <v>14413.81821677713</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1776,19 +1776,19 @@
         <v>0.08</v>
       </c>
       <c r="B14" s="23">
-        <v>1121523.8436480898</v>
+        <v>1124309.2938885181</v>
       </c>
       <c r="C14" s="23">
-        <v>-90142.26821552473</v>
+        <v>-90561.8473832258</v>
       </c>
       <c r="D14" s="24">
-        <v>-0.07439530356830774</v>
+        <v>-0.07454440582762087</v>
       </c>
       <c r="E14" s="23">
-        <v>114922.88649438204</v>
+        <v>117211.11406599099</v>
       </c>
       <c r="F14" s="23">
-        <v>14019.048045601123</v>
+        <v>14053.866173606477</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1796,19 +1796,19 @@
         <v>0.06</v>
       </c>
       <c r="B15" s="23">
-        <v>1094117.9525789008</v>
+        <v>1096781.6838909737</v>
       </c>
       <c r="C15" s="23">
-        <v>-117548.15928471368</v>
+        <v>-118089.45738077024</v>
       </c>
       <c r="D15" s="24">
-        <v>-0.09701365593522923</v>
+        <v>-0.09720327808359376</v>
       </c>
       <c r="E15" s="23">
-        <v>90988.13567032965</v>
+        <v>93173.24203810573</v>
       </c>
       <c r="F15" s="23">
-        <v>13676.474407236261</v>
+        <v>13709.77104863717</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1816,19 +1816,19 @@
         <v>0.04</v>
       </c>
       <c r="B16" s="23">
-        <v>1067890.809512688</v>
+        <v>1070440.6088071163</v>
       </c>
       <c r="C16" s="23">
-        <v>-143775.30235092645</v>
+        <v>-144430.53246462764</v>
       </c>
       <c r="D16" s="24">
-        <v>-0.11865917594228288</v>
+        <v>-0.11888547481129214</v>
       </c>
       <c r="E16" s="23">
-        <v>68082.83649462365</v>
+        <v>70171.4851838362</v>
       </c>
       <c r="F16" s="23">
-        <v>13348.635118908602</v>
+        <v>13380.507610088953</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1836,19 +1836,19 @@
         <v>0.02</v>
       </c>
       <c r="B17" s="23">
-        <v>1042767.9672071579</v>
+        <v>1045210.9714905105</v>
       </c>
       <c r="C17" s="23">
-        <v>-168898.14465645666</v>
+        <v>-169660.16978123342</v>
       </c>
       <c r="D17" s="24">
-        <v>-0.13939330563325011</v>
+        <v>-0.13965281091756843</v>
       </c>
       <c r="E17" s="23">
-        <v>46141.970968421054</v>
+        <v>48140.26659345992</v>
       </c>
       <c r="F17" s="23">
-        <v>13034.599590089474</v>
+        <v>13065.137143631382</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1856,19 +1856,19 @@
         <v>0</v>
       </c>
       <c r="B18" s="26">
-        <v>1018681.1183987629</v>
+        <v>1021023.8811704587</v>
       </c>
       <c r="C18" s="26">
-        <v>-192984.99346485164</v>
+        <v>-193847.26010128518</v>
       </c>
       <c r="D18" s="27">
-        <v>-0.15927241966685793</v>
+        <v>-0.1595619926392878</v>
       </c>
       <c r="E18" s="26">
-        <v>25105.883402061856</v>
+        <v>27019.428936570246</v>
       </c>
       <c r="F18" s="26">
-        <v>12733.513979984536</v>
+        <v>12762.798514630735</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2065,10 +2065,10 @@
       <c r="C37" s="38"/>
       <c r="D37" s="38"/>
       <c r="E37" s="39">
-        <v>73387.94172457838</v>
+        <v>73583.83047722955</v>
       </c>
       <c r="F37" s="39">
-        <v>69630.55878735636</v>
+        <v>69808.76284417766</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2081,10 +2081,10 @@
       <c r="C38" s="38"/>
       <c r="D38" s="38"/>
       <c r="E38" s="39">
-        <v>194335.92338987952</v>
+        <v>194849.14933479228</v>
       </c>
       <c r="F38" s="39">
-        <v>184491.62971678167</v>
+        <v>184958.52199217537</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2097,10 +2097,10 @@
       <c r="C39" s="38"/>
       <c r="D39" s="38"/>
       <c r="E39" s="39">
-        <v>337746.2650602409</v>
+        <v>338647.7850241546</v>
       </c>
       <c r="F39" s="39">
-        <v>320454.0229885057</v>
+        <v>321274.1543778802</v>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2715,7 +2715,7 @@
       <c r="C36" s="53"/>
       <c r="D36" s="53"/>
       <c r="E36" s="57">
-        <v>5868.122144578314</v>
+        <v>6058.765243236716</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2728,7 +2728,7 @@
       <c r="C37" s="50"/>
       <c r="D37" s="50"/>
       <c r="E37" s="56">
-        <v>29340.610722891568</v>
+        <v>31587.931413768118</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -2741,7 +2741,7 @@
       <c r="C38" s="53"/>
       <c r="D38" s="53"/>
       <c r="E38" s="57">
-        <v>164307.42004819278</v>
+        <v>164704.29787439617</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2754,7 +2754,7 @@
       <c r="C39" s="50"/>
       <c r="D39" s="50"/>
       <c r="E39" s="56">
-        <v>193648.03077108436</v>
+        <v>196292.22928816426</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -2767,7 +2767,7 @@
       <c r="C40" s="53"/>
       <c r="D40" s="53"/>
       <c r="E40" s="57">
-        <v>38041.68294795181</v>
+        <v>38411.870740343</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2780,7 +2780,7 @@
       <c r="C41" s="59"/>
       <c r="D41" s="59"/>
       <c r="E41" s="60">
-        <v>1211666.1118636145</v>
+        <v>1214871.141271744</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2793,7 +2793,7 @@
       <c r="C42" s="59"/>
       <c r="D42" s="59"/>
       <c r="E42" s="60">
-        <v>1018018.0810925302</v>
+        <v>1018578.9119835796</v>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
@@ -157,7 +157,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="210">
   <si>
     <t>KALKULACJA NK38</t>
   </si>
@@ -171,25 +171,37 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 27.10.2026, 14:28:46 · ceny netto w zł · szablon NK38</t>
-  </si>
-  <si>
-    <t>Cena ofertowa · zysk 14%</t>
+    <t>Wygenerowano 27.10.2026, 14:33:07 · ceny netto w zł · szablon NK38</t>
+  </si>
+  <si>
+    <t>Cena</t>
+  </si>
+  <si>
+    <t>Cena netto</t>
+  </si>
+  <si>
+    <t>Cena za MP</t>
+  </si>
+  <si>
+    <t>Rabat od oferty</t>
+  </si>
+  <si>
+    <t>Cena ofertowa · zysk 14% · 2000 kg · 3511 € / MP</t>
+  </si>
+  <si>
+    <t>–</t>
   </si>
   <si>
     <t>Można zejść do · zysk 10%</t>
   </si>
   <si>
-    <t>Próg opłacalności · zysk 0%</t>
-  </si>
-  <si>
-    <t>15 186 zł / MP · 3511 € / MP</t>
-  </si>
-  <si>
-    <t>rabat −61 766 zł (−5,08%)</t>
-  </si>
-  <si>
-    <t>maks. rabat −193 847 zł (−15,96%)</t>
+    <t>−61 766 zł (−5,08%)</t>
+  </si>
+  <si>
+    <t>Próg opłacalności · zysk 0% (maks. rabat)</t>
+  </si>
+  <si>
+    <t>−193 847 zł (−15,96%)</t>
   </si>
   <si>
     <t>Pole do negocjacji: o ile można zejść z ceny (2000 kg)</t>
@@ -198,21 +210,12 @@
     <t>Zysk</t>
   </si>
   <si>
-    <t>Cena netto</t>
-  </si>
-  <si>
-    <t>Rabat od oferty</t>
-  </si>
-  <si>
     <t>Rabat %</t>
   </si>
   <si>
     <t>Zysk z narzutem</t>
   </si>
   <si>
-    <t>Cena za MP</t>
-  </si>
-  <si>
     <t>Zielone: rabat bez zejścia poniżej zysku 10%. Żółte: poniżej zysku do porównania. Przy zysku 0% w cenie zostają koszty, KOB, GDW i podatek.</t>
   </si>
   <si>
@@ -270,7 +273,7 @@
     <t>barierki 20 · maskownice 0 · magistrala 6 × 6 m</t>
   </si>
   <si>
-    <t>0,52% / 2,69%</t>
+    <t>0,515% / 2,685%</t>
   </si>
   <si>
     <t>Opis wariantu</t>
@@ -327,28 +330,34 @@
     <t/>
   </si>
   <si>
-    <t>Konserwacja · wariant 1 · 80 MP</t>
-  </si>
-  <si>
-    <t>Konserwacja · wariant 2 · 80 MP</t>
-  </si>
-  <si>
-    <t>40 zł / MP / mies.</t>
-  </si>
-  <si>
-    <t>50 zł / MP / mies.</t>
-  </si>
-  <si>
-    <t>38 400 zł rocznie</t>
-  </si>
-  <si>
-    <t>48 000 zł rocznie</t>
-  </si>
-  <si>
-    <t>jeden przegląd (co pół roku): 19 200 zł</t>
-  </si>
-  <si>
-    <t>jeden przegląd (co pół roku): 24 000 zł</t>
+    <t>Konserwacja (80 MP)</t>
+  </si>
+  <si>
+    <t>Miesięcznie</t>
+  </si>
+  <si>
+    <t>Rocznie</t>
+  </si>
+  <si>
+    <t>Jeden przegląd (co pół roku)</t>
+  </si>
+  <si>
+    <t>35 zł / MP / mies.</t>
+  </si>
+  <si>
+    <t>40 zł / MP / mies.  · wariant 1</t>
+  </si>
+  <si>
+    <t>45 zł / MP / mies.</t>
+  </si>
+  <si>
+    <t>50 zł / MP / mies.  · wariant 2</t>
+  </si>
+  <si>
+    <t>55 zł / MP / mies.</t>
+  </si>
+  <si>
+    <t>60 zł / MP / mies.</t>
   </si>
   <si>
     <t>Pozostałe dane wejściowe</t>
@@ -390,7 +399,7 @@
     <t>4.325</t>
   </si>
   <si>
-    <t>Koszty krok po kroku · 2000 kg, zysk 14%</t>
+    <t>Koszty · 2000 kg · 14%</t>
   </si>
   <si>
     <t>Strona 1: obliczenia · strona 2: cennik szablonu NK38</t>
@@ -570,13 +579,13 @@
     <t>KOB</t>
   </si>
   <si>
-    <t>0,52% ceny przed podatkiem (1 176 459 zł)</t>
+    <t>0,515% ceny przed podatkiem (1 176 459 zł)</t>
   </si>
   <si>
     <t>GDW</t>
   </si>
   <si>
-    <t>2,69% ceny przed podatkiem</t>
+    <t>2,685% ceny przed podatkiem</t>
   </si>
   <si>
     <t>Zysk 14%</t>
@@ -588,7 +597,7 @@
     <t>Zysk z narzutem (zysk + GDW)</t>
   </si>
   <si>
-    <t>zysk 14% + GDW 2,69%</t>
+    <t>zysk 14% + GDW 2,685%</t>
   </si>
   <si>
     <t>Podatek</t>
@@ -794,7 +803,7 @@
     <numFmt numFmtId="170" formatCode="&quot;+&quot;#,##0 &quot;zł&quot;"/>
     <numFmt numFmtId="171" formatCode="#,##0.##"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -803,19 +812,19 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FFC4E4E7"/>
+      <color rgb="FF6A7780"/>
       <sz val="8"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="15"/>
+      <color rgb="FF0E171C"/>
+      <sz val="16"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF0E171C"/>
       <sz val="13"/>
       <name val="Arial"/>
     </font>
@@ -827,13 +836,18 @@
     <font>
       <b/>
       <color rgb="FF0A6B74"/>
-      <sz val="16"/>
+      <sz val="9"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="FF0E171C"/>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0E171C"/>
-      <sz val="16"/>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -845,17 +859,6 @@
     <font>
       <b/>
       <color rgb="FF0A6B74"/>
-      <sz val="9"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF0A6B74"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FF0E171C"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -888,22 +891,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF0E171C"/>
-      <sz val="9.5"/>
-      <name val="Consolas"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF0E171C"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FF0E171C"/>
-      <sz val="9.5"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <color rgb="FF6A7780"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -920,22 +907,12 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF0A6B74"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3F8F8"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -973,49 +950,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD3D9DD"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD3D9DD"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF0A6B74"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD3D9DD"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD3D9DD"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD3D9DD"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD3D9DD"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFD3D9DD"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1045,8 +985,8 @@
     <border>
       <left/>
       <right/>
-      <top style="medium">
-        <color rgb="FF0A6B74"/>
+      <top style="thin">
+        <color rgb="FFD3D9DD"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -1064,197 +1004,189 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="11" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="12" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="bottom" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="10" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment indent="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1596,13 +1528,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="3" width="17" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="6" width="17" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1639,621 +1573,700 @@
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
     </row>
-    <row r="5" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="6"/>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="6"/>
+      <c r="D5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="6"/>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="F5" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="9">
         <v>1214871.141271744</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7">
+      <c r="E6" s="9">
+        <v>15185.8892658968</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="9">
         <v>1153105.4573421704</v>
       </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="8">
+      <c r="E7" s="9">
+        <v>14413.81821677713</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="9">
         <v>1021023.8811704587</v>
       </c>
-      <c r="F6" s="8"/>
-    </row>
-    <row r="7" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="E8" s="9">
+        <v>12762.798514630735</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+    </row>
+    <row r="11" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="9"/>
-    </row>
-    <row r="9" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-    </row>
-    <row r="10" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="12" t="s">
+      <c r="D11" s="13" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="13">
+      <c r="E11" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="14">
         <v>0.14</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B12" s="15">
         <v>1214871.141271744</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C12" s="15">
         <v>0</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D12" s="16">
         <v>0</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E12" s="15">
         <v>196292.22928816426</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F12" s="15">
         <v>15185.8892658968</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="16">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
         <v>0.12</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B13" s="18">
         <v>1183259.9303926933</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C13" s="18">
         <v>-31611.21087905066</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D13" s="19">
         <v>-0.026020217128509292</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E13" s="18">
         <v>168688.44378608488</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F13" s="18">
         <v>14790.749129908665</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="19">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="20">
         <v>0.1</v>
       </c>
-      <c r="B13" s="20">
+      <c r="B14" s="21">
         <v>1153105.4573421704</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C14" s="21">
         <v>-61765.68392957351</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D14" s="22">
         <v>-0.05084134591008256</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E14" s="21">
         <v>142356.72213202767</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F14" s="21">
         <v>14413.81821677713</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="22">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="23">
         <v>0.08</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B15" s="24">
         <v>1124309.2938885181</v>
       </c>
-      <c r="C14" s="23">
+      <c r="C15" s="24">
         <v>-90561.8473832258</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D15" s="25">
         <v>-0.07454440582762087</v>
       </c>
-      <c r="E14" s="23">
+      <c r="E15" s="24">
         <v>117211.11406599099</v>
       </c>
-      <c r="F14" s="23">
+      <c r="F15" s="24">
         <v>14053.866173606477</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="22">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="23">
         <v>0.06</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B16" s="24">
         <v>1096781.6838909737</v>
       </c>
-      <c r="C15" s="23">
+      <c r="C16" s="24">
         <v>-118089.45738077024</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D16" s="25">
         <v>-0.09720327808359376</v>
       </c>
-      <c r="E15" s="23">
+      <c r="E16" s="24">
         <v>93173.24203810573</v>
       </c>
-      <c r="F15" s="23">
+      <c r="F16" s="24">
         <v>13709.77104863717</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="22">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="23">
         <v>0.04</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B17" s="24">
         <v>1070440.6088071163</v>
       </c>
-      <c r="C16" s="23">
+      <c r="C17" s="24">
         <v>-144430.53246462764</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D17" s="25">
         <v>-0.11888547481129214</v>
       </c>
-      <c r="E16" s="23">
+      <c r="E17" s="24">
         <v>70171.4851838362</v>
       </c>
-      <c r="F16" s="23">
+      <c r="F17" s="24">
         <v>13380.507610088953</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="22">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="23">
         <v>0.02</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B18" s="24">
         <v>1045210.9714905105</v>
       </c>
-      <c r="C17" s="23">
+      <c r="C18" s="24">
         <v>-169660.16978123342</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D18" s="25">
         <v>-0.13965281091756843</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E18" s="24">
         <v>48140.26659345992</v>
       </c>
-      <c r="F17" s="23">
+      <c r="F18" s="24">
         <v>13065.137143631382</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="26">
         <v>0</v>
       </c>
-      <c r="B18" s="26">
+      <c r="B19" s="27">
         <v>1021023.8811704587</v>
       </c>
-      <c r="C18" s="26">
+      <c r="C19" s="27">
         <v>-193847.26010128518</v>
       </c>
-      <c r="D18" s="27">
+      <c r="D19" s="28">
         <v>-0.1595619926392878</v>
       </c>
-      <c r="E18" s="26">
+      <c r="E19" s="27">
         <v>27019.428936570246</v>
       </c>
-      <c r="F18" s="26">
+      <c r="F19" s="27">
         <v>12762.798514630735</v>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-    </row>
-    <row r="21" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
+    <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="29" t="s">
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+    </row>
+    <row r="22" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="29"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29" t="s">
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="30" t="s">
         <v>21</v>
-      </c>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-    </row>
-    <row r="23" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="30" t="s">
-        <v>22</v>
       </c>
       <c r="B23" s="30"/>
       <c r="C23" s="30"/>
       <c r="D23" s="30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E23" s="30"/>
       <c r="F23" s="30"/>
     </row>
-    <row r="24" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" s="31"/>
       <c r="C24" s="31"/>
-      <c r="D24" s="32" t="s">
+      <c r="D24" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+    </row>
+    <row r="25" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="E24" s="32"/>
-      <c r="F24" s="32"/>
-    </row>
-    <row r="25" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="30" t="s">
+      <c r="B25" s="32"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30" t="s">
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+    </row>
+    <row r="26" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-    </row>
-    <row r="26" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="32" t="s">
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="32"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32" t="s">
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+    </row>
+    <row r="27" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
-    </row>
-    <row r="27" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="30" t="s">
+      <c r="B27" s="33"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30" t="s">
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+    </row>
+    <row r="28" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-    </row>
-    <row r="28" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="32" t="s">
+      <c r="B28" s="31"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="32"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32" t="s">
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+    </row>
+    <row r="29" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-    </row>
-    <row r="29" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="30" t="s">
+      <c r="B29" s="33"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30" t="s">
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+    </row>
+    <row r="30" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-    </row>
-    <row r="30" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="32" t="s">
+      <c r="B30" s="31"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="B30" s="32"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="32" t="s">
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
+    </row>
+    <row r="31" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32"/>
-    </row>
-    <row r="32" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="33" t="s">
+      <c r="B31" s="33"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="34" t="s">
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+    </row>
+    <row r="33" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="35" t="s">
+      <c r="B33" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="35"/>
-      <c r="C33" s="35" t="s">
+      <c r="C33" s="35"/>
+      <c r="D33" s="35"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="35"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="36" t="s">
         <v>41</v>
-      </c>
-      <c r="D33" s="35"/>
-      <c r="E33" s="35" t="s">
-        <v>42</v>
-      </c>
-      <c r="F33" s="35"/>
-    </row>
-    <row r="34" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="36" t="s">
-        <v>43</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D34" s="36"/>
       <c r="E34" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="F34" s="36"/>
+    </row>
+    <row r="35" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="37"/>
+      <c r="C35" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="F34" s="36"/>
-    </row>
-    <row r="36" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="s">
+      <c r="D35" s="37"/>
+      <c r="E35" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="F35" s="37"/>
+    </row>
+    <row r="37" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="12" t="s">
+      <c r="B37" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="F36" s="12" t="s">
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="13" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="37" t="s">
+      <c r="F37" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="B37" s="38" t="s">
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="C37" s="38"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="39">
+      <c r="B38" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38" s="39"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="40">
         <v>73583.83047722955</v>
       </c>
-      <c r="F37" s="39">
+      <c r="F38" s="40">
         <v>69808.76284417766</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="B38" s="38" t="s">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="C38" s="38"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="39">
+      <c r="B39" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="40">
         <v>194849.14933479228</v>
       </c>
-      <c r="F38" s="39">
+      <c r="F39" s="40">
         <v>184958.52199217537</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="B39" s="38" t="s">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="C39" s="38"/>
-      <c r="D39" s="38"/>
-      <c r="E39" s="39">
+      <c r="B40" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" s="39"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="40">
         <v>338647.7850241546</v>
       </c>
-      <c r="F39" s="39">
+      <c r="F40" s="40">
         <v>321274.1543778802</v>
       </c>
     </row>
-    <row r="41" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="B41" s="40"/>
-      <c r="C41" s="40"/>
-      <c r="D41" s="40" t="s">
+    <row r="42" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="E41" s="40"/>
-      <c r="F41" s="40"/>
-    </row>
-    <row r="42" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="41" t="s">
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B42" s="41"/>
-      <c r="C42" s="41"/>
-      <c r="D42" s="41" t="s">
+      <c r="E42" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E42" s="41"/>
-      <c r="F42" s="41"/>
-    </row>
-    <row r="43" ht="17" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="42" t="s">
+      <c r="F42" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B43" s="42"/>
-      <c r="C43" s="42"/>
-      <c r="D43" s="42" t="s">
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="E43" s="42"/>
-      <c r="F43" s="42"/>
-    </row>
-    <row r="44" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="43" t="s">
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="41">
+        <v>2800</v>
+      </c>
+      <c r="E43" s="41">
+        <v>33600</v>
+      </c>
+      <c r="F43" s="41">
+        <v>16800</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="B44" s="43"/>
-      <c r="C44" s="43"/>
-      <c r="D44" s="43" t="s">
+      <c r="B44" s="42"/>
+      <c r="C44" s="42"/>
+      <c r="D44" s="9">
+        <v>3200</v>
+      </c>
+      <c r="E44" s="9">
+        <v>38400</v>
+      </c>
+      <c r="F44" s="9">
+        <v>19200</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="E44" s="43"/>
-      <c r="F44" s="43"/>
-    </row>
-    <row r="46" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="10" t="s">
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="41">
+        <v>3600</v>
+      </c>
+      <c r="E45" s="41">
+        <v>43200</v>
+      </c>
+      <c r="F45" s="41">
+        <v>21600</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
+      <c r="B46" s="42"/>
+      <c r="C46" s="42"/>
+      <c r="D46" s="9">
+        <v>4000</v>
+      </c>
+      <c r="E46" s="9">
+        <v>48000</v>
+      </c>
+      <c r="F46" s="9">
+        <v>24000</v>
+      </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="44" t="s">
+      <c r="A47" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B47" s="45" t="s">
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="41">
+        <v>4400</v>
+      </c>
+      <c r="E47" s="41">
+        <v>52800</v>
+      </c>
+      <c r="F47" s="41">
+        <v>26400</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C47" s="45"/>
-      <c r="D47" s="45"/>
-      <c r="E47" s="45"/>
-      <c r="F47" s="45"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="44" t="s">
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="41">
+        <v>4800</v>
+      </c>
+      <c r="E48" s="41">
+        <v>57600</v>
+      </c>
+      <c r="F48" s="41">
+        <v>28800</v>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="B48" s="45" t="s">
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="C48" s="45"/>
-      <c r="D48" s="45"/>
-      <c r="E48" s="45"/>
-      <c r="F48" s="45"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="44" t="s">
+      <c r="B51" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="B49" s="45" t="s">
+      <c r="C51" s="44"/>
+      <c r="D51" s="44"/>
+      <c r="E51" s="44"/>
+      <c r="F51" s="44"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="C49" s="45"/>
-      <c r="D49" s="45"/>
-      <c r="E49" s="45"/>
-      <c r="F49" s="45"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="44" t="s">
+      <c r="B52" s="44" t="s">
         <v>71</v>
       </c>
-      <c r="B50" s="45" t="s">
+      <c r="C52" s="44"/>
+      <c r="D52" s="44"/>
+      <c r="E52" s="44"/>
+      <c r="F52" s="44"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="43" t="s">
         <v>72</v>
       </c>
-      <c r="C50" s="45"/>
-      <c r="D50" s="45"/>
-      <c r="E50" s="45"/>
-      <c r="F50" s="45"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="44" t="s">
+      <c r="B53" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="B51" s="45" t="s">
+      <c r="C53" s="44"/>
+      <c r="D53" s="44"/>
+      <c r="E53" s="44"/>
+      <c r="F53" s="44"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="C51" s="45"/>
-      <c r="D51" s="45"/>
-      <c r="E51" s="45"/>
-      <c r="F51" s="45"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="44" t="s">
+      <c r="B54" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="B52" s="45" t="s">
+      <c r="C54" s="44"/>
+      <c r="D54" s="44"/>
+      <c r="E54" s="44"/>
+      <c r="F54" s="44"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="C52" s="45"/>
-      <c r="D52" s="45"/>
-      <c r="E52" s="45"/>
-      <c r="F52" s="45"/>
+      <c r="B55" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="C55" s="44"/>
+      <c r="D55" s="44"/>
+      <c r="E55" s="44"/>
+      <c r="F55" s="44"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="43" t="s">
+        <v>78</v>
+      </c>
+      <c r="B56" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C56" s="44"/>
+      <c r="D56" s="44"/>
+      <c r="E56" s="44"/>
+      <c r="F56" s="44"/>
     </row>
   </sheetData>
-  <mergeCells count="61">
+  <mergeCells count="55">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="D23:F23"/>
     <mergeCell ref="A24:C24"/>
@@ -2270,32 +2283,33 @@
     <mergeCell ref="D29:F29"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="D30:F30"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="B33:F33"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="E34:F34"/>
-    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E35:F35"/>
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B39:D39"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="B40:D40"/>
     <mergeCell ref="A42:C42"/>
-    <mergeCell ref="D42:F42"/>
     <mergeCell ref="A43:C43"/>
-    <mergeCell ref="D43:F43"/>
     <mergeCell ref="A44:C44"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A50:F50"/>
     <mergeCell ref="B51:F51"/>
     <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B54:F54"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B56:F56"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.25" footer="0.25"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="80" fitToWidth="1" fitToHeight="1"/>
@@ -2314,909 +2328,909 @@
     <col min="2" max="5" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
+    <row r="1" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
+      <c r="A2" s="46" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
+      <c r="A4" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="44" t="s">
-        <v>80</v>
-      </c>
-      <c r="B5" s="45" t="s">
-        <v>81</v>
-      </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
+      <c r="A5" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="44" t="s">
-        <v>82</v>
-      </c>
-      <c r="B6" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
+      <c r="A6" s="43" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="44" t="s">
-        <v>84</v>
-      </c>
-      <c r="B7" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
+      <c r="A7" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="44" t="s">
-        <v>87</v>
-      </c>
-      <c r="B9" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
+      <c r="A9" s="43" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="44" t="s">
-        <v>89</v>
-      </c>
-      <c r="B10" s="45" t="s">
+      <c r="A10" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="43" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="43" t="s">
+        <v>100</v>
+      </c>
+      <c r="B14" s="44" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+    </row>
+    <row r="18" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="49">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="50" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="52">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="B21" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" s="48"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="49">
+        <v>22.4568</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="50" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" s="51"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="52">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="B23" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="C23" s="48"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="53">
+        <v>2660</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="B24" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="52">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="C25" s="48"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="54">
+        <v>850524.2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="50" t="s">
+        <v>121</v>
+      </c>
+      <c r="B26" s="51" t="s">
+        <v>122</v>
+      </c>
+      <c r="C26" s="51"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="55">
+        <v>3005.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="47" t="s">
+        <v>123</v>
+      </c>
+      <c r="B27" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="54">
+        <v>23400</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="C28" s="51"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="55">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="47" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="C29" s="48"/>
+      <c r="D29" s="48"/>
+      <c r="E29" s="54">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="B30" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="C30" s="51"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="55">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="47" t="s">
+        <v>130</v>
+      </c>
+      <c r="B31" s="48" t="s">
+        <v>131</v>
+      </c>
+      <c r="C31" s="48"/>
+      <c r="D31" s="48"/>
+      <c r="E31" s="54">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="50" t="s">
+        <v>132</v>
+      </c>
+      <c r="B32" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="C32" s="51"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="55">
+        <v>6582.72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="47" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="48" t="s">
+        <v>134</v>
+      </c>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="54">
+        <v>61200</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="B34" s="51" t="s">
+        <v>136</v>
+      </c>
+      <c r="C34" s="51"/>
+      <c r="D34" s="51"/>
+      <c r="E34" s="55">
+        <v>7895.556</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="56" t="s">
+        <v>137</v>
+      </c>
+      <c r="B35" s="57" t="s">
+        <v>138</v>
+      </c>
+      <c r="C35" s="57"/>
+      <c r="D35" s="57"/>
+      <c r="E35" s="58">
+        <v>974108.276</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="B36" s="51" t="s">
+        <v>140</v>
+      </c>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="55">
+        <v>6058.765243236716</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="47" t="s">
+        <v>141</v>
+      </c>
+      <c r="B37" s="48" t="s">
+        <v>142</v>
+      </c>
+      <c r="C37" s="48"/>
+      <c r="D37" s="48"/>
+      <c r="E37" s="54">
+        <v>31587.931413768118</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="50" t="s">
+        <v>143</v>
+      </c>
+      <c r="B38" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="C38" s="51"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="55">
+        <v>164704.29787439617</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="47" t="s">
+        <v>145</v>
+      </c>
+      <c r="B39" s="48" t="s">
+        <v>146</v>
+      </c>
+      <c r="C39" s="48"/>
+      <c r="D39" s="48"/>
+      <c r="E39" s="54">
+        <v>196292.22928816426</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="50" t="s">
+        <v>147</v>
+      </c>
+      <c r="B40" s="51" t="s">
+        <v>148</v>
+      </c>
+      <c r="C40" s="51"/>
+      <c r="D40" s="51"/>
+      <c r="E40" s="55">
+        <v>38411.870740343</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="56" t="s">
+        <v>149</v>
+      </c>
+      <c r="B41" s="57" t="s">
+        <v>150</v>
+      </c>
+      <c r="C41" s="57"/>
+      <c r="D41" s="57"/>
+      <c r="E41" s="58">
+        <v>1214871.141271744</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="56" t="s">
+        <v>151</v>
+      </c>
+      <c r="B42" s="57" t="s">
+        <v>152</v>
+      </c>
+      <c r="C42" s="57"/>
+      <c r="D42" s="57"/>
+      <c r="E42" s="58">
+        <v>1018578.9119835796</v>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="45" t="s">
+        <v>153</v>
+      </c>
+      <c r="B43" s="45"/>
+      <c r="C43" s="45"/>
+      <c r="D43" s="45"/>
+      <c r="E43" s="45"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="46" t="s">
+        <v>154</v>
+      </c>
+      <c r="B44" s="46"/>
+      <c r="C44" s="46"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="46"/>
+    </row>
+    <row r="46" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="59" t="s">
+        <v>42</v>
+      </c>
+      <c r="B46" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="C46" s="61" t="s">
+        <v>155</v>
+      </c>
+      <c r="D46" s="61"/>
+      <c r="E46" s="62">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="61" t="s">
+        <v>156</v>
+      </c>
+      <c r="B47" s="62">
+        <v>130</v>
+      </c>
+      <c r="C47" s="61" t="s">
+        <v>157</v>
+      </c>
+      <c r="D47" s="61"/>
+      <c r="E47" s="62">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="48" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="61" t="s">
+        <v>158</v>
+      </c>
+      <c r="B48" s="62">
+        <v>45</v>
+      </c>
+      <c r="C48" s="61" t="s">
+        <v>159</v>
+      </c>
+      <c r="D48" s="61"/>
+      <c r="E48" s="62">
         <v>90</v>
       </c>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="B11" s="45" t="s">
+    </row>
+    <row r="49" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="59" t="s">
+        <v>160</v>
+      </c>
+      <c r="B49" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="C49" s="61" t="s">
+        <v>161</v>
+      </c>
+      <c r="D49" s="61"/>
+      <c r="E49" s="62">
+        <v>207.28</v>
+      </c>
+    </row>
+    <row r="50" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="61" t="s">
+        <v>162</v>
+      </c>
+      <c r="B50" s="63" t="s">
+        <v>163</v>
+      </c>
+      <c r="C50" s="61" t="s">
+        <v>164</v>
+      </c>
+      <c r="D50" s="61"/>
+      <c r="E50" s="62">
+        <v>40.14</v>
+      </c>
+    </row>
+    <row r="51" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="61" t="s">
+        <v>165</v>
+      </c>
+      <c r="B51" s="63" t="s">
+        <v>166</v>
+      </c>
+      <c r="C51" s="61" t="s">
+        <v>167</v>
+      </c>
+      <c r="D51" s="61"/>
+      <c r="E51" s="62">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="52" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="61" t="s">
+        <v>168</v>
+      </c>
+      <c r="B52" s="63" t="s">
+        <v>169</v>
+      </c>
+      <c r="C52" s="61" t="s">
+        <v>170</v>
+      </c>
+      <c r="D52" s="61"/>
+      <c r="E52" s="62">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="53" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="59" t="s">
+        <v>171</v>
+      </c>
+      <c r="B53" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="C53" s="61" t="s">
+        <v>172</v>
+      </c>
+      <c r="D53" s="61"/>
+      <c r="E53" s="62">
+        <v>10.95</v>
+      </c>
+    </row>
+    <row r="54" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="61" t="s">
+        <v>173</v>
+      </c>
+      <c r="B54" s="62">
+        <v>0</v>
+      </c>
+      <c r="C54" s="61" t="s">
+        <v>174</v>
+      </c>
+      <c r="D54" s="61"/>
+      <c r="E54" s="62">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="55" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="61" t="s">
+        <v>175</v>
+      </c>
+      <c r="B55" s="62">
+        <v>500</v>
+      </c>
+      <c r="C55" s="61" t="s">
+        <v>176</v>
+      </c>
+      <c r="D55" s="61"/>
+      <c r="E55" s="62">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="56" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="61" t="s">
+        <v>177</v>
+      </c>
+      <c r="B56" s="62">
+        <v>550</v>
+      </c>
+      <c r="C56" s="61" t="s">
+        <v>178</v>
+      </c>
+      <c r="D56" s="61"/>
+      <c r="E56" s="62">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="57" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="61" t="s">
+        <v>179</v>
+      </c>
+      <c r="B57" s="62">
+        <v>600</v>
+      </c>
+      <c r="C57" s="61" t="s">
+        <v>180</v>
+      </c>
+      <c r="D57" s="61"/>
+      <c r="E57" s="62">
+        <v>97.12</v>
+      </c>
+    </row>
+    <row r="58" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="61" t="s">
+        <v>181</v>
+      </c>
+      <c r="B58" s="62">
+        <v>650</v>
+      </c>
+      <c r="C58" s="61" t="s">
+        <v>182</v>
+      </c>
+      <c r="D58" s="61"/>
+      <c r="E58" s="62">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="59" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="61" t="s">
+        <v>183</v>
+      </c>
+      <c r="B59" s="62">
+        <v>700</v>
+      </c>
+      <c r="C59" s="61" t="s">
+        <v>184</v>
+      </c>
+      <c r="D59" s="61"/>
+      <c r="E59" s="62">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="60" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="61" t="s">
+        <v>185</v>
+      </c>
+      <c r="B60" s="62">
+        <v>750</v>
+      </c>
+      <c r="C60" s="61" t="s">
+        <v>186</v>
+      </c>
+      <c r="D60" s="61"/>
+      <c r="E60" s="62">
+        <v>2.98</v>
+      </c>
+    </row>
+    <row r="61" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="61" t="s">
+        <v>187</v>
+      </c>
+      <c r="B61" s="62">
+        <v>800</v>
+      </c>
+      <c r="C61" s="61" t="s">
+        <v>188</v>
+      </c>
+      <c r="D61" s="61"/>
+      <c r="E61" s="62">
+        <v>8.08</v>
+      </c>
+    </row>
+    <row r="62" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="61" t="s">
+        <v>189</v>
+      </c>
+      <c r="B62" s="62">
+        <v>850</v>
+      </c>
+      <c r="C62" s="61" t="s">
+        <v>190</v>
+      </c>
+      <c r="D62" s="61"/>
+      <c r="E62" s="62">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="63" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="59" t="s">
+        <v>191</v>
+      </c>
+      <c r="B63" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="C63" s="61" t="s">
+        <v>192</v>
+      </c>
+      <c r="D63" s="61"/>
+      <c r="E63" s="62">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="64" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="61" t="s">
+        <v>193</v>
+      </c>
+      <c r="B64" s="62">
+        <v>1170</v>
+      </c>
+      <c r="C64" s="61" t="s">
+        <v>194</v>
+      </c>
+      <c r="D64" s="61"/>
+      <c r="E64" s="62">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="65" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B65" s="62">
+        <v>1560</v>
+      </c>
+      <c r="C65" s="61" t="s">
+        <v>196</v>
+      </c>
+      <c r="D65" s="61"/>
+      <c r="E65" s="62">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="66" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="61" t="s">
+        <v>197</v>
+      </c>
+      <c r="B66" s="62">
+        <v>1820</v>
+      </c>
+      <c r="C66" s="61" t="s">
+        <v>198</v>
+      </c>
+      <c r="D66" s="61"/>
+      <c r="E66" s="62">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="67" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="61" t="s">
+        <v>199</v>
+      </c>
+      <c r="B67" s="62">
+        <v>3110</v>
+      </c>
+      <c r="C67" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="D67" s="61"/>
+      <c r="E67" s="62">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="68" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="61" t="s">
+        <v>201</v>
+      </c>
+      <c r="B68" s="62">
+        <v>2340</v>
+      </c>
+      <c r="C68" s="61" t="s">
+        <v>202</v>
+      </c>
+      <c r="D68" s="61"/>
+      <c r="E68" s="62">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="69" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="61" t="s">
+        <v>203</v>
+      </c>
+      <c r="B69" s="62">
+        <v>10</v>
+      </c>
+      <c r="C69" s="61" t="s">
+        <v>204</v>
+      </c>
+      <c r="D69" s="61"/>
+      <c r="E69" s="62">
         <v>92</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="B12" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="44" t="s">
-        <v>95</v>
-      </c>
-      <c r="B13" s="45" t="s">
-        <v>96</v>
-      </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="B14" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="44" t="s">
-        <v>99</v>
-      </c>
-      <c r="B15" s="45" t="s">
-        <v>100</v>
-      </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-    </row>
-    <row r="17" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-    </row>
-    <row r="18" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="47" t="s">
-        <v>102</v>
-      </c>
-      <c r="B18" s="47" t="s">
-        <v>103</v>
-      </c>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="49" t="s">
-        <v>105</v>
-      </c>
-      <c r="B19" s="50" t="s">
-        <v>106</v>
-      </c>
-      <c r="C19" s="50"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="51">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="52" t="s">
-        <v>107</v>
-      </c>
-      <c r="B20" s="53" t="s">
-        <v>108</v>
-      </c>
-      <c r="C20" s="53"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="54">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="49" t="s">
-        <v>109</v>
-      </c>
-      <c r="B21" s="50" t="s">
-        <v>110</v>
-      </c>
-      <c r="C21" s="50"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="51">
-        <v>22.4568</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="52" t="s">
-        <v>111</v>
-      </c>
-      <c r="B22" s="53" t="s">
+    </row>
+    <row r="70" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="61" t="s">
+        <v>205</v>
+      </c>
+      <c r="B70" s="62">
+        <v>20</v>
+      </c>
+      <c r="C70" s="61" t="s">
+        <v>206</v>
+      </c>
+      <c r="D70" s="61"/>
+      <c r="E70" s="62">
         <v>112</v>
       </c>
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="54">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="49" t="s">
-        <v>113</v>
-      </c>
-      <c r="B23" s="50" t="s">
-        <v>114</v>
-      </c>
-      <c r="C23" s="50"/>
-      <c r="D23" s="50"/>
-      <c r="E23" s="55">
-        <v>2660</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="52" t="s">
-        <v>115</v>
-      </c>
-      <c r="B24" s="53" t="s">
-        <v>116</v>
-      </c>
-      <c r="C24" s="53"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="54">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="50" t="s">
-        <v>117</v>
-      </c>
-      <c r="C25" s="50"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="56">
-        <v>850524.2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="52" t="s">
-        <v>118</v>
-      </c>
-      <c r="B26" s="53" t="s">
-        <v>119</v>
-      </c>
-      <c r="C26" s="53"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="57">
-        <v>3005.8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="B27" s="50" t="s">
-        <v>121</v>
-      </c>
-      <c r="C27" s="50"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="56">
-        <v>23400</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="53" t="s">
-        <v>122</v>
-      </c>
-      <c r="C28" s="53"/>
-      <c r="D28" s="53"/>
-      <c r="E28" s="57">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="49" t="s">
-        <v>123</v>
-      </c>
-      <c r="B29" s="50" t="s">
-        <v>124</v>
-      </c>
-      <c r="C29" s="50"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="56">
-        <v>9600</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="52" t="s">
-        <v>125</v>
-      </c>
-      <c r="B30" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="C30" s="53"/>
-      <c r="D30" s="53"/>
-      <c r="E30" s="57">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="49" t="s">
-        <v>127</v>
-      </c>
-      <c r="B31" s="50" t="s">
-        <v>128</v>
-      </c>
-      <c r="C31" s="50"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="56">
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="52" t="s">
-        <v>129</v>
-      </c>
-      <c r="B32" s="53" t="s">
-        <v>130</v>
-      </c>
-      <c r="C32" s="53"/>
-      <c r="D32" s="53"/>
-      <c r="E32" s="57">
-        <v>6582.72</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="49" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="50" t="s">
-        <v>131</v>
-      </c>
-      <c r="C33" s="50"/>
-      <c r="D33" s="50"/>
-      <c r="E33" s="56">
-        <v>61200</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="52" t="s">
-        <v>132</v>
-      </c>
-      <c r="B34" s="53" t="s">
-        <v>133</v>
-      </c>
-      <c r="C34" s="53"/>
-      <c r="D34" s="53"/>
-      <c r="E34" s="57">
-        <v>7895.556</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="58" t="s">
-        <v>134</v>
-      </c>
-      <c r="B35" s="59" t="s">
-        <v>135</v>
-      </c>
-      <c r="C35" s="59"/>
-      <c r="D35" s="59"/>
-      <c r="E35" s="60">
-        <v>974108.276</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="52" t="s">
-        <v>136</v>
-      </c>
-      <c r="B36" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="C36" s="53"/>
-      <c r="D36" s="53"/>
-      <c r="E36" s="57">
-        <v>6058.765243236716</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="49" t="s">
-        <v>138</v>
-      </c>
-      <c r="B37" s="50" t="s">
-        <v>139</v>
-      </c>
-      <c r="C37" s="50"/>
-      <c r="D37" s="50"/>
-      <c r="E37" s="56">
-        <v>31587.931413768118</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="52" t="s">
-        <v>140</v>
-      </c>
-      <c r="B38" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="C38" s="53"/>
-      <c r="D38" s="53"/>
-      <c r="E38" s="57">
-        <v>164704.29787439617</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="49" t="s">
-        <v>142</v>
-      </c>
-      <c r="B39" s="50" t="s">
-        <v>143</v>
-      </c>
-      <c r="C39" s="50"/>
-      <c r="D39" s="50"/>
-      <c r="E39" s="56">
-        <v>196292.22928816426</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="52" t="s">
-        <v>144</v>
-      </c>
-      <c r="B40" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="C40" s="53"/>
-      <c r="D40" s="53"/>
-      <c r="E40" s="57">
-        <v>38411.870740343</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="B41" s="59" t="s">
-        <v>147</v>
-      </c>
-      <c r="C41" s="59"/>
-      <c r="D41" s="59"/>
-      <c r="E41" s="60">
-        <v>1214871.141271744</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="58" t="s">
-        <v>148</v>
-      </c>
-      <c r="B42" s="59" t="s">
-        <v>149</v>
-      </c>
-      <c r="C42" s="59"/>
-      <c r="D42" s="59"/>
-      <c r="E42" s="60">
-        <v>1018578.9119835796</v>
-      </c>
-    </row>
-    <row r="43" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="46" t="s">
-        <v>150</v>
-      </c>
-      <c r="B43" s="46"/>
-      <c r="C43" s="46"/>
-      <c r="D43" s="46"/>
-      <c r="E43" s="46"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-    </row>
-    <row r="46" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="61" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="62" t="s">
-        <v>55</v>
-      </c>
-      <c r="C46" s="63" t="s">
-        <v>152</v>
-      </c>
-      <c r="D46" s="63"/>
-      <c r="E46" s="64">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="63" t="s">
-        <v>153</v>
-      </c>
-      <c r="B47" s="64">
-        <v>130</v>
-      </c>
-      <c r="C47" s="63" t="s">
-        <v>154</v>
-      </c>
-      <c r="D47" s="63"/>
-      <c r="E47" s="64">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="48" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="63" t="s">
-        <v>155</v>
-      </c>
-      <c r="B48" s="64">
+    </row>
+    <row r="71" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="59" t="s">
+        <v>207</v>
+      </c>
+      <c r="B71" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="C71" s="61" t="s">
+        <v>208</v>
+      </c>
+      <c r="D71" s="61"/>
+      <c r="E71" s="62">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="72" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="61" t="s">
+        <v>209</v>
+      </c>
+      <c r="B72" s="62">
         <v>45</v>
       </c>
-      <c r="C48" s="63" t="s">
-        <v>156</v>
-      </c>
-      <c r="D48" s="63"/>
-      <c r="E48" s="64">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="49" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="61" t="s">
-        <v>157</v>
-      </c>
-      <c r="B49" s="62" t="s">
-        <v>55</v>
-      </c>
-      <c r="C49" s="63" t="s">
-        <v>158</v>
-      </c>
-      <c r="D49" s="63"/>
-      <c r="E49" s="64">
-        <v>207.28</v>
-      </c>
-    </row>
-    <row r="50" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="63" t="s">
-        <v>159</v>
-      </c>
-      <c r="B50" s="65" t="s">
-        <v>160</v>
-      </c>
-      <c r="C50" s="63" t="s">
-        <v>161</v>
-      </c>
-      <c r="D50" s="63"/>
-      <c r="E50" s="64">
-        <v>40.14</v>
-      </c>
-    </row>
-    <row r="51" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="63" t="s">
-        <v>162</v>
-      </c>
-      <c r="B51" s="65" t="s">
-        <v>163</v>
-      </c>
-      <c r="C51" s="63" t="s">
-        <v>164</v>
-      </c>
-      <c r="D51" s="63"/>
-      <c r="E51" s="64">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="52" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="63" t="s">
-        <v>165</v>
-      </c>
-      <c r="B52" s="65" t="s">
-        <v>166</v>
-      </c>
-      <c r="C52" s="63" t="s">
-        <v>167</v>
-      </c>
-      <c r="D52" s="63"/>
-      <c r="E52" s="64">
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="53" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="61" t="s">
-        <v>168</v>
-      </c>
-      <c r="B53" s="62" t="s">
-        <v>55</v>
-      </c>
-      <c r="C53" s="63" t="s">
-        <v>169</v>
-      </c>
-      <c r="D53" s="63"/>
-      <c r="E53" s="64">
-        <v>10.95</v>
-      </c>
-    </row>
-    <row r="54" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="63" t="s">
-        <v>170</v>
-      </c>
-      <c r="B54" s="64">
-        <v>0</v>
-      </c>
-      <c r="C54" s="63" t="s">
-        <v>171</v>
-      </c>
-      <c r="D54" s="63"/>
-      <c r="E54" s="64">
-        <v>3.81</v>
-      </c>
-    </row>
-    <row r="55" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="63" t="s">
-        <v>172</v>
-      </c>
-      <c r="B55" s="64">
-        <v>500</v>
-      </c>
-      <c r="C55" s="63" t="s">
-        <v>173</v>
-      </c>
-      <c r="D55" s="63"/>
-      <c r="E55" s="64">
-        <v>2.84</v>
-      </c>
-    </row>
-    <row r="56" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="63" t="s">
-        <v>174</v>
-      </c>
-      <c r="B56" s="64">
-        <v>550</v>
-      </c>
-      <c r="C56" s="63" t="s">
-        <v>175</v>
-      </c>
-      <c r="D56" s="63"/>
-      <c r="E56" s="64">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="57" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="63" t="s">
-        <v>176</v>
-      </c>
-      <c r="B57" s="64">
-        <v>600</v>
-      </c>
-      <c r="C57" s="63" t="s">
-        <v>177</v>
-      </c>
-      <c r="D57" s="63"/>
-      <c r="E57" s="64">
-        <v>97.12</v>
-      </c>
-    </row>
-    <row r="58" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="63" t="s">
-        <v>178</v>
-      </c>
-      <c r="B58" s="64">
-        <v>650</v>
-      </c>
-      <c r="C58" s="63" t="s">
-        <v>179</v>
-      </c>
-      <c r="D58" s="63"/>
-      <c r="E58" s="64">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="59" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="63" t="s">
-        <v>180</v>
-      </c>
-      <c r="B59" s="64">
-        <v>700</v>
-      </c>
-      <c r="C59" s="63" t="s">
-        <v>181</v>
-      </c>
-      <c r="D59" s="63"/>
-      <c r="E59" s="64">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="60" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="63" t="s">
-        <v>182</v>
-      </c>
-      <c r="B60" s="64">
-        <v>750</v>
-      </c>
-      <c r="C60" s="63" t="s">
-        <v>183</v>
-      </c>
-      <c r="D60" s="63"/>
-      <c r="E60" s="64">
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="61" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="63" t="s">
-        <v>184</v>
-      </c>
-      <c r="B61" s="64">
-        <v>800</v>
-      </c>
-      <c r="C61" s="63" t="s">
-        <v>185</v>
-      </c>
-      <c r="D61" s="63"/>
-      <c r="E61" s="64">
-        <v>8.08</v>
-      </c>
-    </row>
-    <row r="62" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="63" t="s">
-        <v>186</v>
-      </c>
-      <c r="B62" s="64">
-        <v>850</v>
-      </c>
-      <c r="C62" s="63" t="s">
-        <v>187</v>
-      </c>
-      <c r="D62" s="63"/>
-      <c r="E62" s="64">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="63" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="61" t="s">
-        <v>188</v>
-      </c>
-      <c r="B63" s="62" t="s">
-        <v>55</v>
-      </c>
-      <c r="C63" s="63" t="s">
-        <v>189</v>
-      </c>
-      <c r="D63" s="63"/>
-      <c r="E63" s="64">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="64" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="63" t="s">
-        <v>190</v>
-      </c>
-      <c r="B64" s="64">
-        <v>1170</v>
-      </c>
-      <c r="C64" s="63" t="s">
-        <v>191</v>
-      </c>
-      <c r="D64" s="63"/>
-      <c r="E64" s="64">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="65" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="63" t="s">
-        <v>192</v>
-      </c>
-      <c r="B65" s="64">
-        <v>1560</v>
-      </c>
-      <c r="C65" s="63" t="s">
-        <v>193</v>
-      </c>
-      <c r="D65" s="63"/>
-      <c r="E65" s="64">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="66" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="63" t="s">
-        <v>194</v>
-      </c>
-      <c r="B66" s="64">
-        <v>1820</v>
-      </c>
-      <c r="C66" s="63" t="s">
-        <v>195</v>
-      </c>
-      <c r="D66" s="63"/>
-      <c r="E66" s="64">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="67" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="63" t="s">
-        <v>196</v>
-      </c>
-      <c r="B67" s="64">
-        <v>3110</v>
-      </c>
-      <c r="C67" s="63" t="s">
-        <v>197</v>
-      </c>
-      <c r="D67" s="63"/>
-      <c r="E67" s="64">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="68" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="63" t="s">
-        <v>198</v>
-      </c>
-      <c r="B68" s="64">
-        <v>2340</v>
-      </c>
-      <c r="C68" s="63" t="s">
-        <v>199</v>
-      </c>
-      <c r="D68" s="63"/>
-      <c r="E68" s="64">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="69" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="63" t="s">
-        <v>200</v>
-      </c>
-      <c r="B69" s="64">
-        <v>10</v>
-      </c>
-      <c r="C69" s="63" t="s">
-        <v>201</v>
-      </c>
-      <c r="D69" s="63"/>
-      <c r="E69" s="64">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="70" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="63" t="s">
-        <v>202</v>
-      </c>
-      <c r="B70" s="64">
-        <v>20</v>
-      </c>
-      <c r="C70" s="63" t="s">
-        <v>203</v>
-      </c>
-      <c r="D70" s="63"/>
-      <c r="E70" s="64">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="71" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="61" t="s">
-        <v>204</v>
-      </c>
-      <c r="B71" s="62" t="s">
-        <v>55</v>
-      </c>
-      <c r="C71" s="63" t="s">
-        <v>205</v>
-      </c>
-      <c r="D71" s="63"/>
-      <c r="E71" s="64">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="72" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="63" t="s">
-        <v>206</v>
-      </c>
-      <c r="B72" s="64">
-        <v>45</v>
-      </c>
       <c r="C72" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D72"/>
       <c r="E72" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
@@ -168,10 +168,10 @@
     <t>ul. Polna 5, Katowice</t>
   </si>
   <si>
-    <t>21.10.2026</t>
-  </si>
-  <si>
-    <t>Wygenerowano 27.10.2026, 14:33:07 · ceny netto w zł · szablon NK38</t>
+    <t>21.10.2026, 14:43</t>
+  </si>
+  <si>
+    <t>Wygenerowano 27.10.2026, 14:43:39 · ceny netto w zł · szablon NK38</t>
   </si>
   <si>
     <t>Cena</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
@@ -168,10 +168,10 @@
     <t>ul. Polna 5, Katowice</t>
   </si>
   <si>
-    <t>21.10.2026, 14:43</t>
-  </si>
-  <si>
-    <t>Wygenerowano 27.10.2026, 14:43:39 · ceny netto w zł · szablon NK38</t>
+    <t>21.10.2026, 17:30</t>
+  </si>
+  <si>
+    <t>Wygenerowano 27.10.2026, 17:30:54 · ceny netto w zł · szablon NK38</t>
   </si>
   <si>
     <t>Cena</t>
@@ -950,7 +950,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1000,6 +1000,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FFD3D9DD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1180,13 +1189,13 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
@@ -168,10 +168,10 @@
     <t>ul. Polna 5, Katowice</t>
   </si>
   <si>
-    <t>21.10.2026, 17:30</t>
-  </si>
-  <si>
-    <t>Wygenerowano 27.10.2026, 17:30:54 · ceny netto w zł · szablon NK38</t>
+    <t>21.10.2026, 10:10</t>
+  </si>
+  <si>
+    <t>Wygenerowano 30.10.2026, 10:10:16 · ceny netto w zł · szablon NK38</t>
   </si>
   <si>
     <t>Cena</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
@@ -4,158 +4,12 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Podsumowanie" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Obliczenia i cennik" state="visible" r:id="rId5"/>
+    <sheet sheetId="1" name="Kalkulacja" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="E46" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B47" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E47" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B48" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E48" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E49" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E50" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E51" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E52" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E53" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B54" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E54" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B55" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E55" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B56" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E56" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B57" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E57" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B58" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E58" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B59" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E59" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B60" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E60" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B61" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E61" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B62" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E62" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E63" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B64" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E64" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B65" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E65" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B66" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E66" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B67" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E67" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B68" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E68" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B69" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E69" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B70" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E70" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E71" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B72" authorId="0">
-      <text/>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="210">
   <si>
@@ -168,10 +22,10 @@
     <t>ul. Polna 5, Katowice</t>
   </si>
   <si>
-    <t>21.10.2026, 10:10</t>
-  </si>
-  <si>
-    <t>Wygenerowano 30.10.2026, 10:10:16 · ceny netto w zł · szablon NK38</t>
+    <t>21.10.2026, 10:27</t>
+  </si>
+  <si>
+    <t>Wygenerowano 30.10.2026, 10:27:59 · ceny netto w zł · szablon NK38</t>
   </si>
   <si>
     <t>Cena</t>
@@ -360,6 +214,225 @@
     <t>60 zł / MP / mies.</t>
   </si>
   <si>
+    <t>Koszty · 2000 kg · 14%</t>
+  </si>
+  <si>
+    <t>Skąd się biorą kwoty (wariant 2000 kg) · ceny netto w zł</t>
+  </si>
+  <si>
+    <t>Materiały i urządzenia</t>
+  </si>
+  <si>
+    <t>Cena platformy D / S / N.P.</t>
+  </si>
+  <si>
+    <t>32 500 zł / 19 825 zł / 27 625 zł</t>
+  </si>
+  <si>
+    <t>Platformy S z dopłatami</t>
+  </si>
+  <si>
+    <t>0 zł</t>
+  </si>
+  <si>
+    <t>Platformy D z dopłatami</t>
+  </si>
+  <si>
+    <t>665 651 zł</t>
+  </si>
+  <si>
+    <t>Platformy N.P.</t>
+  </si>
+  <si>
+    <t>Siłowniki (pary): std / 2000 / 2250</t>
+  </si>
+  <si>
+    <t>0 / 20 / 0</t>
+  </si>
+  <si>
+    <t>Hydraulika</t>
+  </si>
+  <si>
+    <t>92 884 zł</t>
+  </si>
+  <si>
+    <t>Barierki i maskownice</t>
+  </si>
+  <si>
+    <t>12 000 zł</t>
+  </si>
+  <si>
+    <t>Elektryka</t>
+  </si>
+  <si>
+    <t>11 440 zł</t>
+  </si>
+  <si>
+    <t>Mechanika zakupowa i pozostałe</t>
+  </si>
+  <si>
+    <t>68 550 zł</t>
+  </si>
+  <si>
+    <t>Suma Q=2000</t>
+  </si>
+  <si>
+    <t>850 524 zł</t>
+  </si>
+  <si>
+    <t>Suma Q=2500 (+7%)</t>
+  </si>
+  <si>
+    <t>910 061 zł</t>
+  </si>
+  <si>
+    <t>Montaż, narzuty i cena</t>
+  </si>
+  <si>
+    <t>Pozycja</t>
+  </si>
+  <si>
+    <t>Skąd ta kwota</t>
+  </si>
+  <si>
+    <t>Kwota</t>
+  </si>
+  <si>
+    <t>Osobodni montażu</t>
+  </si>
+  <si>
+    <t>z cennika osobodni na urządzenie + utrudnienia</t>
+  </si>
+  <si>
+    <t>Tygodnie / dni montażu</t>
+  </si>
+  <si>
+    <t>tygodniowe wyjazdy ekipy</t>
+  </si>
+  <si>
+    <t>Osobodni podróży i rozładunku</t>
+  </si>
+  <si>
+    <t>pomiary, odbiory, rozładunek i dojazdy ekipy</t>
+  </si>
+  <si>
+    <t>Dni pracy ekipy</t>
+  </si>
+  <si>
+    <t>(osd montażu + podróży) ÷ 4 os.</t>
+  </si>
+  <si>
+    <t>Kilometry auta</t>
+  </si>
+  <si>
+    <t>dojazdy na montaż, pomiary i odbiory w obie strony</t>
+  </si>
+  <si>
+    <t>Noclegi (osobonoce)</t>
+  </si>
+  <si>
+    <t>(dni pracy + 1) × 4 os.</t>
+  </si>
+  <si>
+    <t>platformy, siłowniki, hydraulika, elektryka (patrz wyżej)</t>
+  </si>
+  <si>
+    <t>Paliwo</t>
+  </si>
+  <si>
+    <t>2660 km × 113 zł/100 km (12 l × 9,4 zł)</t>
+  </si>
+  <si>
+    <t>Hotel</t>
+  </si>
+  <si>
+    <t>180 noclegów × 130 zł/doba</t>
+  </si>
+  <si>
+    <t>3 TIR × 2500 zł</t>
+  </si>
+  <si>
+    <t>Spider Crane</t>
+  </si>
+  <si>
+    <t>4 dni × 2400 zł/dzień</t>
+  </si>
+  <si>
+    <t>Rozładunek, sprzęt</t>
+  </si>
+  <si>
+    <t>2000 zł jednorazowo</t>
+  </si>
+  <si>
+    <t>Rozładunek, ludzie</t>
+  </si>
+  <si>
+    <t>1,5 dni × 4 os. × 400 zł</t>
+  </si>
+  <si>
+    <t>Dojazdy, ludzie</t>
+  </si>
+  <si>
+    <t>16,46 osd podróży × 400 zł</t>
+  </si>
+  <si>
+    <t>153 osd × 400 zł (średnia stawka)</t>
+  </si>
+  <si>
+    <t>Diety</t>
+  </si>
+  <si>
+    <t>175,46 osd × 45 zł</t>
+  </si>
+  <si>
+    <t>Suma przed narzutami</t>
+  </si>
+  <si>
+    <t>suma kosztów powyżej</t>
+  </si>
+  <si>
+    <t>KOB</t>
+  </si>
+  <si>
+    <t>0,515% ceny przed podatkiem (1 176 459 zł)</t>
+  </si>
+  <si>
+    <t>GDW</t>
+  </si>
+  <si>
+    <t>2,685% ceny przed podatkiem</t>
+  </si>
+  <si>
+    <t>Zysk 14%</t>
+  </si>
+  <si>
+    <t>14% ceny przed podatkiem</t>
+  </si>
+  <si>
+    <t>Zysk z narzutem (zysk + GDW)</t>
+  </si>
+  <si>
+    <t>zysk 14% + GDW 2,685%</t>
+  </si>
+  <si>
+    <t>Podatek</t>
+  </si>
+  <si>
+    <t>14% od robocizny (78 078 zł) i zysku z narzutem</t>
+  </si>
+  <si>
+    <t>Cena kontraktu, zysk 14%</t>
+  </si>
+  <si>
+    <t>suma ÷ (1 − KOB − GDW − zysk) + podatek</t>
+  </si>
+  <si>
+    <t>Koszt rzeczywisty</t>
+  </si>
+  <si>
+    <t>cena − zysk z narzutem</t>
+  </si>
+  <si>
     <t>Pozostałe dane wejściowe</t>
   </si>
   <si>
@@ -397,225 +470,6 @@
   </si>
   <si>
     <t>4.325</t>
-  </si>
-  <si>
-    <t>Koszty · 2000 kg · 14%</t>
-  </si>
-  <si>
-    <t>Strona 1: obliczenia · strona 2: cennik szablonu NK38</t>
-  </si>
-  <si>
-    <t>Materiały i urządzenia</t>
-  </si>
-  <si>
-    <t>Cena platformy D / S / N.P.</t>
-  </si>
-  <si>
-    <t>32 500 zł / 19 825 zł / 27 625 zł</t>
-  </si>
-  <si>
-    <t>Platformy S z dopłatami</t>
-  </si>
-  <si>
-    <t>0 zł</t>
-  </si>
-  <si>
-    <t>Platformy D z dopłatami</t>
-  </si>
-  <si>
-    <t>665 651 zł</t>
-  </si>
-  <si>
-    <t>Platformy N.P.</t>
-  </si>
-  <si>
-    <t>Siłowniki (pary): std / 2000 / 2250</t>
-  </si>
-  <si>
-    <t>0 / 20 / 0</t>
-  </si>
-  <si>
-    <t>Hydraulika</t>
-  </si>
-  <si>
-    <t>92 884 zł</t>
-  </si>
-  <si>
-    <t>Barierki i maskownice</t>
-  </si>
-  <si>
-    <t>12 000 zł</t>
-  </si>
-  <si>
-    <t>Elektryka</t>
-  </si>
-  <si>
-    <t>11 440 zł</t>
-  </si>
-  <si>
-    <t>Mechanika zakupowa i pozostałe</t>
-  </si>
-  <si>
-    <t>68 550 zł</t>
-  </si>
-  <si>
-    <t>Suma Q=2000</t>
-  </si>
-  <si>
-    <t>850 524 zł</t>
-  </si>
-  <si>
-    <t>Suma Q=2500 (+7%)</t>
-  </si>
-  <si>
-    <t>910 061 zł</t>
-  </si>
-  <si>
-    <t>Montaż, narzuty i cena</t>
-  </si>
-  <si>
-    <t>Pozycja</t>
-  </si>
-  <si>
-    <t>Skąd ta kwota</t>
-  </si>
-  <si>
-    <t>Kwota</t>
-  </si>
-  <si>
-    <t>Osobodni montażu</t>
-  </si>
-  <si>
-    <t>z cennika osobodni na urządzenie + utrudnienia</t>
-  </si>
-  <si>
-    <t>Tygodnie / dni montażu</t>
-  </si>
-  <si>
-    <t>tygodniowe wyjazdy ekipy</t>
-  </si>
-  <si>
-    <t>Osobodni podróży i rozładunku</t>
-  </si>
-  <si>
-    <t>pomiary, odbiory, rozładunek i dojazdy ekipy</t>
-  </si>
-  <si>
-    <t>Dni pracy ekipy</t>
-  </si>
-  <si>
-    <t>(osd montażu + podróży) ÷ 4 os.</t>
-  </si>
-  <si>
-    <t>Kilometry auta</t>
-  </si>
-  <si>
-    <t>dojazdy na montaż, pomiary i odbiory w obie strony</t>
-  </si>
-  <si>
-    <t>Noclegi (osobonoce)</t>
-  </si>
-  <si>
-    <t>(dni pracy + 1) × 4 os.</t>
-  </si>
-  <si>
-    <t>platformy, siłowniki, hydraulika, elektryka (patrz wyżej)</t>
-  </si>
-  <si>
-    <t>Paliwo</t>
-  </si>
-  <si>
-    <t>2660 km × 113 zł/100 km (12 l × 9,4 zł)</t>
-  </si>
-  <si>
-    <t>Hotel</t>
-  </si>
-  <si>
-    <t>180 noclegów × 130 zł/doba</t>
-  </si>
-  <si>
-    <t>3 TIR × 2500 zł</t>
-  </si>
-  <si>
-    <t>Spider Crane</t>
-  </si>
-  <si>
-    <t>4 dni × 2400 zł/dzień</t>
-  </si>
-  <si>
-    <t>Rozładunek, sprzęt</t>
-  </si>
-  <si>
-    <t>2000 zł jednorazowo</t>
-  </si>
-  <si>
-    <t>Rozładunek, ludzie</t>
-  </si>
-  <si>
-    <t>1,5 dni × 4 os. × 400 zł</t>
-  </si>
-  <si>
-    <t>Dojazdy, ludzie</t>
-  </si>
-  <si>
-    <t>16,46 osd podróży × 400 zł</t>
-  </si>
-  <si>
-    <t>153 osd × 400 zł (średnia stawka)</t>
-  </si>
-  <si>
-    <t>Diety</t>
-  </si>
-  <si>
-    <t>175,46 osd × 45 zł</t>
-  </si>
-  <si>
-    <t>Suma przed narzutami</t>
-  </si>
-  <si>
-    <t>suma kosztów powyżej</t>
-  </si>
-  <si>
-    <t>KOB</t>
-  </si>
-  <si>
-    <t>0,515% ceny przed podatkiem (1 176 459 zł)</t>
-  </si>
-  <si>
-    <t>GDW</t>
-  </si>
-  <si>
-    <t>2,685% ceny przed podatkiem</t>
-  </si>
-  <si>
-    <t>Zysk 14%</t>
-  </si>
-  <si>
-    <t>14% ceny przed podatkiem</t>
-  </si>
-  <si>
-    <t>Zysk z narzutem (zysk + GDW)</t>
-  </si>
-  <si>
-    <t>zysk 14% + GDW 2,685%</t>
-  </si>
-  <si>
-    <t>Podatek</t>
-  </si>
-  <si>
-    <t>14% od robocizny (78 078 zł) i zysku z narzutem</t>
-  </si>
-  <si>
-    <t>Cena kontraktu, zysk 14%</t>
-  </si>
-  <si>
-    <t>suma ÷ (1 − KOB − GDW − zysk) + podatek</t>
-  </si>
-  <si>
-    <t>Koszt rzeczywisty</t>
-  </si>
-  <si>
-    <t>cena − zysk z narzutem</t>
   </si>
   <si>
     <t>Cennik szablonu NK38</t>
@@ -1013,7 +867,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
@@ -1139,17 +993,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
@@ -1190,10 +1044,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment indent="1"/>
+      <alignment indent="3"/>
     </xf>
     <xf numFmtId="171" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1537,7 +1394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F130"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2180,90 +2037,1064 @@
         <v>28800</v>
       </c>
     </row>
-    <row r="50" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="11" t="s">
+    <row r="50" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="B50" s="11"/>
-      <c r="C50" s="11"/>
-      <c r="D50" s="11"/>
-      <c r="E50" s="11"/>
-      <c r="F50" s="11"/>
+      <c r="B50" s="43"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="43"/>
+      <c r="F50" s="43"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="43" t="s">
+      <c r="A51" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="B51" s="44" t="s">
-        <v>69</v>
-      </c>
+      <c r="B51" s="44"/>
       <c r="C51" s="44"/>
       <c r="D51" s="44"/>
       <c r="E51" s="44"/>
       <c r="F51" s="44"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="43" t="s">
+    <row r="53" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B53" s="11"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="B52" s="44" t="s">
+      <c r="B54" s="45"/>
+      <c r="C54" s="46" t="s">
         <v>71</v>
       </c>
-      <c r="C52" s="44"/>
-      <c r="D52" s="44"/>
-      <c r="E52" s="44"/>
-      <c r="F52" s="44"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="43" t="s">
+      <c r="D54" s="46"/>
+      <c r="E54" s="46"/>
+      <c r="F54" s="46"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="B53" s="44" t="s">
+      <c r="B55" s="45"/>
+      <c r="C55" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="C53" s="44"/>
-      <c r="D53" s="44"/>
-      <c r="E53" s="44"/>
-      <c r="F53" s="44"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="43" t="s">
+      <c r="D55" s="46"/>
+      <c r="E55" s="46"/>
+      <c r="F55" s="46"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="45" t="s">
         <v>74</v>
       </c>
-      <c r="B54" s="44" t="s">
+      <c r="B56" s="45"/>
+      <c r="C56" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="C54" s="44"/>
-      <c r="D54" s="44"/>
-      <c r="E54" s="44"/>
-      <c r="F54" s="44"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="43" t="s">
+      <c r="D56" s="46"/>
+      <c r="E56" s="46"/>
+      <c r="F56" s="46"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="45" t="s">
         <v>76</v>
       </c>
-      <c r="B55" s="44" t="s">
+      <c r="B57" s="45"/>
+      <c r="C57" s="46" t="s">
+        <v>73</v>
+      </c>
+      <c r="D57" s="46"/>
+      <c r="E57" s="46"/>
+      <c r="F57" s="46"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="45" t="s">
         <v>77</v>
       </c>
-      <c r="C55" s="44"/>
-      <c r="D55" s="44"/>
-      <c r="E55" s="44"/>
-      <c r="F55" s="44"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="43" t="s">
+      <c r="B58" s="45"/>
+      <c r="C58" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="B56" s="44" t="s">
+      <c r="D58" s="46"/>
+      <c r="E58" s="46"/>
+      <c r="F58" s="46"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="45" t="s">
         <v>79</v>
       </c>
-      <c r="C56" s="44"/>
-      <c r="D56" s="44"/>
-      <c r="E56" s="44"/>
-      <c r="F56" s="44"/>
+      <c r="B59" s="45"/>
+      <c r="C59" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="D59" s="46"/>
+      <c r="E59" s="46"/>
+      <c r="F59" s="46"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="B60" s="45"/>
+      <c r="C60" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="D60" s="46"/>
+      <c r="E60" s="46"/>
+      <c r="F60" s="46"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="B61" s="45"/>
+      <c r="C61" s="46" t="s">
+        <v>84</v>
+      </c>
+      <c r="D61" s="46"/>
+      <c r="E61" s="46"/>
+      <c r="F61" s="46"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="45" t="s">
+        <v>85</v>
+      </c>
+      <c r="B62" s="45"/>
+      <c r="C62" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="D62" s="46"/>
+      <c r="E62" s="46"/>
+      <c r="F62" s="46"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="B63" s="45"/>
+      <c r="C63" s="46" t="s">
+        <v>88</v>
+      </c>
+      <c r="D63" s="46"/>
+      <c r="E63" s="46"/>
+      <c r="F63" s="46"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="45" t="s">
+        <v>89</v>
+      </c>
+      <c r="B64" s="45"/>
+      <c r="C64" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="D64" s="46"/>
+      <c r="E64" s="46"/>
+      <c r="F64" s="46"/>
+    </row>
+    <row r="66" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B66" s="11"/>
+      <c r="C66" s="11"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="11"/>
+    </row>
+    <row r="67" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B67" s="6"/>
+      <c r="C67" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="47" t="s">
+        <v>95</v>
+      </c>
+      <c r="B68" s="47"/>
+      <c r="C68" s="48" t="s">
+        <v>96</v>
+      </c>
+      <c r="D68" s="48"/>
+      <c r="E68" s="48"/>
+      <c r="F68" s="49">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B69" s="50"/>
+      <c r="C69" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="D69" s="51"/>
+      <c r="E69" s="51"/>
+      <c r="F69" s="52">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="B70" s="47"/>
+      <c r="C70" s="48" t="s">
+        <v>100</v>
+      </c>
+      <c r="D70" s="48"/>
+      <c r="E70" s="48"/>
+      <c r="F70" s="49">
+        <v>22.4568</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="B71" s="50"/>
+      <c r="C71" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="D71" s="51"/>
+      <c r="E71" s="51"/>
+      <c r="F71" s="52">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="47" t="s">
+        <v>103</v>
+      </c>
+      <c r="B72" s="47"/>
+      <c r="C72" s="48" t="s">
+        <v>104</v>
+      </c>
+      <c r="D72" s="48"/>
+      <c r="E72" s="48"/>
+      <c r="F72" s="53">
+        <v>2660</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="B73" s="50"/>
+      <c r="C73" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="D73" s="51"/>
+      <c r="E73" s="51"/>
+      <c r="F73" s="52">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="B74" s="47"/>
+      <c r="C74" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="D74" s="48"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="54">
+        <v>850524.2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="B75" s="50"/>
+      <c r="C75" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="D75" s="51"/>
+      <c r="E75" s="51"/>
+      <c r="F75" s="55">
+        <v>3005.8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="47" t="s">
+        <v>110</v>
+      </c>
+      <c r="B76" s="47"/>
+      <c r="C76" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="D76" s="48"/>
+      <c r="E76" s="48"/>
+      <c r="F76" s="54">
+        <v>23400</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="B77" s="50"/>
+      <c r="C77" s="51" t="s">
+        <v>112</v>
+      </c>
+      <c r="D77" s="51"/>
+      <c r="E77" s="51"/>
+      <c r="F77" s="55">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="B78" s="47"/>
+      <c r="C78" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="D78" s="48"/>
+      <c r="E78" s="48"/>
+      <c r="F78" s="54">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="B79" s="50"/>
+      <c r="C79" s="51" t="s">
+        <v>116</v>
+      </c>
+      <c r="D79" s="51"/>
+      <c r="E79" s="51"/>
+      <c r="F79" s="55">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="B80" s="47"/>
+      <c r="C80" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="D80" s="48"/>
+      <c r="E80" s="48"/>
+      <c r="F80" s="54">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="50" t="s">
+        <v>119</v>
+      </c>
+      <c r="B81" s="50"/>
+      <c r="C81" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="D81" s="51"/>
+      <c r="E81" s="51"/>
+      <c r="F81" s="55">
+        <v>6582.72</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="47" t="s">
+        <v>42</v>
+      </c>
+      <c r="B82" s="47"/>
+      <c r="C82" s="48" t="s">
+        <v>121</v>
+      </c>
+      <c r="D82" s="48"/>
+      <c r="E82" s="48"/>
+      <c r="F82" s="54">
+        <v>61200</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="B83" s="50"/>
+      <c r="C83" s="51" t="s">
+        <v>123</v>
+      </c>
+      <c r="D83" s="51"/>
+      <c r="E83" s="51"/>
+      <c r="F83" s="55">
+        <v>7895.556</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="56" t="s">
+        <v>124</v>
+      </c>
+      <c r="B84" s="56"/>
+      <c r="C84" s="57" t="s">
+        <v>125</v>
+      </c>
+      <c r="D84" s="57"/>
+      <c r="E84" s="57"/>
+      <c r="F84" s="58">
+        <v>974108.276</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="50" t="s">
+        <v>126</v>
+      </c>
+      <c r="B85" s="50"/>
+      <c r="C85" s="51" t="s">
+        <v>127</v>
+      </c>
+      <c r="D85" s="51"/>
+      <c r="E85" s="51"/>
+      <c r="F85" s="55">
+        <v>6058.765243236716</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="47" t="s">
+        <v>128</v>
+      </c>
+      <c r="B86" s="47"/>
+      <c r="C86" s="48" t="s">
+        <v>129</v>
+      </c>
+      <c r="D86" s="48"/>
+      <c r="E86" s="48"/>
+      <c r="F86" s="54">
+        <v>31587.931413768118</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="B87" s="50"/>
+      <c r="C87" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="D87" s="51"/>
+      <c r="E87" s="51"/>
+      <c r="F87" s="55">
+        <v>164704.29787439617</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="47" t="s">
+        <v>132</v>
+      </c>
+      <c r="B88" s="47"/>
+      <c r="C88" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="D88" s="48"/>
+      <c r="E88" s="48"/>
+      <c r="F88" s="54">
+        <v>196292.22928816426</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="B89" s="50"/>
+      <c r="C89" s="51" t="s">
+        <v>135</v>
+      </c>
+      <c r="D89" s="51"/>
+      <c r="E89" s="51"/>
+      <c r="F89" s="55">
+        <v>38411.870740343</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="56" t="s">
+        <v>136</v>
+      </c>
+      <c r="B90" s="56"/>
+      <c r="C90" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="D90" s="57"/>
+      <c r="E90" s="57"/>
+      <c r="F90" s="58">
+        <v>1214871.141271744</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="56" t="s">
+        <v>138</v>
+      </c>
+      <c r="B91" s="56"/>
+      <c r="C91" s="57" t="s">
+        <v>139</v>
+      </c>
+      <c r="D91" s="57"/>
+      <c r="E91" s="57"/>
+      <c r="F91" s="58">
+        <v>1018578.9119835796</v>
+      </c>
+    </row>
+    <row r="93" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="B93" s="11"/>
+      <c r="C93" s="11"/>
+      <c r="D93" s="11"/>
+      <c r="E93" s="11"/>
+      <c r="F93" s="11"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="45" t="s">
+        <v>141</v>
+      </c>
+      <c r="B94" s="45"/>
+      <c r="C94" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="D94" s="46"/>
+      <c r="E94" s="46"/>
+      <c r="F94" s="46"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="45" t="s">
+        <v>143</v>
+      </c>
+      <c r="B95" s="45"/>
+      <c r="C95" s="46" t="s">
+        <v>144</v>
+      </c>
+      <c r="D95" s="46"/>
+      <c r="E95" s="46"/>
+      <c r="F95" s="46"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="45" t="s">
+        <v>145</v>
+      </c>
+      <c r="B96" s="45"/>
+      <c r="C96" s="46" t="s">
+        <v>146</v>
+      </c>
+      <c r="D96" s="46"/>
+      <c r="E96" s="46"/>
+      <c r="F96" s="46"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="B97" s="45"/>
+      <c r="C97" s="46" t="s">
+        <v>148</v>
+      </c>
+      <c r="D97" s="46"/>
+      <c r="E97" s="46"/>
+      <c r="F97" s="46"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="45" t="s">
+        <v>149</v>
+      </c>
+      <c r="B98" s="45"/>
+      <c r="C98" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="D98" s="46"/>
+      <c r="E98" s="46"/>
+      <c r="F98" s="46"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="45" t="s">
+        <v>151</v>
+      </c>
+      <c r="B99" s="45"/>
+      <c r="C99" s="46" t="s">
+        <v>152</v>
+      </c>
+      <c r="D99" s="46"/>
+      <c r="E99" s="46"/>
+      <c r="F99" s="46"/>
+    </row>
+    <row r="101" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="43" t="s">
+        <v>153</v>
+      </c>
+      <c r="B101" s="43"/>
+      <c r="C101" s="43"/>
+      <c r="D101" s="43"/>
+      <c r="E101" s="43"/>
+      <c r="F101" s="43"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="44" t="s">
+        <v>154</v>
+      </c>
+      <c r="B102" s="44"/>
+      <c r="C102" s="44"/>
+      <c r="D102" s="44"/>
+      <c r="E102" s="44"/>
+      <c r="F102" s="44"/>
+    </row>
+    <row r="104" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="59" t="s">
+        <v>42</v>
+      </c>
+      <c r="B104" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="C104" s="61" t="s">
+        <v>155</v>
+      </c>
+      <c r="D104" s="61"/>
+      <c r="E104" s="61"/>
+      <c r="F104" s="62">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="63" t="s">
+        <v>156</v>
+      </c>
+      <c r="B105" s="62">
+        <v>130</v>
+      </c>
+      <c r="C105" s="61" t="s">
+        <v>157</v>
+      </c>
+      <c r="D105" s="61"/>
+      <c r="E105" s="61"/>
+      <c r="F105" s="62">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="106" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="63" t="s">
+        <v>158</v>
+      </c>
+      <c r="B106" s="62">
+        <v>45</v>
+      </c>
+      <c r="C106" s="61" t="s">
+        <v>159</v>
+      </c>
+      <c r="D106" s="61"/>
+      <c r="E106" s="61"/>
+      <c r="F106" s="62">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="107" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="59" t="s">
+        <v>160</v>
+      </c>
+      <c r="B107" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="C107" s="61" t="s">
+        <v>161</v>
+      </c>
+      <c r="D107" s="61"/>
+      <c r="E107" s="61"/>
+      <c r="F107" s="62">
+        <v>207.28</v>
+      </c>
+    </row>
+    <row r="108" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="63" t="s">
+        <v>162</v>
+      </c>
+      <c r="B108" s="64" t="s">
+        <v>163</v>
+      </c>
+      <c r="C108" s="61" t="s">
+        <v>164</v>
+      </c>
+      <c r="D108" s="61"/>
+      <c r="E108" s="61"/>
+      <c r="F108" s="62">
+        <v>40.14</v>
+      </c>
+    </row>
+    <row r="109" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="63" t="s">
+        <v>165</v>
+      </c>
+      <c r="B109" s="64" t="s">
+        <v>166</v>
+      </c>
+      <c r="C109" s="61" t="s">
+        <v>167</v>
+      </c>
+      <c r="D109" s="61"/>
+      <c r="E109" s="61"/>
+      <c r="F109" s="62">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="110" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="63" t="s">
+        <v>168</v>
+      </c>
+      <c r="B110" s="64" t="s">
+        <v>169</v>
+      </c>
+      <c r="C110" s="61" t="s">
+        <v>170</v>
+      </c>
+      <c r="D110" s="61"/>
+      <c r="E110" s="61"/>
+      <c r="F110" s="62">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="111" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="59" t="s">
+        <v>171</v>
+      </c>
+      <c r="B111" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="C111" s="61" t="s">
+        <v>172</v>
+      </c>
+      <c r="D111" s="61"/>
+      <c r="E111" s="61"/>
+      <c r="F111" s="62">
+        <v>10.95</v>
+      </c>
+    </row>
+    <row r="112" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="63" t="s">
+        <v>173</v>
+      </c>
+      <c r="B112" s="62">
+        <v>0</v>
+      </c>
+      <c r="C112" s="61" t="s">
+        <v>174</v>
+      </c>
+      <c r="D112" s="61"/>
+      <c r="E112" s="61"/>
+      <c r="F112" s="62">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="113" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="63" t="s">
+        <v>175</v>
+      </c>
+      <c r="B113" s="62">
+        <v>500</v>
+      </c>
+      <c r="C113" s="61" t="s">
+        <v>176</v>
+      </c>
+      <c r="D113" s="61"/>
+      <c r="E113" s="61"/>
+      <c r="F113" s="62">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="114" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="63" t="s">
+        <v>177</v>
+      </c>
+      <c r="B114" s="62">
+        <v>550</v>
+      </c>
+      <c r="C114" s="61" t="s">
+        <v>178</v>
+      </c>
+      <c r="D114" s="61"/>
+      <c r="E114" s="61"/>
+      <c r="F114" s="62">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="115" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="63" t="s">
+        <v>179</v>
+      </c>
+      <c r="B115" s="62">
+        <v>600</v>
+      </c>
+      <c r="C115" s="61" t="s">
+        <v>180</v>
+      </c>
+      <c r="D115" s="61"/>
+      <c r="E115" s="61"/>
+      <c r="F115" s="62">
+        <v>97.12</v>
+      </c>
+    </row>
+    <row r="116" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="63" t="s">
+        <v>181</v>
+      </c>
+      <c r="B116" s="62">
+        <v>650</v>
+      </c>
+      <c r="C116" s="61" t="s">
+        <v>182</v>
+      </c>
+      <c r="D116" s="61"/>
+      <c r="E116" s="61"/>
+      <c r="F116" s="62">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="117" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="63" t="s">
+        <v>183</v>
+      </c>
+      <c r="B117" s="62">
+        <v>700</v>
+      </c>
+      <c r="C117" s="61" t="s">
+        <v>184</v>
+      </c>
+      <c r="D117" s="61"/>
+      <c r="E117" s="61"/>
+      <c r="F117" s="62">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="118" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="B118" s="62">
+        <v>750</v>
+      </c>
+      <c r="C118" s="61" t="s">
+        <v>186</v>
+      </c>
+      <c r="D118" s="61"/>
+      <c r="E118" s="61"/>
+      <c r="F118" s="62">
+        <v>2.98</v>
+      </c>
+    </row>
+    <row r="119" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="63" t="s">
+        <v>187</v>
+      </c>
+      <c r="B119" s="62">
+        <v>800</v>
+      </c>
+      <c r="C119" s="61" t="s">
+        <v>188</v>
+      </c>
+      <c r="D119" s="61"/>
+      <c r="E119" s="61"/>
+      <c r="F119" s="62">
+        <v>8.08</v>
+      </c>
+    </row>
+    <row r="120" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="63" t="s">
+        <v>189</v>
+      </c>
+      <c r="B120" s="62">
+        <v>850</v>
+      </c>
+      <c r="C120" s="61" t="s">
+        <v>190</v>
+      </c>
+      <c r="D120" s="61"/>
+      <c r="E120" s="61"/>
+      <c r="F120" s="62">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="121" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="59" t="s">
+        <v>191</v>
+      </c>
+      <c r="B121" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="C121" s="61" t="s">
+        <v>192</v>
+      </c>
+      <c r="D121" s="61"/>
+      <c r="E121" s="61"/>
+      <c r="F121" s="62">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="122" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="63" t="s">
+        <v>193</v>
+      </c>
+      <c r="B122" s="62">
+        <v>1170</v>
+      </c>
+      <c r="C122" s="61" t="s">
+        <v>194</v>
+      </c>
+      <c r="D122" s="61"/>
+      <c r="E122" s="61"/>
+      <c r="F122" s="62">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="123" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="63" t="s">
+        <v>195</v>
+      </c>
+      <c r="B123" s="62">
+        <v>1560</v>
+      </c>
+      <c r="C123" s="61" t="s">
+        <v>196</v>
+      </c>
+      <c r="D123" s="61"/>
+      <c r="E123" s="61"/>
+      <c r="F123" s="62">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="124" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="63" t="s">
+        <v>197</v>
+      </c>
+      <c r="B124" s="62">
+        <v>1820</v>
+      </c>
+      <c r="C124" s="61" t="s">
+        <v>198</v>
+      </c>
+      <c r="D124" s="61"/>
+      <c r="E124" s="61"/>
+      <c r="F124" s="62">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="125" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="63" t="s">
+        <v>199</v>
+      </c>
+      <c r="B125" s="62">
+        <v>3110</v>
+      </c>
+      <c r="C125" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="D125" s="61"/>
+      <c r="E125" s="61"/>
+      <c r="F125" s="62">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="126" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="63" t="s">
+        <v>201</v>
+      </c>
+      <c r="B126" s="62">
+        <v>2340</v>
+      </c>
+      <c r="C126" s="61" t="s">
+        <v>202</v>
+      </c>
+      <c r="D126" s="61"/>
+      <c r="E126" s="61"/>
+      <c r="F126" s="62">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="127" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="63" t="s">
+        <v>203</v>
+      </c>
+      <c r="B127" s="62">
+        <v>10</v>
+      </c>
+      <c r="C127" s="61" t="s">
+        <v>204</v>
+      </c>
+      <c r="D127" s="61"/>
+      <c r="E127" s="61"/>
+      <c r="F127" s="62">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="128" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="63" t="s">
+        <v>205</v>
+      </c>
+      <c r="B128" s="62">
+        <v>20</v>
+      </c>
+      <c r="C128" s="61" t="s">
+        <v>206</v>
+      </c>
+      <c r="D128" s="61"/>
+      <c r="E128" s="61"/>
+      <c r="F128" s="62">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="129" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" s="59" t="s">
+        <v>207</v>
+      </c>
+      <c r="B129" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="C129" s="61" t="s">
+        <v>208</v>
+      </c>
+      <c r="D129" s="61"/>
+      <c r="E129" s="61"/>
+      <c r="F129" s="62">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="130" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" s="63" t="s">
+        <v>209</v>
+      </c>
+      <c r="B130" s="62">
+        <v>45</v>
+      </c>
+      <c r="C130" t="s">
+        <v>56</v>
+      </c>
+      <c r="D130"/>
+      <c r="E130"/>
+      <c r="F130" t="s">
+        <v>56</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="55">
+  <mergeCells count="166">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A2:D2"/>
@@ -2313,1015 +3144,132 @@
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="A48:C48"/>
     <mergeCell ref="A50:F50"/>
-    <mergeCell ref="B51:F51"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="B56:F56"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="C55:F55"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="C56:F56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="C57:F57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="C58:F58"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="C59:F59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="C60:F60"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="C61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="C62:F62"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="C63:F63"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="C64:F64"/>
+    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="C70:E70"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:E73"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="C74:E74"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="C75:E75"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="C79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="C82:E82"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="C83:E83"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="C84:E84"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="C85:E85"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="C86:E86"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="C87:E87"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="C88:E88"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="C89:E89"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="C91:E91"/>
+    <mergeCell ref="A93:F93"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:F94"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="C95:F95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:F96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:F97"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="C98:F98"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="C99:F99"/>
+    <mergeCell ref="A101:F101"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="C104:E104"/>
+    <mergeCell ref="C105:E105"/>
+    <mergeCell ref="C106:E106"/>
+    <mergeCell ref="C107:E107"/>
+    <mergeCell ref="C108:E108"/>
+    <mergeCell ref="C109:E109"/>
+    <mergeCell ref="C110:E110"/>
+    <mergeCell ref="C111:E111"/>
+    <mergeCell ref="C112:E112"/>
+    <mergeCell ref="C113:E113"/>
+    <mergeCell ref="C114:E114"/>
+    <mergeCell ref="C115:E115"/>
+    <mergeCell ref="C116:E116"/>
+    <mergeCell ref="C117:E117"/>
+    <mergeCell ref="C118:E118"/>
+    <mergeCell ref="C119:E119"/>
+    <mergeCell ref="C120:E120"/>
+    <mergeCell ref="C121:E121"/>
+    <mergeCell ref="C122:E122"/>
+    <mergeCell ref="C123:E123"/>
+    <mergeCell ref="C124:E124"/>
+    <mergeCell ref="C125:E125"/>
+    <mergeCell ref="C126:E126"/>
+    <mergeCell ref="C127:E127"/>
+    <mergeCell ref="C128:E128"/>
+    <mergeCell ref="C129:E129"/>
+    <mergeCell ref="C130:E130"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.25" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="80" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="78" fitToWidth="1" fitToHeight="1"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;8ul. Polna 5, Katowice&amp;R&amp;8Strona &amp;P z &amp;N</oddFooter>
   </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E72"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="5" width="19" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
-        <v>80</v>
-      </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
-        <v>81</v>
-      </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="43" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="44" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="43" t="s">
-        <v>85</v>
-      </c>
-      <c r="B6" s="44" t="s">
-        <v>86</v>
-      </c>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="B7" s="44" t="s">
-        <v>88</v>
-      </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="43" t="s">
-        <v>89</v>
-      </c>
-      <c r="B8" s="44" t="s">
-        <v>86</v>
-      </c>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="43" t="s">
-        <v>90</v>
-      </c>
-      <c r="B9" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="43" t="s">
-        <v>92</v>
-      </c>
-      <c r="B10" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="43" t="s">
-        <v>94</v>
-      </c>
-      <c r="B11" s="44" t="s">
-        <v>95</v>
-      </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="43" t="s">
-        <v>96</v>
-      </c>
-      <c r="B12" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="43" t="s">
-        <v>98</v>
-      </c>
-      <c r="B13" s="44" t="s">
-        <v>99</v>
-      </c>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="43" t="s">
-        <v>100</v>
-      </c>
-      <c r="B14" s="44" t="s">
-        <v>101</v>
-      </c>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="B15" s="44" t="s">
-        <v>103</v>
-      </c>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
-    </row>
-    <row r="17" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-    </row>
-    <row r="18" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="47" t="s">
-        <v>108</v>
-      </c>
-      <c r="B19" s="48" t="s">
-        <v>109</v>
-      </c>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="49">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="50" t="s">
-        <v>110</v>
-      </c>
-      <c r="B20" s="51" t="s">
-        <v>111</v>
-      </c>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="52">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="47" t="s">
-        <v>112</v>
-      </c>
-      <c r="B21" s="48" t="s">
-        <v>113</v>
-      </c>
-      <c r="C21" s="48"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="49">
-        <v>22.4568</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="50" t="s">
-        <v>114</v>
-      </c>
-      <c r="B22" s="51" t="s">
-        <v>115</v>
-      </c>
-      <c r="C22" s="51"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="52">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="B23" s="48" t="s">
-        <v>117</v>
-      </c>
-      <c r="C23" s="48"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="53">
-        <v>2660</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="50" t="s">
-        <v>118</v>
-      </c>
-      <c r="B24" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="C24" s="51"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="52">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" s="48" t="s">
-        <v>120</v>
-      </c>
-      <c r="C25" s="48"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="54">
-        <v>850524.2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="50" t="s">
-        <v>121</v>
-      </c>
-      <c r="B26" s="51" t="s">
-        <v>122</v>
-      </c>
-      <c r="C26" s="51"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="55">
-        <v>3005.8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="47" t="s">
-        <v>123</v>
-      </c>
-      <c r="B27" s="48" t="s">
-        <v>124</v>
-      </c>
-      <c r="C27" s="48"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="54">
-        <v>23400</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="50" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" s="51" t="s">
-        <v>125</v>
-      </c>
-      <c r="C28" s="51"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="55">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="47" t="s">
-        <v>126</v>
-      </c>
-      <c r="B29" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="C29" s="48"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="54">
-        <v>9600</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="50" t="s">
-        <v>128</v>
-      </c>
-      <c r="B30" s="51" t="s">
-        <v>129</v>
-      </c>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="55">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="47" t="s">
-        <v>130</v>
-      </c>
-      <c r="B31" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="C31" s="48"/>
-      <c r="D31" s="48"/>
-      <c r="E31" s="54">
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="50" t="s">
-        <v>132</v>
-      </c>
-      <c r="B32" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="55">
-        <v>6582.72</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="47" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="48" t="s">
-        <v>134</v>
-      </c>
-      <c r="C33" s="48"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="54">
-        <v>61200</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="50" t="s">
-        <v>135</v>
-      </c>
-      <c r="B34" s="51" t="s">
-        <v>136</v>
-      </c>
-      <c r="C34" s="51"/>
-      <c r="D34" s="51"/>
-      <c r="E34" s="55">
-        <v>7895.556</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="56" t="s">
-        <v>137</v>
-      </c>
-      <c r="B35" s="57" t="s">
-        <v>138</v>
-      </c>
-      <c r="C35" s="57"/>
-      <c r="D35" s="57"/>
-      <c r="E35" s="58">
-        <v>974108.276</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="50" t="s">
-        <v>139</v>
-      </c>
-      <c r="B36" s="51" t="s">
-        <v>140</v>
-      </c>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="55">
-        <v>6058.765243236716</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="47" t="s">
-        <v>141</v>
-      </c>
-      <c r="B37" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="C37" s="48"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="54">
-        <v>31587.931413768118</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="50" t="s">
-        <v>143</v>
-      </c>
-      <c r="B38" s="51" t="s">
-        <v>144</v>
-      </c>
-      <c r="C38" s="51"/>
-      <c r="D38" s="51"/>
-      <c r="E38" s="55">
-        <v>164704.29787439617</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="47" t="s">
-        <v>145</v>
-      </c>
-      <c r="B39" s="48" t="s">
-        <v>146</v>
-      </c>
-      <c r="C39" s="48"/>
-      <c r="D39" s="48"/>
-      <c r="E39" s="54">
-        <v>196292.22928816426</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="50" t="s">
-        <v>147</v>
-      </c>
-      <c r="B40" s="51" t="s">
-        <v>148</v>
-      </c>
-      <c r="C40" s="51"/>
-      <c r="D40" s="51"/>
-      <c r="E40" s="55">
-        <v>38411.870740343</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="56" t="s">
-        <v>149</v>
-      </c>
-      <c r="B41" s="57" t="s">
-        <v>150</v>
-      </c>
-      <c r="C41" s="57"/>
-      <c r="D41" s="57"/>
-      <c r="E41" s="58">
-        <v>1214871.141271744</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="56" t="s">
-        <v>151</v>
-      </c>
-      <c r="B42" s="57" t="s">
-        <v>152</v>
-      </c>
-      <c r="C42" s="57"/>
-      <c r="D42" s="57"/>
-      <c r="E42" s="58">
-        <v>1018578.9119835796</v>
-      </c>
-    </row>
-    <row r="43" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="45" t="s">
-        <v>153</v>
-      </c>
-      <c r="B43" s="45"/>
-      <c r="C43" s="45"/>
-      <c r="D43" s="45"/>
-      <c r="E43" s="45"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="46" t="s">
-        <v>154</v>
-      </c>
-      <c r="B44" s="46"/>
-      <c r="C44" s="46"/>
-      <c r="D44" s="46"/>
-      <c r="E44" s="46"/>
-    </row>
-    <row r="46" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="B46" s="60" t="s">
-        <v>56</v>
-      </c>
-      <c r="C46" s="61" t="s">
-        <v>155</v>
-      </c>
-      <c r="D46" s="61"/>
-      <c r="E46" s="62">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="61" t="s">
-        <v>156</v>
-      </c>
-      <c r="B47" s="62">
-        <v>130</v>
-      </c>
-      <c r="C47" s="61" t="s">
-        <v>157</v>
-      </c>
-      <c r="D47" s="61"/>
-      <c r="E47" s="62">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="48" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="61" t="s">
-        <v>158</v>
-      </c>
-      <c r="B48" s="62">
-        <v>45</v>
-      </c>
-      <c r="C48" s="61" t="s">
-        <v>159</v>
-      </c>
-      <c r="D48" s="61"/>
-      <c r="E48" s="62">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="49" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="59" t="s">
-        <v>160</v>
-      </c>
-      <c r="B49" s="60" t="s">
-        <v>56</v>
-      </c>
-      <c r="C49" s="61" t="s">
-        <v>161</v>
-      </c>
-      <c r="D49" s="61"/>
-      <c r="E49" s="62">
-        <v>207.28</v>
-      </c>
-    </row>
-    <row r="50" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="61" t="s">
-        <v>162</v>
-      </c>
-      <c r="B50" s="63" t="s">
-        <v>163</v>
-      </c>
-      <c r="C50" s="61" t="s">
-        <v>164</v>
-      </c>
-      <c r="D50" s="61"/>
-      <c r="E50" s="62">
-        <v>40.14</v>
-      </c>
-    </row>
-    <row r="51" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="61" t="s">
-        <v>165</v>
-      </c>
-      <c r="B51" s="63" t="s">
-        <v>166</v>
-      </c>
-      <c r="C51" s="61" t="s">
-        <v>167</v>
-      </c>
-      <c r="D51" s="61"/>
-      <c r="E51" s="62">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="52" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="61" t="s">
-        <v>168</v>
-      </c>
-      <c r="B52" s="63" t="s">
-        <v>169</v>
-      </c>
-      <c r="C52" s="61" t="s">
-        <v>170</v>
-      </c>
-      <c r="D52" s="61"/>
-      <c r="E52" s="62">
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="53" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="59" t="s">
-        <v>171</v>
-      </c>
-      <c r="B53" s="60" t="s">
-        <v>56</v>
-      </c>
-      <c r="C53" s="61" t="s">
-        <v>172</v>
-      </c>
-      <c r="D53" s="61"/>
-      <c r="E53" s="62">
-        <v>10.95</v>
-      </c>
-    </row>
-    <row r="54" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="61" t="s">
-        <v>173</v>
-      </c>
-      <c r="B54" s="62">
-        <v>0</v>
-      </c>
-      <c r="C54" s="61" t="s">
-        <v>174</v>
-      </c>
-      <c r="D54" s="61"/>
-      <c r="E54" s="62">
-        <v>3.81</v>
-      </c>
-    </row>
-    <row r="55" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="61" t="s">
-        <v>175</v>
-      </c>
-      <c r="B55" s="62">
-        <v>500</v>
-      </c>
-      <c r="C55" s="61" t="s">
-        <v>176</v>
-      </c>
-      <c r="D55" s="61"/>
-      <c r="E55" s="62">
-        <v>2.84</v>
-      </c>
-    </row>
-    <row r="56" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="61" t="s">
-        <v>177</v>
-      </c>
-      <c r="B56" s="62">
-        <v>550</v>
-      </c>
-      <c r="C56" s="61" t="s">
-        <v>178</v>
-      </c>
-      <c r="D56" s="61"/>
-      <c r="E56" s="62">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="57" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="61" t="s">
-        <v>179</v>
-      </c>
-      <c r="B57" s="62">
-        <v>600</v>
-      </c>
-      <c r="C57" s="61" t="s">
-        <v>180</v>
-      </c>
-      <c r="D57" s="61"/>
-      <c r="E57" s="62">
-        <v>97.12</v>
-      </c>
-    </row>
-    <row r="58" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="61" t="s">
-        <v>181</v>
-      </c>
-      <c r="B58" s="62">
-        <v>650</v>
-      </c>
-      <c r="C58" s="61" t="s">
-        <v>182</v>
-      </c>
-      <c r="D58" s="61"/>
-      <c r="E58" s="62">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="59" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="61" t="s">
-        <v>183</v>
-      </c>
-      <c r="B59" s="62">
-        <v>700</v>
-      </c>
-      <c r="C59" s="61" t="s">
-        <v>184</v>
-      </c>
-      <c r="D59" s="61"/>
-      <c r="E59" s="62">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="60" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="61" t="s">
-        <v>185</v>
-      </c>
-      <c r="B60" s="62">
-        <v>750</v>
-      </c>
-      <c r="C60" s="61" t="s">
-        <v>186</v>
-      </c>
-      <c r="D60" s="61"/>
-      <c r="E60" s="62">
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="61" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="61" t="s">
-        <v>187</v>
-      </c>
-      <c r="B61" s="62">
-        <v>800</v>
-      </c>
-      <c r="C61" s="61" t="s">
-        <v>188</v>
-      </c>
-      <c r="D61" s="61"/>
-      <c r="E61" s="62">
-        <v>8.08</v>
-      </c>
-    </row>
-    <row r="62" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="61" t="s">
-        <v>189</v>
-      </c>
-      <c r="B62" s="62">
-        <v>850</v>
-      </c>
-      <c r="C62" s="61" t="s">
-        <v>190</v>
-      </c>
-      <c r="D62" s="61"/>
-      <c r="E62" s="62">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="63" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="59" t="s">
-        <v>191</v>
-      </c>
-      <c r="B63" s="60" t="s">
-        <v>56</v>
-      </c>
-      <c r="C63" s="61" t="s">
-        <v>192</v>
-      </c>
-      <c r="D63" s="61"/>
-      <c r="E63" s="62">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="64" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="61" t="s">
-        <v>193</v>
-      </c>
-      <c r="B64" s="62">
-        <v>1170</v>
-      </c>
-      <c r="C64" s="61" t="s">
-        <v>194</v>
-      </c>
-      <c r="D64" s="61"/>
-      <c r="E64" s="62">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="65" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="61" t="s">
-        <v>195</v>
-      </c>
-      <c r="B65" s="62">
-        <v>1560</v>
-      </c>
-      <c r="C65" s="61" t="s">
-        <v>196</v>
-      </c>
-      <c r="D65" s="61"/>
-      <c r="E65" s="62">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="66" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="61" t="s">
-        <v>197</v>
-      </c>
-      <c r="B66" s="62">
-        <v>1820</v>
-      </c>
-      <c r="C66" s="61" t="s">
-        <v>198</v>
-      </c>
-      <c r="D66" s="61"/>
-      <c r="E66" s="62">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="67" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="61" t="s">
-        <v>199</v>
-      </c>
-      <c r="B67" s="62">
-        <v>3110</v>
-      </c>
-      <c r="C67" s="61" t="s">
-        <v>200</v>
-      </c>
-      <c r="D67" s="61"/>
-      <c r="E67" s="62">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="68" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="61" t="s">
-        <v>201</v>
-      </c>
-      <c r="B68" s="62">
-        <v>2340</v>
-      </c>
-      <c r="C68" s="61" t="s">
-        <v>202</v>
-      </c>
-      <c r="D68" s="61"/>
-      <c r="E68" s="62">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="69" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="61" t="s">
-        <v>203</v>
-      </c>
-      <c r="B69" s="62">
-        <v>10</v>
-      </c>
-      <c r="C69" s="61" t="s">
-        <v>204</v>
-      </c>
-      <c r="D69" s="61"/>
-      <c r="E69" s="62">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="70" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="61" t="s">
-        <v>205</v>
-      </c>
-      <c r="B70" s="62">
-        <v>20</v>
-      </c>
-      <c r="C70" s="61" t="s">
-        <v>206</v>
-      </c>
-      <c r="D70" s="61"/>
-      <c r="E70" s="62">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="71" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="59" t="s">
-        <v>207</v>
-      </c>
-      <c r="B71" s="60" t="s">
-        <v>56</v>
-      </c>
-      <c r="C71" s="61" t="s">
-        <v>208</v>
-      </c>
-      <c r="D71" s="61"/>
-      <c r="E71" s="62">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="72" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="61" t="s">
-        <v>209</v>
-      </c>
-      <c r="B72" s="62">
-        <v>45</v>
-      </c>
-      <c r="C72" t="s">
-        <v>56</v>
-      </c>
-      <c r="D72"/>
-      <c r="E72" t="s">
-        <v>56</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="69">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-  </mergeCells>
-  <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.25" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="82" fitToWidth="1" fitToHeight="1"/>
-  <headerFooter>
-    <oddFooter>&amp;L&amp;8ul. Polna 5, Katowice&amp;R&amp;8Strona &amp;P z &amp;N</oddFooter>
-  </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="42" max="16838" man="1"/>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="49" max="16838" man="1"/>
+    <brk id="100" max="16838" man="1"/>
   </rowBreaks>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
@@ -22,10 +22,10 @@
     <t>ul. Polna 5, Katowice</t>
   </si>
   <si>
-    <t>21.10.2026, 10:27</t>
-  </si>
-  <si>
-    <t>Wygenerowano 30.10.2026, 10:27:59 · ceny netto w zł · szablon NK38</t>
+    <t>21.10.2026, 11:44</t>
+  </si>
+  <si>
+    <t>Wygenerowano 30.10.2026, 11:44:45 · ceny netto w zł · szablon NK38</t>
   </si>
   <si>
     <t>Cena</t>
@@ -867,7 +867,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
@@ -1052,8 +1052,11 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="3"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" indent="3"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2681,7 +2684,7 @@
       <c r="A105" s="63" t="s">
         <v>156</v>
       </c>
-      <c r="B105" s="62">
+      <c r="B105" s="64">
         <v>130</v>
       </c>
       <c r="C105" s="61" t="s">
@@ -2697,7 +2700,7 @@
       <c r="A106" s="63" t="s">
         <v>158</v>
       </c>
-      <c r="B106" s="62">
+      <c r="B106" s="64">
         <v>45</v>
       </c>
       <c r="C106" s="61" t="s">
@@ -2729,7 +2732,7 @@
       <c r="A108" s="63" t="s">
         <v>162</v>
       </c>
-      <c r="B108" s="64" t="s">
+      <c r="B108" s="65" t="s">
         <v>163</v>
       </c>
       <c r="C108" s="61" t="s">
@@ -2745,7 +2748,7 @@
       <c r="A109" s="63" t="s">
         <v>165</v>
       </c>
-      <c r="B109" s="64" t="s">
+      <c r="B109" s="65" t="s">
         <v>166</v>
       </c>
       <c r="C109" s="61" t="s">
@@ -2761,7 +2764,7 @@
       <c r="A110" s="63" t="s">
         <v>168</v>
       </c>
-      <c r="B110" s="64" t="s">
+      <c r="B110" s="65" t="s">
         <v>169</v>
       </c>
       <c r="C110" s="61" t="s">
@@ -2793,7 +2796,7 @@
       <c r="A112" s="63" t="s">
         <v>173</v>
       </c>
-      <c r="B112" s="62">
+      <c r="B112" s="64">
         <v>0</v>
       </c>
       <c r="C112" s="61" t="s">
@@ -2809,7 +2812,7 @@
       <c r="A113" s="63" t="s">
         <v>175</v>
       </c>
-      <c r="B113" s="62">
+      <c r="B113" s="64">
         <v>500</v>
       </c>
       <c r="C113" s="61" t="s">
@@ -2825,7 +2828,7 @@
       <c r="A114" s="63" t="s">
         <v>177</v>
       </c>
-      <c r="B114" s="62">
+      <c r="B114" s="64">
         <v>550</v>
       </c>
       <c r="C114" s="61" t="s">
@@ -2841,7 +2844,7 @@
       <c r="A115" s="63" t="s">
         <v>179</v>
       </c>
-      <c r="B115" s="62">
+      <c r="B115" s="64">
         <v>600</v>
       </c>
       <c r="C115" s="61" t="s">
@@ -2857,7 +2860,7 @@
       <c r="A116" s="63" t="s">
         <v>181</v>
       </c>
-      <c r="B116" s="62">
+      <c r="B116" s="64">
         <v>650</v>
       </c>
       <c r="C116" s="61" t="s">
@@ -2873,7 +2876,7 @@
       <c r="A117" s="63" t="s">
         <v>183</v>
       </c>
-      <c r="B117" s="62">
+      <c r="B117" s="64">
         <v>700</v>
       </c>
       <c r="C117" s="61" t="s">
@@ -2889,7 +2892,7 @@
       <c r="A118" s="63" t="s">
         <v>185</v>
       </c>
-      <c r="B118" s="62">
+      <c r="B118" s="64">
         <v>750</v>
       </c>
       <c r="C118" s="61" t="s">
@@ -2905,7 +2908,7 @@
       <c r="A119" s="63" t="s">
         <v>187</v>
       </c>
-      <c r="B119" s="62">
+      <c r="B119" s="64">
         <v>800</v>
       </c>
       <c r="C119" s="61" t="s">
@@ -2921,7 +2924,7 @@
       <c r="A120" s="63" t="s">
         <v>189</v>
       </c>
-      <c r="B120" s="62">
+      <c r="B120" s="64">
         <v>850</v>
       </c>
       <c r="C120" s="61" t="s">
@@ -2953,7 +2956,7 @@
       <c r="A122" s="63" t="s">
         <v>193</v>
       </c>
-      <c r="B122" s="62">
+      <c r="B122" s="64">
         <v>1170</v>
       </c>
       <c r="C122" s="61" t="s">
@@ -2969,7 +2972,7 @@
       <c r="A123" s="63" t="s">
         <v>195</v>
       </c>
-      <c r="B123" s="62">
+      <c r="B123" s="64">
         <v>1560</v>
       </c>
       <c r="C123" s="61" t="s">
@@ -2985,7 +2988,7 @@
       <c r="A124" s="63" t="s">
         <v>197</v>
       </c>
-      <c r="B124" s="62">
+      <c r="B124" s="64">
         <v>1820</v>
       </c>
       <c r="C124" s="61" t="s">
@@ -3001,7 +3004,7 @@
       <c r="A125" s="63" t="s">
         <v>199</v>
       </c>
-      <c r="B125" s="62">
+      <c r="B125" s="64">
         <v>3110</v>
       </c>
       <c r="C125" s="61" t="s">
@@ -3017,7 +3020,7 @@
       <c r="A126" s="63" t="s">
         <v>201</v>
       </c>
-      <c r="B126" s="62">
+      <c r="B126" s="64">
         <v>2340</v>
       </c>
       <c r="C126" s="61" t="s">
@@ -3033,7 +3036,7 @@
       <c r="A127" s="63" t="s">
         <v>203</v>
       </c>
-      <c r="B127" s="62">
+      <c r="B127" s="64">
         <v>10</v>
       </c>
       <c r="C127" s="61" t="s">
@@ -3049,7 +3052,7 @@
       <c r="A128" s="63" t="s">
         <v>205</v>
       </c>
-      <c r="B128" s="62">
+      <c r="B128" s="64">
         <v>20</v>
       </c>
       <c r="C128" s="61" t="s">
@@ -3081,7 +3084,7 @@
       <c r="A130" s="63" t="s">
         <v>209</v>
       </c>
-      <c r="B130" s="62">
+      <c r="B130" s="64">
         <v>45</v>
       </c>
       <c r="C130" t="s">

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
@@ -22,10 +22,10 @@
     <t>ul. Polna 5, Katowice</t>
   </si>
   <si>
-    <t>21.10.2026, 11:44</t>
-  </si>
-  <si>
-    <t>Wygenerowano 30.10.2026, 11:44:45 · ceny netto w zł · szablon NK38</t>
+    <t>21.10.2026, 12:42</t>
+  </si>
+  <si>
+    <t>Wygenerowano 30.10.2026, 12:42:33 · ceny netto w zł · szablon NK38</t>
   </si>
   <si>
     <t>Cena</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Polna_5_Katowice_NK38.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="211">
   <si>
     <t>KALKULACJA NK38</t>
   </si>
@@ -22,10 +22,10 @@
     <t>ul. Polna 5, Katowice</t>
   </si>
   <si>
-    <t>21.10.2026, 12:42</t>
-  </si>
-  <si>
-    <t>Wygenerowano 30.10.2026, 12:42:33 · ceny netto w zł · szablon NK38</t>
+    <t>21.10.2026, 12:45</t>
+  </si>
+  <si>
+    <t>Ceny netto · wygenerowano 30.10.2026</t>
   </si>
   <si>
     <t>Cena</t>
@@ -40,7 +40,10 @@
     <t>Rabat od oferty</t>
   </si>
   <si>
-    <t>Cena ofertowa · zysk 14% · 2000 kg · 3511 € / MP</t>
+    <t>Cena ofertowa · zysk 14% · 2000 kg</t>
+  </si>
+  <si>
+    <t>15 186 zł · 3511 €</t>
   </si>
   <si>
     <t>–</t>
@@ -52,13 +55,13 @@
     <t>−61 766 zł (−5,08%)</t>
   </si>
   <si>
-    <t>Próg opłacalności · zysk 0% (maks. rabat)</t>
+    <t>Próg opłacalności · zysk 0% · maks. rabat</t>
   </si>
   <si>
     <t>−193 847 zł (−15,96%)</t>
   </si>
   <si>
-    <t>Pole do negocjacji: o ile można zejść z ceny (2000 kg)</t>
+    <t>Pole do negocjacji (2000 kg)</t>
   </si>
   <si>
     <t>Zysk</t>
@@ -657,7 +660,7 @@
     <numFmt numFmtId="170" formatCode="&quot;+&quot;#,##0 &quot;zł&quot;"/>
     <numFmt numFmtId="171" formatCode="#,##0.##"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -667,98 +670,104 @@
     </font>
     <font>
       <color rgb="FF6A7780"/>
-      <sz val="8"/>
-      <name val="Arial"/>
+      <sz val="9"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0E171C"/>
-      <sz val="16"/>
-      <name val="Arial"/>
+      <sz val="17.5"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0E171C"/>
-      <sz val="13"/>
-      <name val="Arial"/>
+      <sz val="14.5"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <color rgb="FF6A7780"/>
-      <sz val="9"/>
-      <name val="Arial"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0A6B74"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF0E171C"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0E171C"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0A6B74"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0A6B74"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF13794A"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FFB42318"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF6A7780"/>
+      <sz val="9.5"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0A6B74"/>
       <sz val="9"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FF0E171C"/>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0E171C"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF0A6B74"/>
-      <sz val="11"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF0A6B74"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF13794A"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FFB42318"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FF6A7780"/>
-      <sz val="8.5"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF0A6B74"/>
-      <sz val="8"/>
-      <name val="Arial"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0E171C"/>
-      <sz val="11"/>
-      <name val="Arial"/>
+      <sz val="11.5"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <color rgb="FF6A7780"/>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF6A7780"/>
-      <sz val="9"/>
-      <name val="Arial"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <color rgb="FF0E171C"/>
-      <sz val="8.5"/>
-      <name val="Arial"/>
+      <sz val="9.5"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="9">
@@ -804,7 +813,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -837,12 +846,40 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFD3D9DD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD3D9DD"/>
+      </right>
       <top style="thin">
         <color rgb="FFD3D9DD"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD3D9DD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD3D9DD"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD3D9DD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD3D9DD"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD3D9DD"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -867,7 +904,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
@@ -955,21 +992,24 @@
       <alignment wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment indent="1"/>
+      <alignment vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -999,7 +1039,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1035,27 +1075,27 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="3"/>
     </xf>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="18" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="18" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="3"/>
     </xf>
   </cellXfs>
@@ -1397,7 +1437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F130"/>
+  <dimension ref="A1:F131"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1467,16 +1507,16 @@
       <c r="D6" s="9">
         <v>1214871.141271744</v>
       </c>
-      <c r="E6" s="9">
-        <v>15185.8892658968</v>
+      <c r="E6" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -1487,12 +1527,12 @@
         <v>14413.81821677713</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -1503,12 +1543,12 @@
         <v>12762.798514630735</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -1518,7 +1558,7 @@
     </row>
     <row r="11" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>6</v>
@@ -1527,10 +1567,10 @@
         <v>8</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F11" s="13" t="s">
         <v>7</v>
@@ -1698,7 +1738,7 @@
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" s="29"/>
       <c r="C20" s="29"/>
@@ -1708,7 +1748,7 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -1718,119 +1758,117 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="30"/>
       <c r="C23" s="30"/>
       <c r="D23" s="30" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E23" s="30"/>
       <c r="F23" s="30"/>
     </row>
     <row r="24" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" s="31"/>
       <c r="C24" s="31"/>
       <c r="D24" s="31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E24" s="31"/>
       <c r="F24" s="31"/>
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E25" s="33"/>
       <c r="F25" s="33"/>
     </row>
     <row r="26" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
       <c r="D26" s="31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E26" s="31"/>
       <c r="F26" s="31"/>
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" s="33"/>
       <c r="C27" s="33"/>
       <c r="D27" s="33" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E27" s="33"/>
       <c r="F27" s="33"/>
     </row>
     <row r="28" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B28" s="31"/>
       <c r="C28" s="31"/>
       <c r="D28" s="31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E28" s="31"/>
       <c r="F28" s="31"/>
     </row>
     <row r="29" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="33" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29" s="33"/>
       <c r="C29" s="33"/>
       <c r="D29" s="33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E29" s="33"/>
       <c r="F29" s="33"/>
     </row>
     <row r="30" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="31" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B30" s="31"/>
       <c r="C30" s="31"/>
       <c r="D30" s="31" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E30" s="31"/>
       <c r="F30" s="31"/>
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="33"/>
-      <c r="C31" s="33"/>
-      <c r="D31" s="33" t="s">
+      <c r="A31" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="E31" s="33"/>
-      <c r="F31" s="33"/>
-    </row>
-    <row r="33" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="34" t="s">
+      <c r="B31" s="34"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="35" t="s">
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="35" t="s">
         <v>40</v>
       </c>
+      <c r="B33" s="35"/>
       <c r="C33" s="35"/>
       <c r="D33" s="35"/>
       <c r="E33" s="35"/>
@@ -1841,187 +1879,181 @@
         <v>41</v>
       </c>
       <c r="B34" s="36"/>
-      <c r="C34" s="36" t="s">
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="37" t="s">
         <v>42</v>
-      </c>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="F34" s="36"/>
-    </row>
-    <row r="35" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="37" t="s">
-        <v>44</v>
       </c>
       <c r="B35" s="37"/>
       <c r="C35" s="37" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D35" s="37"/>
       <c r="E35" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="F35" s="37"/>
+    </row>
+    <row r="36" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="F35" s="37"/>
-    </row>
-    <row r="37" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
+      <c r="D36" s="38"/>
+      <c r="E36" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="F36" s="38"/>
+    </row>
+    <row r="38" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="13" t="s">
+      <c r="B38" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="F37" s="13" t="s">
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="13" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="38" t="s">
+      <c r="F38" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="B38" s="39" t="s">
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="C38" s="39"/>
-      <c r="D38" s="39"/>
-      <c r="E38" s="40">
+      <c r="B39" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" s="40"/>
+      <c r="D39" s="40"/>
+      <c r="E39" s="41">
         <v>73583.83047722955</v>
       </c>
-      <c r="F38" s="40">
+      <c r="F39" s="41">
         <v>69808.76284417766</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="B39" s="39" t="s">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="39"/>
-      <c r="D39" s="39"/>
-      <c r="E39" s="40">
+      <c r="B40" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="41">
         <v>194849.14933479228</v>
       </c>
-      <c r="F39" s="40">
+      <c r="F40" s="41">
         <v>184958.52199217537</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="B40" s="39" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="C40" s="39"/>
-      <c r="D40" s="39"/>
-      <c r="E40" s="40">
+      <c r="B41" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="C41" s="40"/>
+      <c r="D41" s="40"/>
+      <c r="E41" s="41">
         <v>338647.7850241546</v>
       </c>
-      <c r="F40" s="40">
+      <c r="F41" s="41">
         <v>321274.1543778802</v>
       </c>
     </row>
-    <row r="42" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="13" t="s">
+    <row r="43" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="E42" s="13" t="s">
+      <c r="B43" s="12"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="F42" s="13" t="s">
+      <c r="E43" s="13" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="8" t="s">
+      <c r="F43" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="41">
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="42">
         <v>2800</v>
       </c>
-      <c r="E43" s="41">
+      <c r="E44" s="42">
         <v>33600</v>
       </c>
-      <c r="F43" s="41">
+      <c r="F44" s="42">
         <v>16800</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="B44" s="42"/>
-      <c r="C44" s="42"/>
-      <c r="D44" s="9">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="43" t="s">
+        <v>63</v>
+      </c>
+      <c r="B45" s="43"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="9">
         <v>3200</v>
       </c>
-      <c r="E44" s="9">
+      <c r="E45" s="9">
         <v>38400</v>
       </c>
-      <c r="F44" s="9">
+      <c r="F45" s="9">
         <v>19200</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="41">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="42">
         <v>3600</v>
       </c>
-      <c r="E45" s="41">
+      <c r="E46" s="42">
         <v>43200</v>
       </c>
-      <c r="F45" s="41">
+      <c r="F46" s="42">
         <v>21600</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="42" t="s">
-        <v>64</v>
-      </c>
-      <c r="B46" s="42"/>
-      <c r="C46" s="42"/>
-      <c r="D46" s="9">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="B47" s="43"/>
+      <c r="C47" s="43"/>
+      <c r="D47" s="9">
         <v>4000</v>
       </c>
-      <c r="E46" s="9">
+      <c r="E47" s="9">
         <v>48000</v>
       </c>
-      <c r="F46" s="9">
+      <c r="F47" s="9">
         <v>24000</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="41">
-        <v>4400</v>
-      </c>
-      <c r="E47" s="41">
-        <v>52800</v>
-      </c>
-      <c r="F47" s="41">
-        <v>26400</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2030,27 +2062,33 @@
       </c>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
-      <c r="D48" s="41">
+      <c r="D48" s="42">
+        <v>4400</v>
+      </c>
+      <c r="E48" s="42">
+        <v>52800</v>
+      </c>
+      <c r="F48" s="42">
+        <v>26400</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="42">
         <v>4800</v>
       </c>
-      <c r="E48" s="41">
+      <c r="E49" s="42">
         <v>57600</v>
       </c>
-      <c r="F48" s="41">
+      <c r="F49" s="42">
         <v>28800</v>
       </c>
     </row>
-    <row r="50" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="43" t="s">
-        <v>67</v>
-      </c>
-      <c r="B50" s="43"/>
-      <c r="C50" s="43"/>
-      <c r="D50" s="43"/>
-      <c r="E50" s="43"/>
-      <c r="F50" s="43"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="44" t="s">
         <v>68</v>
       </c>
@@ -2060,601 +2098,601 @@
       <c r="E51" s="44"/>
       <c r="F51" s="44"/>
     </row>
-    <row r="53" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="11" t="s">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="11"/>
-      <c r="F53" s="11"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="45" t="s">
+      <c r="B52" s="45"/>
+      <c r="C52" s="45"/>
+      <c r="D52" s="45"/>
+      <c r="E52" s="45"/>
+      <c r="F52" s="45"/>
+    </row>
+    <row r="54" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="B54" s="45"/>
-      <c r="C54" s="46" t="s">
+      <c r="B54" s="11"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="46" t="s">
         <v>71</v>
       </c>
-      <c r="D54" s="46"/>
-      <c r="E54" s="46"/>
-      <c r="F54" s="46"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="45" t="s">
+      <c r="B55" s="46"/>
+      <c r="C55" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="B55" s="45"/>
-      <c r="C55" s="46" t="s">
+      <c r="D55" s="47"/>
+      <c r="E55" s="47"/>
+      <c r="F55" s="47"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="D55" s="46"/>
-      <c r="E55" s="46"/>
-      <c r="F55" s="46"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="45" t="s">
+      <c r="B56" s="46"/>
+      <c r="C56" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="B56" s="45"/>
-      <c r="C56" s="46" t="s">
+      <c r="D56" s="47"/>
+      <c r="E56" s="47"/>
+      <c r="F56" s="47"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="D56" s="46"/>
-      <c r="E56" s="46"/>
-      <c r="F56" s="46"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="45" t="s">
+      <c r="B57" s="46"/>
+      <c r="C57" s="47" t="s">
         <v>76</v>
       </c>
-      <c r="B57" s="45"/>
-      <c r="C57" s="46" t="s">
-        <v>73</v>
-      </c>
-      <c r="D57" s="46"/>
-      <c r="E57" s="46"/>
-      <c r="F57" s="46"/>
+      <c r="D57" s="47"/>
+      <c r="E57" s="47"/>
+      <c r="F57" s="47"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="45" t="s">
+      <c r="A58" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="B58" s="45"/>
-      <c r="C58" s="46" t="s">
+      <c r="B58" s="46"/>
+      <c r="C58" s="47" t="s">
+        <v>74</v>
+      </c>
+      <c r="D58" s="47"/>
+      <c r="E58" s="47"/>
+      <c r="F58" s="47"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="D58" s="46"/>
-      <c r="E58" s="46"/>
-      <c r="F58" s="46"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="45" t="s">
+      <c r="B59" s="46"/>
+      <c r="C59" s="47" t="s">
         <v>79</v>
       </c>
-      <c r="B59" s="45"/>
-      <c r="C59" s="46" t="s">
+      <c r="D59" s="47"/>
+      <c r="E59" s="47"/>
+      <c r="F59" s="47"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="D59" s="46"/>
-      <c r="E59" s="46"/>
-      <c r="F59" s="46"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="45" t="s">
+      <c r="B60" s="46"/>
+      <c r="C60" s="47" t="s">
         <v>81</v>
       </c>
-      <c r="B60" s="45"/>
-      <c r="C60" s="46" t="s">
+      <c r="D60" s="47"/>
+      <c r="E60" s="47"/>
+      <c r="F60" s="47"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="D60" s="46"/>
-      <c r="E60" s="46"/>
-      <c r="F60" s="46"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="45" t="s">
+      <c r="B61" s="46"/>
+      <c r="C61" s="47" t="s">
         <v>83</v>
       </c>
-      <c r="B61" s="45"/>
-      <c r="C61" s="46" t="s">
+      <c r="D61" s="47"/>
+      <c r="E61" s="47"/>
+      <c r="F61" s="47"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="D61" s="46"/>
-      <c r="E61" s="46"/>
-      <c r="F61" s="46"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="45" t="s">
+      <c r="B62" s="46"/>
+      <c r="C62" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="B62" s="45"/>
-      <c r="C62" s="46" t="s">
+      <c r="D62" s="47"/>
+      <c r="E62" s="47"/>
+      <c r="F62" s="47"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="D62" s="46"/>
-      <c r="E62" s="46"/>
-      <c r="F62" s="46"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="45" t="s">
+      <c r="B63" s="46"/>
+      <c r="C63" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="B63" s="45"/>
-      <c r="C63" s="46" t="s">
+      <c r="D63" s="47"/>
+      <c r="E63" s="47"/>
+      <c r="F63" s="47"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="D63" s="46"/>
-      <c r="E63" s="46"/>
-      <c r="F63" s="46"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="45" t="s">
+      <c r="B64" s="46"/>
+      <c r="C64" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="B64" s="45"/>
-      <c r="C64" s="46" t="s">
+      <c r="D64" s="47"/>
+      <c r="E64" s="47"/>
+      <c r="F64" s="47"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="D64" s="46"/>
-      <c r="E64" s="46"/>
-      <c r="F64" s="46"/>
-    </row>
-    <row r="66" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="11" t="s">
+      <c r="B65" s="46"/>
+      <c r="C65" s="47" t="s">
         <v>91</v>
       </c>
-      <c r="B66" s="11"/>
-      <c r="C66" s="11"/>
-      <c r="D66" s="11"/>
-      <c r="E66" s="11"/>
-      <c r="F66" s="11"/>
-    </row>
-    <row r="67" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="6" t="s">
+      <c r="D65" s="47"/>
+      <c r="E65" s="47"/>
+      <c r="F65" s="47"/>
+    </row>
+    <row r="67" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B67" s="6"/>
-      <c r="C67" s="6" t="s">
+      <c r="B67" s="11"/>
+      <c r="C67" s="11"/>
+      <c r="D67" s="11"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="11"/>
+    </row>
+    <row r="68" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D67" s="6"/>
-      <c r="E67" s="6"/>
-      <c r="F67" s="7" t="s">
+      <c r="B68" s="6"/>
+      <c r="C68" s="6" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="47" t="s">
+      <c r="D68" s="6"/>
+      <c r="E68" s="6"/>
+      <c r="F68" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B68" s="47"/>
-      <c r="C68" s="48" t="s">
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="48" t="s">
         <v>96</v>
       </c>
-      <c r="D68" s="48"/>
-      <c r="E68" s="48"/>
-      <c r="F68" s="49">
+      <c r="B69" s="48"/>
+      <c r="C69" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="D69" s="49"/>
+      <c r="E69" s="49"/>
+      <c r="F69" s="50">
         <v>153</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="50" t="s">
-        <v>97</v>
-      </c>
-      <c r="B69" s="50"/>
-      <c r="C69" s="51" t="s">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="D69" s="51"/>
-      <c r="E69" s="51"/>
-      <c r="F69" s="52">
+      <c r="B70" s="51"/>
+      <c r="C70" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="D70" s="52"/>
+      <c r="E70" s="52"/>
+      <c r="F70" s="53">
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="B70" s="47"/>
-      <c r="C70" s="48" t="s">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="D70" s="48"/>
-      <c r="E70" s="48"/>
-      <c r="F70" s="49">
+      <c r="B71" s="48"/>
+      <c r="C71" s="49" t="s">
+        <v>101</v>
+      </c>
+      <c r="D71" s="49"/>
+      <c r="E71" s="49"/>
+      <c r="F71" s="50">
         <v>22.4568</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="B71" s="50"/>
-      <c r="C71" s="51" t="s">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="D71" s="51"/>
-      <c r="E71" s="51"/>
-      <c r="F71" s="52">
+      <c r="B72" s="51"/>
+      <c r="C72" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="D72" s="52"/>
+      <c r="E72" s="52"/>
+      <c r="F72" s="53">
         <v>44</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="47" t="s">
-        <v>103</v>
-      </c>
-      <c r="B72" s="47"/>
-      <c r="C72" s="48" t="s">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="48" t="s">
         <v>104</v>
       </c>
-      <c r="D72" s="48"/>
-      <c r="E72" s="48"/>
-      <c r="F72" s="53">
+      <c r="B73" s="48"/>
+      <c r="C73" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="D73" s="49"/>
+      <c r="E73" s="49"/>
+      <c r="F73" s="54">
         <v>2660</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="50" t="s">
-        <v>105</v>
-      </c>
-      <c r="B73" s="50"/>
-      <c r="C73" s="51" t="s">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="D73" s="51"/>
-      <c r="E73" s="51"/>
-      <c r="F73" s="52">
+      <c r="B74" s="51"/>
+      <c r="C74" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="D74" s="52"/>
+      <c r="E74" s="52"/>
+      <c r="F74" s="53">
         <v>180</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="B74" s="47"/>
-      <c r="C74" s="48" t="s">
-        <v>107</v>
-      </c>
-      <c r="D74" s="48"/>
-      <c r="E74" s="48"/>
-      <c r="F74" s="54">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="B75" s="48"/>
+      <c r="C75" s="49" t="s">
+        <v>108</v>
+      </c>
+      <c r="D75" s="49"/>
+      <c r="E75" s="49"/>
+      <c r="F75" s="55">
         <v>850524.2</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="50" t="s">
-        <v>108</v>
-      </c>
-      <c r="B75" s="50"/>
-      <c r="C75" s="51" t="s">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="51" t="s">
         <v>109</v>
       </c>
-      <c r="D75" s="51"/>
-      <c r="E75" s="51"/>
-      <c r="F75" s="55">
+      <c r="B76" s="51"/>
+      <c r="C76" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="D76" s="52"/>
+      <c r="E76" s="52"/>
+      <c r="F76" s="56">
         <v>3005.8</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="B76" s="47"/>
-      <c r="C76" s="48" t="s">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="48" t="s">
         <v>111</v>
       </c>
-      <c r="D76" s="48"/>
-      <c r="E76" s="48"/>
-      <c r="F76" s="54">
+      <c r="B77" s="48"/>
+      <c r="C77" s="49" t="s">
+        <v>112</v>
+      </c>
+      <c r="D77" s="49"/>
+      <c r="E77" s="49"/>
+      <c r="F77" s="55">
         <v>23400</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="50" t="s">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="51" t="s">
+        <v>44</v>
+      </c>
+      <c r="B78" s="51"/>
+      <c r="C78" s="52" t="s">
+        <v>113</v>
+      </c>
+      <c r="D78" s="52"/>
+      <c r="E78" s="52"/>
+      <c r="F78" s="56">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="B79" s="48"/>
+      <c r="C79" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="D79" s="49"/>
+      <c r="E79" s="49"/>
+      <c r="F79" s="55">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="51" t="s">
+        <v>116</v>
+      </c>
+      <c r="B80" s="51"/>
+      <c r="C80" s="52" t="s">
+        <v>117</v>
+      </c>
+      <c r="D80" s="52"/>
+      <c r="E80" s="52"/>
+      <c r="F80" s="56">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="B81" s="48"/>
+      <c r="C81" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="D81" s="49"/>
+      <c r="E81" s="49"/>
+      <c r="F81" s="55">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="B82" s="51"/>
+      <c r="C82" s="52" t="s">
+        <v>121</v>
+      </c>
+      <c r="D82" s="52"/>
+      <c r="E82" s="52"/>
+      <c r="F82" s="56">
+        <v>6582.72</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B77" s="50"/>
-      <c r="C77" s="51" t="s">
-        <v>112</v>
-      </c>
-      <c r="D77" s="51"/>
-      <c r="E77" s="51"/>
-      <c r="F77" s="55">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="B78" s="47"/>
-      <c r="C78" s="48" t="s">
-        <v>114</v>
-      </c>
-      <c r="D78" s="48"/>
-      <c r="E78" s="48"/>
-      <c r="F78" s="54">
-        <v>9600</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="50" t="s">
-        <v>115</v>
-      </c>
-      <c r="B79" s="50"/>
-      <c r="C79" s="51" t="s">
-        <v>116</v>
-      </c>
-      <c r="D79" s="51"/>
-      <c r="E79" s="51"/>
-      <c r="F79" s="55">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="47" t="s">
-        <v>117</v>
-      </c>
-      <c r="B80" s="47"/>
-      <c r="C80" s="48" t="s">
-        <v>118</v>
-      </c>
-      <c r="D80" s="48"/>
-      <c r="E80" s="48"/>
-      <c r="F80" s="54">
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="50" t="s">
-        <v>119</v>
-      </c>
-      <c r="B81" s="50"/>
-      <c r="C81" s="51" t="s">
-        <v>120</v>
-      </c>
-      <c r="D81" s="51"/>
-      <c r="E81" s="51"/>
-      <c r="F81" s="55">
-        <v>6582.72</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="47" t="s">
-        <v>42</v>
-      </c>
-      <c r="B82" s="47"/>
-      <c r="C82" s="48" t="s">
-        <v>121</v>
-      </c>
-      <c r="D82" s="48"/>
-      <c r="E82" s="48"/>
-      <c r="F82" s="54">
+      <c r="B83" s="48"/>
+      <c r="C83" s="49" t="s">
+        <v>122</v>
+      </c>
+      <c r="D83" s="49"/>
+      <c r="E83" s="49"/>
+      <c r="F83" s="55">
         <v>61200</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="B83" s="50"/>
-      <c r="C83" s="51" t="s">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="51" t="s">
         <v>123</v>
       </c>
-      <c r="D83" s="51"/>
-      <c r="E83" s="51"/>
-      <c r="F83" s="55">
+      <c r="B84" s="51"/>
+      <c r="C84" s="52" t="s">
+        <v>124</v>
+      </c>
+      <c r="D84" s="52"/>
+      <c r="E84" s="52"/>
+      <c r="F84" s="56">
         <v>7895.556</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="56" t="s">
-        <v>124</v>
-      </c>
-      <c r="B84" s="56"/>
-      <c r="C84" s="57" t="s">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="57" t="s">
         <v>125</v>
       </c>
-      <c r="D84" s="57"/>
-      <c r="E84" s="57"/>
-      <c r="F84" s="58">
+      <c r="B85" s="57"/>
+      <c r="C85" s="58" t="s">
+        <v>126</v>
+      </c>
+      <c r="D85" s="58"/>
+      <c r="E85" s="58"/>
+      <c r="F85" s="59">
         <v>974108.276</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="50" t="s">
-        <v>126</v>
-      </c>
-      <c r="B85" s="50"/>
-      <c r="C85" s="51" t="s">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="D85" s="51"/>
-      <c r="E85" s="51"/>
-      <c r="F85" s="55">
+      <c r="B86" s="51"/>
+      <c r="C86" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="D86" s="52"/>
+      <c r="E86" s="52"/>
+      <c r="F86" s="56">
         <v>6058.765243236716</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="47" t="s">
-        <v>128</v>
-      </c>
-      <c r="B86" s="47"/>
-      <c r="C86" s="48" t="s">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="48" t="s">
         <v>129</v>
       </c>
-      <c r="D86" s="48"/>
-      <c r="E86" s="48"/>
-      <c r="F86" s="54">
+      <c r="B87" s="48"/>
+      <c r="C87" s="49" t="s">
+        <v>130</v>
+      </c>
+      <c r="D87" s="49"/>
+      <c r="E87" s="49"/>
+      <c r="F87" s="55">
         <v>31587.931413768118</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="50" t="s">
-        <v>130</v>
-      </c>
-      <c r="B87" s="50"/>
-      <c r="C87" s="51" t="s">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="D87" s="51"/>
-      <c r="E87" s="51"/>
-      <c r="F87" s="55">
+      <c r="B88" s="51"/>
+      <c r="C88" s="52" t="s">
+        <v>132</v>
+      </c>
+      <c r="D88" s="52"/>
+      <c r="E88" s="52"/>
+      <c r="F88" s="56">
         <v>164704.29787439617</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="47" t="s">
-        <v>132</v>
-      </c>
-      <c r="B88" s="47"/>
-      <c r="C88" s="48" t="s">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="48" t="s">
         <v>133</v>
       </c>
-      <c r="D88" s="48"/>
-      <c r="E88" s="48"/>
-      <c r="F88" s="54">
+      <c r="B89" s="48"/>
+      <c r="C89" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="D89" s="49"/>
+      <c r="E89" s="49"/>
+      <c r="F89" s="55">
         <v>196292.22928816426</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="B89" s="50"/>
-      <c r="C89" s="51" t="s">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="51" t="s">
         <v>135</v>
       </c>
-      <c r="D89" s="51"/>
-      <c r="E89" s="51"/>
-      <c r="F89" s="55">
+      <c r="B90" s="51"/>
+      <c r="C90" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="D90" s="52"/>
+      <c r="E90" s="52"/>
+      <c r="F90" s="56">
         <v>38411.870740343</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="56" t="s">
-        <v>136</v>
-      </c>
-      <c r="B90" s="56"/>
-      <c r="C90" s="57" t="s">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="57" t="s">
         <v>137</v>
       </c>
-      <c r="D90" s="57"/>
-      <c r="E90" s="57"/>
-      <c r="F90" s="58">
+      <c r="B91" s="57"/>
+      <c r="C91" s="58" t="s">
+        <v>138</v>
+      </c>
+      <c r="D91" s="58"/>
+      <c r="E91" s="58"/>
+      <c r="F91" s="59">
         <v>1214871.141271744</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="56" t="s">
-        <v>138</v>
-      </c>
-      <c r="B91" s="56"/>
-      <c r="C91" s="57" t="s">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="57" t="s">
         <v>139</v>
       </c>
-      <c r="D91" s="57"/>
-      <c r="E91" s="57"/>
-      <c r="F91" s="58">
+      <c r="B92" s="57"/>
+      <c r="C92" s="58" t="s">
+        <v>140</v>
+      </c>
+      <c r="D92" s="58"/>
+      <c r="E92" s="58"/>
+      <c r="F92" s="59">
         <v>1018578.9119835796</v>
       </c>
     </row>
-    <row r="93" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="B93" s="11"/>
-      <c r="C93" s="11"/>
-      <c r="D93" s="11"/>
-      <c r="E93" s="11"/>
-      <c r="F93" s="11"/>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="45" t="s">
+    <row r="94" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="B94" s="45"/>
-      <c r="C94" s="46" t="s">
+      <c r="B94" s="11"/>
+      <c r="C94" s="11"/>
+      <c r="D94" s="11"/>
+      <c r="E94" s="11"/>
+      <c r="F94" s="11"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="46" t="s">
         <v>142</v>
       </c>
-      <c r="D94" s="46"/>
-      <c r="E94" s="46"/>
-      <c r="F94" s="46"/>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="45" t="s">
+      <c r="B95" s="46"/>
+      <c r="C95" s="47" t="s">
         <v>143</v>
       </c>
-      <c r="B95" s="45"/>
-      <c r="C95" s="46" t="s">
+      <c r="D95" s="47"/>
+      <c r="E95" s="47"/>
+      <c r="F95" s="47"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="46" t="s">
         <v>144</v>
       </c>
-      <c r="D95" s="46"/>
-      <c r="E95" s="46"/>
-      <c r="F95" s="46"/>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="45" t="s">
+      <c r="B96" s="46"/>
+      <c r="C96" s="47" t="s">
         <v>145</v>
       </c>
-      <c r="B96" s="45"/>
-      <c r="C96" s="46" t="s">
+      <c r="D96" s="47"/>
+      <c r="E96" s="47"/>
+      <c r="F96" s="47"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="46" t="s">
         <v>146</v>
       </c>
-      <c r="D96" s="46"/>
-      <c r="E96" s="46"/>
-      <c r="F96" s="46"/>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" s="45" t="s">
+      <c r="B97" s="46"/>
+      <c r="C97" s="47" t="s">
         <v>147</v>
       </c>
-      <c r="B97" s="45"/>
-      <c r="C97" s="46" t="s">
+      <c r="D97" s="47"/>
+      <c r="E97" s="47"/>
+      <c r="F97" s="47"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="46" t="s">
         <v>148</v>
       </c>
-      <c r="D97" s="46"/>
-      <c r="E97" s="46"/>
-      <c r="F97" s="46"/>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="45" t="s">
+      <c r="B98" s="46"/>
+      <c r="C98" s="47" t="s">
         <v>149</v>
       </c>
-      <c r="B98" s="45"/>
-      <c r="C98" s="46" t="s">
+      <c r="D98" s="47"/>
+      <c r="E98" s="47"/>
+      <c r="F98" s="47"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="46" t="s">
         <v>150</v>
       </c>
-      <c r="D98" s="46"/>
-      <c r="E98" s="46"/>
-      <c r="F98" s="46"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" s="45" t="s">
+      <c r="B99" s="46"/>
+      <c r="C99" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="B99" s="45"/>
-      <c r="C99" s="46" t="s">
+      <c r="D99" s="47"/>
+      <c r="E99" s="47"/>
+      <c r="F99" s="47"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="46" t="s">
         <v>152</v>
       </c>
-      <c r="D99" s="46"/>
-      <c r="E99" s="46"/>
-      <c r="F99" s="46"/>
-    </row>
-    <row r="101" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101" s="43" t="s">
+      <c r="B100" s="46"/>
+      <c r="C100" s="47" t="s">
         <v>153</v>
       </c>
-      <c r="B101" s="43"/>
-      <c r="C101" s="43"/>
-      <c r="D101" s="43"/>
-      <c r="E101" s="43"/>
-      <c r="F101" s="43"/>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D100" s="47"/>
+      <c r="E100" s="47"/>
+      <c r="F100" s="47"/>
+    </row>
+    <row r="102" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="44" t="s">
         <v>154</v>
       </c>
@@ -2664,440 +2702,450 @@
       <c r="E102" s="44"/>
       <c r="F102" s="44"/>
     </row>
-    <row r="104" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="B104" s="60" t="s">
-        <v>56</v>
-      </c>
-      <c r="C104" s="61" t="s">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="45" t="s">
         <v>155</v>
       </c>
-      <c r="D104" s="61"/>
-      <c r="E104" s="61"/>
-      <c r="F104" s="62">
+      <c r="B103" s="45"/>
+      <c r="C103" s="45"/>
+      <c r="D103" s="45"/>
+      <c r="E103" s="45"/>
+      <c r="F103" s="45"/>
+    </row>
+    <row r="105" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="60" t="s">
+        <v>43</v>
+      </c>
+      <c r="B105" s="61" t="s">
+        <v>57</v>
+      </c>
+      <c r="C105" s="62" t="s">
+        <v>156</v>
+      </c>
+      <c r="D105" s="62"/>
+      <c r="E105" s="62"/>
+      <c r="F105" s="63">
         <v>8</v>
       </c>
     </row>
-    <row r="105" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="63" t="s">
-        <v>156</v>
-      </c>
-      <c r="B105" s="64">
+    <row r="106" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="64" t="s">
+        <v>157</v>
+      </c>
+      <c r="B106" s="65">
         <v>130</v>
       </c>
-      <c r="C105" s="61" t="s">
-        <v>157</v>
-      </c>
-      <c r="D105" s="61"/>
-      <c r="E105" s="61"/>
-      <c r="F105" s="62">
+      <c r="C106" s="62" t="s">
+        <v>158</v>
+      </c>
+      <c r="D106" s="62"/>
+      <c r="E106" s="62"/>
+      <c r="F106" s="63">
         <v>36</v>
       </c>
     </row>
-    <row r="106" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="63" t="s">
-        <v>158</v>
-      </c>
-      <c r="B106" s="64">
+    <row r="107" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="64" t="s">
+        <v>159</v>
+      </c>
+      <c r="B107" s="65">
         <v>45</v>
       </c>
-      <c r="C106" s="61" t="s">
-        <v>159</v>
-      </c>
-      <c r="D106" s="61"/>
-      <c r="E106" s="61"/>
-      <c r="F106" s="62">
+      <c r="C107" s="62" t="s">
+        <v>160</v>
+      </c>
+      <c r="D107" s="62"/>
+      <c r="E107" s="62"/>
+      <c r="F107" s="63">
         <v>90</v>
       </c>
     </row>
-    <row r="107" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" s="59" t="s">
-        <v>160</v>
-      </c>
-      <c r="B107" s="60" t="s">
-        <v>56</v>
-      </c>
-      <c r="C107" s="61" t="s">
+    <row r="108" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="60" t="s">
         <v>161</v>
       </c>
-      <c r="D107" s="61"/>
-      <c r="E107" s="61"/>
-      <c r="F107" s="62">
+      <c r="B108" s="61" t="s">
+        <v>57</v>
+      </c>
+      <c r="C108" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="D108" s="62"/>
+      <c r="E108" s="62"/>
+      <c r="F108" s="63">
         <v>207.28</v>
       </c>
     </row>
-    <row r="108" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A108" s="63" t="s">
-        <v>162</v>
-      </c>
-      <c r="B108" s="65" t="s">
+    <row r="109" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="64" t="s">
         <v>163</v>
       </c>
-      <c r="C108" s="61" t="s">
+      <c r="B109" s="66" t="s">
         <v>164</v>
       </c>
-      <c r="D108" s="61"/>
-      <c r="E108" s="61"/>
-      <c r="F108" s="62">
+      <c r="C109" s="62" t="s">
+        <v>165</v>
+      </c>
+      <c r="D109" s="62"/>
+      <c r="E109" s="62"/>
+      <c r="F109" s="63">
         <v>40.14</v>
       </c>
     </row>
-    <row r="109" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A109" s="63" t="s">
-        <v>165</v>
-      </c>
-      <c r="B109" s="65" t="s">
+    <row r="110" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="64" t="s">
         <v>166</v>
       </c>
-      <c r="C109" s="61" t="s">
+      <c r="B110" s="66" t="s">
         <v>167</v>
       </c>
-      <c r="D109" s="61"/>
-      <c r="E109" s="61"/>
-      <c r="F109" s="62">
+      <c r="C110" s="62" t="s">
+        <v>168</v>
+      </c>
+      <c r="D110" s="62"/>
+      <c r="E110" s="62"/>
+      <c r="F110" s="63">
         <v>3.3</v>
       </c>
     </row>
-    <row r="110" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A110" s="63" t="s">
-        <v>168</v>
-      </c>
-      <c r="B110" s="65" t="s">
+    <row r="111" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="C110" s="61" t="s">
+      <c r="B111" s="66" t="s">
         <v>170</v>
       </c>
-      <c r="D110" s="61"/>
-      <c r="E110" s="61"/>
-      <c r="F110" s="62">
+      <c r="C111" s="62" t="s">
+        <v>171</v>
+      </c>
+      <c r="D111" s="62"/>
+      <c r="E111" s="62"/>
+      <c r="F111" s="63">
         <v>10.8</v>
       </c>
     </row>
-    <row r="111" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A111" s="59" t="s">
-        <v>171</v>
-      </c>
-      <c r="B111" s="60" t="s">
-        <v>56</v>
-      </c>
-      <c r="C111" s="61" t="s">
+    <row r="112" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="60" t="s">
         <v>172</v>
       </c>
-      <c r="D111" s="61"/>
-      <c r="E111" s="61"/>
-      <c r="F111" s="62">
+      <c r="B112" s="61" t="s">
+        <v>57</v>
+      </c>
+      <c r="C112" s="62" t="s">
+        <v>173</v>
+      </c>
+      <c r="D112" s="62"/>
+      <c r="E112" s="62"/>
+      <c r="F112" s="63">
         <v>10.95</v>
       </c>
     </row>
-    <row r="112" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="63" t="s">
-        <v>173</v>
-      </c>
-      <c r="B112" s="64">
+    <row r="113" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="64" t="s">
+        <v>174</v>
+      </c>
+      <c r="B113" s="65">
         <v>0</v>
       </c>
-      <c r="C112" s="61" t="s">
-        <v>174</v>
-      </c>
-      <c r="D112" s="61"/>
-      <c r="E112" s="61"/>
-      <c r="F112" s="62">
+      <c r="C113" s="62" t="s">
+        <v>175</v>
+      </c>
+      <c r="D113" s="62"/>
+      <c r="E113" s="62"/>
+      <c r="F113" s="63">
         <v>3.81</v>
       </c>
     </row>
-    <row r="113" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" s="63" t="s">
-        <v>175</v>
-      </c>
-      <c r="B113" s="64">
+    <row r="114" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="64" t="s">
+        <v>176</v>
+      </c>
+      <c r="B114" s="65">
         <v>500</v>
       </c>
-      <c r="C113" s="61" t="s">
-        <v>176</v>
-      </c>
-      <c r="D113" s="61"/>
-      <c r="E113" s="61"/>
-      <c r="F113" s="62">
+      <c r="C114" s="62" t="s">
+        <v>177</v>
+      </c>
+      <c r="D114" s="62"/>
+      <c r="E114" s="62"/>
+      <c r="F114" s="63">
         <v>2.84</v>
       </c>
     </row>
-    <row r="114" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" s="63" t="s">
-        <v>177</v>
-      </c>
-      <c r="B114" s="64">
+    <row r="115" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="64" t="s">
+        <v>178</v>
+      </c>
+      <c r="B115" s="65">
         <v>550</v>
       </c>
-      <c r="C114" s="61" t="s">
-        <v>178</v>
-      </c>
-      <c r="D114" s="61"/>
-      <c r="E114" s="61"/>
-      <c r="F114" s="62">
+      <c r="C115" s="62" t="s">
+        <v>179</v>
+      </c>
+      <c r="D115" s="62"/>
+      <c r="E115" s="62"/>
+      <c r="F115" s="63">
         <v>4.4</v>
       </c>
     </row>
-    <row r="115" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" s="63" t="s">
-        <v>179</v>
-      </c>
-      <c r="B115" s="64">
+    <row r="116" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="64" t="s">
+        <v>180</v>
+      </c>
+      <c r="B116" s="65">
         <v>600</v>
       </c>
-      <c r="C115" s="61" t="s">
-        <v>180</v>
-      </c>
-      <c r="D115" s="61"/>
-      <c r="E115" s="61"/>
-      <c r="F115" s="62">
+      <c r="C116" s="62" t="s">
+        <v>181</v>
+      </c>
+      <c r="D116" s="62"/>
+      <c r="E116" s="62"/>
+      <c r="F116" s="63">
         <v>97.12</v>
       </c>
     </row>
-    <row r="116" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" s="63" t="s">
-        <v>181</v>
-      </c>
-      <c r="B116" s="64">
+    <row r="117" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="64" t="s">
+        <v>182</v>
+      </c>
+      <c r="B117" s="65">
         <v>650</v>
       </c>
-      <c r="C116" s="61" t="s">
-        <v>182</v>
-      </c>
-      <c r="D116" s="61"/>
-      <c r="E116" s="61"/>
-      <c r="F116" s="62">
+      <c r="C117" s="62" t="s">
+        <v>183</v>
+      </c>
+      <c r="D117" s="62"/>
+      <c r="E117" s="62"/>
+      <c r="F117" s="63">
         <v>345</v>
       </c>
     </row>
-    <row r="117" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" s="63" t="s">
-        <v>183</v>
-      </c>
-      <c r="B117" s="64">
+    <row r="118" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="64" t="s">
+        <v>184</v>
+      </c>
+      <c r="B118" s="65">
         <v>700</v>
       </c>
-      <c r="C117" s="61" t="s">
-        <v>184</v>
-      </c>
-      <c r="D117" s="61"/>
-      <c r="E117" s="61"/>
-      <c r="F117" s="62">
+      <c r="C118" s="62" t="s">
+        <v>185</v>
+      </c>
+      <c r="D118" s="62"/>
+      <c r="E118" s="62"/>
+      <c r="F118" s="63">
         <v>546</v>
       </c>
     </row>
-    <row r="118" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" s="63" t="s">
-        <v>185</v>
-      </c>
-      <c r="B118" s="64">
+    <row r="119" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="64" t="s">
+        <v>186</v>
+      </c>
+      <c r="B119" s="65">
         <v>750</v>
       </c>
-      <c r="C118" s="61" t="s">
-        <v>186</v>
-      </c>
-      <c r="D118" s="61"/>
-      <c r="E118" s="61"/>
-      <c r="F118" s="62">
+      <c r="C119" s="62" t="s">
+        <v>187</v>
+      </c>
+      <c r="D119" s="62"/>
+      <c r="E119" s="62"/>
+      <c r="F119" s="63">
         <v>2.98</v>
       </c>
     </row>
-    <row r="119" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A119" s="63" t="s">
-        <v>187</v>
-      </c>
-      <c r="B119" s="64">
+    <row r="120" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="64" t="s">
+        <v>188</v>
+      </c>
+      <c r="B120" s="65">
         <v>800</v>
       </c>
-      <c r="C119" s="61" t="s">
-        <v>188</v>
-      </c>
-      <c r="D119" s="61"/>
-      <c r="E119" s="61"/>
-      <c r="F119" s="62">
+      <c r="C120" s="62" t="s">
+        <v>189</v>
+      </c>
+      <c r="D120" s="62"/>
+      <c r="E120" s="62"/>
+      <c r="F120" s="63">
         <v>8.08</v>
       </c>
     </row>
-    <row r="120" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A120" s="63" t="s">
-        <v>189</v>
-      </c>
-      <c r="B120" s="64">
+    <row r="121" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="64" t="s">
+        <v>190</v>
+      </c>
+      <c r="B121" s="65">
         <v>850</v>
       </c>
-      <c r="C120" s="61" t="s">
-        <v>190</v>
-      </c>
-      <c r="D120" s="61"/>
-      <c r="E120" s="61"/>
-      <c r="F120" s="62">
+      <c r="C121" s="62" t="s">
+        <v>191</v>
+      </c>
+      <c r="D121" s="62"/>
+      <c r="E121" s="62"/>
+      <c r="F121" s="63">
         <v>5.4</v>
       </c>
     </row>
-    <row r="121" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A121" s="59" t="s">
-        <v>191</v>
-      </c>
-      <c r="B121" s="60" t="s">
-        <v>56</v>
-      </c>
-      <c r="C121" s="61" t="s">
+    <row r="122" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="60" t="s">
         <v>192</v>
       </c>
-      <c r="D121" s="61"/>
-      <c r="E121" s="61"/>
-      <c r="F121" s="62">
+      <c r="B122" s="61" t="s">
+        <v>57</v>
+      </c>
+      <c r="C122" s="62" t="s">
+        <v>193</v>
+      </c>
+      <c r="D122" s="62"/>
+      <c r="E122" s="62"/>
+      <c r="F122" s="63">
         <v>300</v>
       </c>
     </row>
-    <row r="122" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" s="63" t="s">
-        <v>193</v>
-      </c>
-      <c r="B122" s="64">
+    <row r="123" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="64" t="s">
+        <v>194</v>
+      </c>
+      <c r="B123" s="65">
         <v>1170</v>
       </c>
-      <c r="C122" s="61" t="s">
-        <v>194</v>
-      </c>
-      <c r="D122" s="61"/>
-      <c r="E122" s="61"/>
-      <c r="F122" s="62">
+      <c r="C123" s="62" t="s">
+        <v>195</v>
+      </c>
+      <c r="D123" s="62"/>
+      <c r="E123" s="62"/>
+      <c r="F123" s="63">
         <v>40</v>
       </c>
     </row>
-    <row r="123" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" s="63" t="s">
-        <v>195</v>
-      </c>
-      <c r="B123" s="64">
+    <row r="124" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="64" t="s">
+        <v>196</v>
+      </c>
+      <c r="B124" s="65">
         <v>1560</v>
       </c>
-      <c r="C123" s="61" t="s">
-        <v>196</v>
-      </c>
-      <c r="D123" s="61"/>
-      <c r="E123" s="61"/>
-      <c r="F123" s="62">
+      <c r="C124" s="62" t="s">
+        <v>197</v>
+      </c>
+      <c r="D124" s="62"/>
+      <c r="E124" s="62"/>
+      <c r="F124" s="63">
         <v>172</v>
       </c>
     </row>
-    <row r="124" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124" s="63" t="s">
-        <v>197</v>
-      </c>
-      <c r="B124" s="64">
+    <row r="125" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="64" t="s">
+        <v>198</v>
+      </c>
+      <c r="B125" s="65">
         <v>1820</v>
       </c>
-      <c r="C124" s="61" t="s">
-        <v>198</v>
-      </c>
-      <c r="D124" s="61"/>
-      <c r="E124" s="61"/>
-      <c r="F124" s="62">
+      <c r="C125" s="62" t="s">
+        <v>199</v>
+      </c>
+      <c r="D125" s="62"/>
+      <c r="E125" s="62"/>
+      <c r="F125" s="63">
         <v>207</v>
       </c>
     </row>
-    <row r="125" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" s="63" t="s">
-        <v>199</v>
-      </c>
-      <c r="B125" s="64">
+    <row r="126" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="64" t="s">
+        <v>200</v>
+      </c>
+      <c r="B126" s="65">
         <v>3110</v>
       </c>
-      <c r="C125" s="61" t="s">
-        <v>200</v>
-      </c>
-      <c r="D125" s="61"/>
-      <c r="E125" s="61"/>
-      <c r="F125" s="62">
+      <c r="C126" s="62" t="s">
+        <v>201</v>
+      </c>
+      <c r="D126" s="62"/>
+      <c r="E126" s="62"/>
+      <c r="F126" s="63">
         <v>240</v>
       </c>
     </row>
-    <row r="126" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A126" s="63" t="s">
-        <v>201</v>
-      </c>
-      <c r="B126" s="64">
+    <row r="127" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="64" t="s">
+        <v>202</v>
+      </c>
+      <c r="B127" s="65">
         <v>2340</v>
       </c>
-      <c r="C126" s="61" t="s">
-        <v>202</v>
-      </c>
-      <c r="D126" s="61"/>
-      <c r="E126" s="61"/>
-      <c r="F126" s="62">
+      <c r="C127" s="62" t="s">
+        <v>203</v>
+      </c>
+      <c r="D127" s="62"/>
+      <c r="E127" s="62"/>
+      <c r="F127" s="63">
         <v>90</v>
       </c>
     </row>
-    <row r="127" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A127" s="63" t="s">
-        <v>203</v>
-      </c>
-      <c r="B127" s="64">
+    <row r="128" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="64" t="s">
+        <v>204</v>
+      </c>
+      <c r="B128" s="65">
         <v>10</v>
       </c>
-      <c r="C127" s="61" t="s">
-        <v>204</v>
-      </c>
-      <c r="D127" s="61"/>
-      <c r="E127" s="61"/>
-      <c r="F127" s="62">
+      <c r="C128" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="D128" s="62"/>
+      <c r="E128" s="62"/>
+      <c r="F128" s="63">
         <v>92</v>
       </c>
     </row>
-    <row r="128" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A128" s="63" t="s">
-        <v>205</v>
-      </c>
-      <c r="B128" s="64">
+    <row r="129" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" s="64" t="s">
+        <v>206</v>
+      </c>
+      <c r="B129" s="65">
         <v>20</v>
       </c>
-      <c r="C128" s="61" t="s">
-        <v>206</v>
-      </c>
-      <c r="D128" s="61"/>
-      <c r="E128" s="61"/>
-      <c r="F128" s="62">
+      <c r="C129" s="62" t="s">
+        <v>207</v>
+      </c>
+      <c r="D129" s="62"/>
+      <c r="E129" s="62"/>
+      <c r="F129" s="63">
         <v>112</v>
       </c>
     </row>
-    <row r="129" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129" s="59" t="s">
-        <v>207</v>
-      </c>
-      <c r="B129" s="60" t="s">
-        <v>56</v>
-      </c>
-      <c r="C129" s="61" t="s">
+    <row r="130" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" s="60" t="s">
         <v>208</v>
       </c>
-      <c r="D129" s="61"/>
-      <c r="E129" s="61"/>
-      <c r="F129" s="62">
+      <c r="B130" s="61" t="s">
+        <v>57</v>
+      </c>
+      <c r="C130" s="62" t="s">
+        <v>209</v>
+      </c>
+      <c r="D130" s="62"/>
+      <c r="E130" s="62"/>
+      <c r="F130" s="63">
         <v>170</v>
       </c>
     </row>
-    <row r="130" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130" s="63" t="s">
-        <v>209</v>
-      </c>
-      <c r="B130" s="64">
+    <row r="131" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" s="64" t="s">
+        <v>210</v>
+      </c>
+      <c r="B131" s="65">
         <v>45</v>
       </c>
-      <c r="C130" t="s">
-        <v>56</v>
-      </c>
-      <c r="D130"/>
-      <c r="E130"/>
-      <c r="F130" t="s">
-        <v>56</v>
+      <c r="C131" t="s">
+        <v>57</v>
+      </c>
+      <c r="D131"/>
+      <c r="E131"/>
+      <c r="F131" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="166">
+  <mergeCells count="167">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A2:D2"/>
@@ -3128,29 +3176,28 @@
     <mergeCell ref="D30:F30"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="D31:F31"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A34:F34"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="E35:F35"/>
-    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="E36:F36"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="B40:D40"/>
-    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="B41:D41"/>
     <mergeCell ref="A43:C43"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A49:C49"/>
     <mergeCell ref="A51:F51"/>
-    <mergeCell ref="A53:F53"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A54:F54"/>
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="C55:F55"/>
     <mergeCell ref="A56:B56"/>
@@ -3171,9 +3218,9 @@
     <mergeCell ref="C63:F63"/>
     <mergeCell ref="A64:B64"/>
     <mergeCell ref="C64:F64"/>
-    <mergeCell ref="A66:F66"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="C65:F65"/>
+    <mergeCell ref="A67:F67"/>
     <mergeCell ref="A68:B68"/>
     <mergeCell ref="C68:E68"/>
     <mergeCell ref="A69:B69"/>
@@ -3222,9 +3269,9 @@
     <mergeCell ref="C90:E90"/>
     <mergeCell ref="A91:B91"/>
     <mergeCell ref="C91:E91"/>
-    <mergeCell ref="A93:F93"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:F94"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="A94:F94"/>
     <mergeCell ref="A95:B95"/>
     <mergeCell ref="C95:F95"/>
     <mergeCell ref="A96:B96"/>
@@ -3235,9 +3282,10 @@
     <mergeCell ref="C98:F98"/>
     <mergeCell ref="A99:B99"/>
     <mergeCell ref="C99:F99"/>
-    <mergeCell ref="A101:F101"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="C100:F100"/>
     <mergeCell ref="A102:F102"/>
-    <mergeCell ref="C104:E104"/>
+    <mergeCell ref="A103:F103"/>
     <mergeCell ref="C105:E105"/>
     <mergeCell ref="C106:E106"/>
     <mergeCell ref="C107:E107"/>
@@ -3264,15 +3312,16 @@
     <mergeCell ref="C128:E128"/>
     <mergeCell ref="C129:E129"/>
     <mergeCell ref="C130:E130"/>
+    <mergeCell ref="C131:E131"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.25" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="78" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="82" fitToWidth="1" fitToHeight="1"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;8ul. Polna 5, Katowice&amp;R&amp;8Strona &amp;P z &amp;N</oddFooter>
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="49" max="16838" man="1"/>
-    <brk id="100" max="16838" man="1"/>
+    <brk id="50" max="16838" man="1"/>
+    <brk id="101" max="16838" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>